--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F035EAE8-32E8-4623-AA00-A89506FE76AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A085C0A5-02D0-4979-93F7-E631966FA866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -175,227 +175,6 @@
     <t>Instalación por ductos , no lleva pasamuros.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DIRECCIÓN </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Calle - Numero)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Instala Pasa-muros</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Roseta Óptica en norma y atornillada</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Deja Área de Trabajo Limpio</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Quien recibe en domicilio</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fotografía Roseta  Óptica Atornillada</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fotografías Pasa-muros</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Estado Auditoria</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Con que nota se evalúa al técnico</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Observaciones (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>detallar observaciones</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>Se llevó a cabo la mesa de trabajo.</t>
   </si>
   <si>
@@ -403,6 +182,69 @@
   </si>
   <si>
     <t xml:space="preserve">Observaciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRECCIÓN (Calle - Numero) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instala Pasa-muros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roseta Óptica en norma y atornillada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deja Área de Trabajo Limpio </t>
+  </si>
+  <si>
+    <t>Quien recibe en domicilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotografía Roseta  Óptica Atornillada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotografías Pasa-muros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado Auditoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con que nota se evalúa al técnico </t>
+  </si>
+  <si>
+    <t>Observaciones (detallar observaciones)</t>
+  </si>
+  <si>
+    <t>1-3N1OD3VC</t>
+  </si>
+  <si>
+    <t>LUIS ROBERTO QUIROGA SEGUEL</t>
+  </si>
+  <si>
+    <t>DANILO OJEDA</t>
+  </si>
+  <si>
+    <t>Modificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasaje diesiseis 4576, Quinta Normal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvara Ceron </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1xRoqVLV7TnRBkCtOSTEgYjJzWnnxmSh9</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HftL8nuwMbjUi_N_uPN54iieHc1SNhZ7</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=19_stumq0aaIfxRLjsrQcctleoeYxzyCD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1IfDHf1Ap0Yyo32pZFKUGiyCTMwkquF8X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No instala soporte drop, la capacitación sobre el uso del control, cliente manifestó que su hija lo vería después, ella no quedo clara, roseta instalada sobre 30 centímetros a petición de cliente. </t>
   </si>
 </sst>
 </file>
@@ -413,7 +255,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -446,26 +288,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -527,22 +349,6 @@
       </font>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
@@ -566,13 +372,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="secondRowStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -587,7 +409,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE4" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE5" headerRowDxfId="0">
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación"/>
@@ -826,7 +648,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
@@ -897,13 +719,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>11</v>
@@ -915,10 +737,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="T1" s="6" t="s">
         <v>14</v>
@@ -927,34 +749,34 @@
         <v>15</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Z1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AC1" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="AD1" s="7" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1197,6 +1019,86 @@
       </c>
       <c r="AB4" s="3" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>46243.7506640625</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5" t="s">
+        <v>70</v>
+      </c>
+      <c r="V5" t="s">
+        <v>71</v>
+      </c>
+      <c r="W5" t="s">
+        <v>72</v>
+      </c>
+      <c r="X5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA5">
+        <v>7</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A085C0A5-02D0-4979-93F7-E631966FA866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC88D161-5DD1-4B7A-A992-F59E220B815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4176" yWindow="2664" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="87">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -184,36 +184,6 @@
     <t xml:space="preserve">Observaciones </t>
   </si>
   <si>
-    <t xml:space="preserve">DIRECCIÓN (Calle - Numero) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instala Pasa-muros </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roseta Óptica en norma y atornillada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deja Área de Trabajo Limpio </t>
-  </si>
-  <si>
-    <t>Quien recibe en domicilio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotografía Roseta  Óptica Atornillada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotografías Pasa-muros </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado Auditoria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con que nota se evalúa al técnico </t>
-  </si>
-  <si>
-    <t>Observaciones (detallar observaciones)</t>
-  </si>
-  <si>
     <t>1-3N1OD3VC</t>
   </si>
   <si>
@@ -245,6 +215,266 @@
   </si>
   <si>
     <t xml:space="preserve">No instala soporte drop, la capacitación sobre el uso del control, cliente manifestó que su hija lo vería después, ella no quedo clara, roseta instalada sobre 30 centímetros a petición de cliente. </t>
+  </si>
+  <si>
+    <t>1-3N3QTY2X</t>
+  </si>
+  <si>
+    <t>BENJAMIN ALEJANDRO PEREZ POVEDA</t>
+  </si>
+  <si>
+    <t>ROLANDO MOTOYA</t>
+  </si>
+  <si>
+    <t>Reparacion</t>
+  </si>
+  <si>
+    <t>MEXICO 1163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANES AMADOR SABA MIOSOTI </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Ct3HMcGgtkRN1ays-ZSxeiG2cr3txlbM</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cAg185xHKS5Jvh4Ti7ijYMyyD7sf934v</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1FMSZOl4jm7NCv0YV2I76OTv48kR4YjC0</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1n6c6KG1MLLnZmc2xervPDiZcGEiOiCyi</t>
+  </si>
+  <si>
+    <t>No Cumple</t>
+  </si>
+  <si>
+    <t>Tecnico no utiliza one click segun procedimiento
+Cliente en reparacion representa problemas de inestabilidad en navegación ,desconexiones y lentitud en descargas
+Se verifica cobertura con app wifi analizar encontrando problemas de cobertura( -63dbm) ,se solicita repetidor wifi como mejoramiento de servicio en petición 1-3N4VBVMB quedando con -44 dbm -50 dbm y -38 dbm..veloc.en app marca 544 Mbps en domicilio ..se prueba conexiones con cliente quedando conforme .
+Nota se debió solicitar repetidor desde la.peticion de instalacion por técnico instalador de otras eps</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DIRECCIÓN </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Calle - Numero)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Instala Pasa-muros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Roseta Óptica en norma y atornillada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Deja Área de Trabajo Limpio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Quien recibe en domicilio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fotografía Roseta  Óptica Atornillada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fotografías Pasa-muros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Estado Auditoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Con que nota se evalúa al técnico</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Observaciones (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>detallar observaciones</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -255,7 +485,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -288,6 +518,26 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -335,7 +585,495 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -391,10 +1129,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="31"/>
+      <tableStyleElement type="headerRow" dxfId="30"/>
+      <tableStyleElement type="firstRowStripe" dxfId="29"/>
+      <tableStyleElement type="secondRowStripe" dxfId="28"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -409,36 +1147,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE5" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE6" headerRowDxfId="27">
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN "/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) "/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros "/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada "/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio "/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado "/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada "/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="5"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros "/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria "/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  "/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico "/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="4"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="3"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="2"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="1"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="0"/>
     <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo."/>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?"/>
     <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones "/>
@@ -648,10 +1386,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
     <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.33203125" bestFit="1" customWidth="1"/>
@@ -678,7 +1416,7 @@
     <col min="25" max="25" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="44.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="79.21875" customWidth="1"/>
     <col min="29" max="29" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="31.109375" bestFit="1" customWidth="1"/>
     <col min="31" max="34" width="18.88671875" customWidth="1"/>
@@ -719,13 +1457,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>11</v>
@@ -737,10 +1475,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="T1" s="6" t="s">
         <v>14</v>
@@ -749,25 +1487,25 @@
         <v>15</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="Z1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="AC1" s="7" t="s">
         <v>51</v>
@@ -1022,101 +1760,195 @@
       </c>
     </row>
     <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>46243.7506640625</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>0</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="T5" s="3">
+        <v>3</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46244.901713009254</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I5" t="s">
+      <c r="H6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J5" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="J6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="P6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="R6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="R5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" t="s">
-        <v>69</v>
-      </c>
-      <c r="T5">
-        <v>3</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="S6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="V5" t="s">
+      <c r="T6" s="3">
+        <v>4</v>
+      </c>
+      <c r="U6" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="W5" t="s">
+      <c r="V6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="X5" t="s">
+      <c r="W6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="Y5" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA5">
+      <c r="X6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA6" s="3">
         <v>7</v>
       </c>
-      <c r="AB5" t="s">
-        <v>74</v>
+      <c r="AB6" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{0FC40A9E-6577-4915-BCB0-B1E8B0C5B43B}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{E7EE3755-FDEB-4A1D-9847-1AFF42352F78}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{2E63DE00-29A2-4D8B-91B2-644F2B51DE6B}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{31F98311-D8AE-4B91-B12D-8841D2A76AF2}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{1B3D1CF7-0F23-4EB2-A5C6-65E09069C3BE}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{F5311F23-E6BB-42BC-B532-E57FFF2B5278}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{EE3D9668-F5C5-4ADC-B002-33E9A659A5CD}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{8393D88C-A544-4122-9F9F-22EED0124707}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{319FFB09-4F93-4494-9A84-2E078F74A086}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{E1DEA385-B299-4426-A5F6-33AFC883C9D8}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{47F14B85-FBBE-44A4-8BAA-38CFDF649266}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{3FD7782C-F3E7-4F8D-9FE4-C8B9E4CF51FA}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{8616A3D5-4CF6-4460-9110-C48FB7BB4A8D}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{510B5F45-5D38-47ED-9AC6-804A8D35DF10}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{7FCFAC9D-4976-4197-A85C-954E27D35602}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{BF686BCB-6CCE-4C70-A0FB-773C4B64C084}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{6ADD0EF1-32E0-46C3-8C91-9D43B112C7F5}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{79E4E284-65F0-48BC-AF3B-31CC8172F7B6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId19"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC88D161-5DD1-4B7A-A992-F59E220B815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5374CA92-4E43-4737-B0F3-66DCE1E21B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4176" yWindow="2664" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="105">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -475,6 +475,60 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>1-3N1EXTB4</t>
+  </si>
+  <si>
+    <t>JORGE LUIS REYES TOLOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alsino 4691 torre B dpto 54, Quinta Normal </t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>MINERVA DEL CARMEN LLANOS SANHUEZA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1YKKAkGD4EQW-dPfPbHSEbpsBuE7HuDQ2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PhtfDwK7_KSjjmrTzZRu8eaRaS76mByG</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qvV5AHtlp5_I4SZ6Ec-EBbt55zMespJ8</t>
+  </si>
+  <si>
+    <t>No limpia fibra con alcohol isopropilico, no capacita a cliente</t>
+  </si>
+  <si>
+    <t>1-3N4ZJYPV</t>
+  </si>
+  <si>
+    <t>EUDIS JESUS ALDAMA MARIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freirina 2024, Independencia </t>
+  </si>
+  <si>
+    <t>Guillermina Retamal Barrera</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1WwnXsHKOqdcxhVKy7K78PfZqcdpIXWPD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1a49an2Uxx5--xhVG5AJh9DzmiTTr-8zE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cFFm7QlOqMpnPhvBRjg5rcmtQTiDSSzl</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1hUQTu7-Yh2d6RG0qCUag9TKWRnYl2eLN</t>
+  </si>
+  <si>
+    <t>No instala pasa muros, cliente posee adaptador de red para decodificador por cobertura</t>
   </si>
 </sst>
 </file>
@@ -585,7 +639,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="33">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -721,6 +787,24 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
@@ -1073,18 +1157,6 @@
       </font>
       <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1129,10 +1201,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="31"/>
-      <tableStyleElement type="headerRow" dxfId="30"/>
-      <tableStyleElement type="firstRowStripe" dxfId="29"/>
-      <tableStyleElement type="secondRowStripe" dxfId="28"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="32"/>
+      <tableStyleElement type="headerRow" dxfId="31"/>
+      <tableStyleElement type="firstRowStripe" dxfId="30"/>
+      <tableStyleElement type="secondRowStripe" dxfId="29"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1147,36 +1219,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE6" headerRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE8" headerRowDxfId="0">
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="5"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros "/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="4"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="2"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="1"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="13"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="11"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="6"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="5"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="4"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="3"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="2"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="1"/>
     <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo."/>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?"/>
     <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones "/>
@@ -1386,7 +1458,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
@@ -1925,30 +1997,188 @@
         <v>76</v>
       </c>
     </row>
+    <row r="7" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46245.540172881942</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T7" s="3">
+        <v>3</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46245.569448587965</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T8" s="3">
+        <v>4</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{0FC40A9E-6577-4915-BCB0-B1E8B0C5B43B}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{E7EE3755-FDEB-4A1D-9847-1AFF42352F78}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{2E63DE00-29A2-4D8B-91B2-644F2B51DE6B}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{31F98311-D8AE-4B91-B12D-8841D2A76AF2}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{1B3D1CF7-0F23-4EB2-A5C6-65E09069C3BE}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{F5311F23-E6BB-42BC-B532-E57FFF2B5278}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{EE3D9668-F5C5-4ADC-B002-33E9A659A5CD}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{8393D88C-A544-4122-9F9F-22EED0124707}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{319FFB09-4F93-4494-9A84-2E078F74A086}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{E1DEA385-B299-4426-A5F6-33AFC883C9D8}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{47F14B85-FBBE-44A4-8BAA-38CFDF649266}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{3FD7782C-F3E7-4F8D-9FE4-C8B9E4CF51FA}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{8616A3D5-4CF6-4460-9110-C48FB7BB4A8D}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{510B5F45-5D38-47ED-9AC6-804A8D35DF10}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{7FCFAC9D-4976-4197-A85C-954E27D35602}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{BF686BCB-6CCE-4C70-A0FB-773C4B64C084}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{6ADD0EF1-32E0-46C3-8C91-9D43B112C7F5}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{79E4E284-65F0-48BC-AF3B-31CC8172F7B6}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{E29536BD-22BA-4D4A-B894-8F7490A52157}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{7E017801-0D52-46ED-A70D-82A9AEB5EE09}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{5115B7A9-9A0D-4AB8-BD01-973DAD17D50F}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{2D023C15-46CD-482F-AF5B-84F9A4519C91}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{C8CCBC35-B247-4467-959E-71228A520BDD}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{900B5C18-54A1-4936-933E-4C57AF2F212D}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{B49C1AE5-1CA1-42D6-8424-2F4CF7F9E870}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{187CED53-8A22-4D17-B9A7-864B2BE88286}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{C4231EE2-225B-45C9-B746-DC9FBF09A01A}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{25DB33BC-CF77-49A3-BC43-A81DA49A16D3}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{20BB0EE5-6687-4A61-9A9F-1A1CCD26B678}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{37AF6A1F-D79B-4AB7-AAE6-3B5FCF95F6DE}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{55414734-8555-4268-A5AB-26A52AE0085E}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{20E6C479-DCFA-410F-9D1F-F2A5C525FCA8}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{D5CF8C4C-E88D-4B73-8A9E-FCD7BA890C1A}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{B4908581-A4AF-47FE-B7BD-FEC258CFA399}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{4E90DEB7-8E00-4562-9BBA-38373DDBA8EC}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{58917473-CB6E-4031-9639-0E2BD165B5F5}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{6482190F-F05E-4A5E-8E71-E274537BF4E4}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{9AFD53CB-E99B-4BF1-9283-1792D9ABD9CE}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{D4FCE4C6-69C6-4FFC-8798-E17A8C63AA1E}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{095C23AD-063E-4571-AE12-F4CA242D0B95}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{8D85BF7D-66DA-4564-A78A-9B129D219D87}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{656B2AE2-976D-4D7A-8773-35C4398D5B0F}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{89B96F93-2346-49BE-8426-20724066CF10}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId19"/>
+    <tablePart r:id="rId26"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5374CA92-4E43-4737-B0F3-66DCE1E21B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B828D936-072D-4FF2-A845-10D509C6A055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="113">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -256,13 +256,66 @@
 Nota se debió solicitar repetidor desde la.peticion de instalacion por técnico instalador de otras eps</t>
   </si>
   <si>
+    <t>1-3N1EXTB4</t>
+  </si>
+  <si>
+    <t>JORGE LUIS REYES TOLOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alsino 4691 torre B dpto 54, Quinta Normal </t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>MINERVA DEL CARMEN LLANOS SANHUEZA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1YKKAkGD4EQW-dPfPbHSEbpsBuE7HuDQ2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PhtfDwK7_KSjjmrTzZRu8eaRaS76mByG</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qvV5AHtlp5_I4SZ6Ec-EBbt55zMespJ8</t>
+  </si>
+  <si>
+    <t>No limpia fibra con alcohol isopropilico, no capacita a cliente</t>
+  </si>
+  <si>
+    <t>1-3N4ZJYPV</t>
+  </si>
+  <si>
+    <t>EUDIS JESUS ALDAMA MARIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freirina 2024, Independencia </t>
+  </si>
+  <si>
+    <t>Guillermina Retamal Barrera</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1WwnXsHKOqdcxhVKy7K78PfZqcdpIXWPD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1a49an2Uxx5--xhVG5AJh9DzmiTTr-8zE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cFFm7QlOqMpnPhvBRjg5rcmtQTiDSSzl</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1hUQTu7-Yh2d6RG0qCUag9TKWRnYl2eLN</t>
+  </si>
+  <si>
+    <t>No instala pasa muros, cliente posee adaptador de red para decodificador por cobertura</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">DIRECCIÓN </t>
     </r>
@@ -270,18 +323,16 @@
       <rPr>
         <i/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Calle - Numero)</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -291,18 +342,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Instala Pasa-muros</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -312,18 +361,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Roseta Óptica en norma y atornillada</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -333,18 +380,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Deja Área de Trabajo Limpio</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -354,30 +399,45 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
-      <t>Quien recibe en domicilio</t>
+      <t xml:space="preserve">Quien </t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ecibe en domicilio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t>Fotografía Roseta  Óptica Atornillada</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -387,18 +447,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Fotografías Pasa-muros</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -408,18 +466,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Estado Auditoria</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -429,18 +485,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Con que nota se evalúa al técnico</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -450,18 +504,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Observaciones (</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>detallar observaciones</t>
     </r>
@@ -469,66 +521,35 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <t>1-3N1EXTB4</t>
-  </si>
-  <si>
-    <t>JORGE LUIS REYES TOLOZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alsino 4691 torre B dpto 54, Quinta Normal </t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>MINERVA DEL CARMEN LLANOS SANHUEZA</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1YKKAkGD4EQW-dPfPbHSEbpsBuE7HuDQ2</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1PhtfDwK7_KSjjmrTzZRu8eaRaS76mByG</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1qvV5AHtlp5_I4SZ6Ec-EBbt55zMespJ8</t>
-  </si>
-  <si>
-    <t>No limpia fibra con alcohol isopropilico, no capacita a cliente</t>
-  </si>
-  <si>
-    <t>1-3N4ZJYPV</t>
-  </si>
-  <si>
-    <t>EUDIS JESUS ALDAMA MARIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freirina 2024, Independencia </t>
-  </si>
-  <si>
-    <t>Guillermina Retamal Barrera</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1WwnXsHKOqdcxhVKy7K78PfZqcdpIXWPD</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1a49an2Uxx5--xhVG5AJh9DzmiTTr-8zE</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1cFFm7QlOqMpnPhvBRjg5rcmtQTiDSSzl</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1hUQTu7-Yh2d6RG0qCUag9TKWRnYl2eLN</t>
-  </si>
-  <si>
-    <t>No instala pasa muros, cliente posee adaptador de red para decodificador por cobertura</t>
+    <t>1-3N38LO21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuquen 1658, Quinta Normal </t>
+  </si>
+  <si>
+    <t>Jonhy Arevalo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1nF8b6PoUw5jmaMs3GmfPKH9f_sIPQnnU</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1bm95wbg0W4QfOhTQ-l3iSNpuXZbayYdA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=13gcBcAKvwZidaHyvwSsOryf5yBWRFTBU</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_qsmYESpm1TZYZBTcSA0bVI1OVnaOqPZ</t>
+  </si>
+  <si>
+    <t>No limpia fibra con alcohol isopropilico fibra</t>
   </si>
 </sst>
 </file>
@@ -568,30 +589,26 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -628,13 +645,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -642,18 +659,6 @@
   <dxfs count="33">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1100,42 +1105,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1157,6 +1126,54 @@
       </font>
       <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1219,36 +1236,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE8" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE9" headerRowDxfId="28">
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="6"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="4"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="3"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="2"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="7"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="6"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="5"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="4"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="3"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="2"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="1"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="0"/>
     <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo."/>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?"/>
     <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones "/>
@@ -1458,7 +1475,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
@@ -1494,98 +1511,98 @@
     <col min="31" max="34" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:31" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="T1" s="6" t="s">
+      <c r="R1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="T1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="X1" s="6" t="s">
+      <c r="V1" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="X1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AA1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AD1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AE1" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2005,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>56</v>
@@ -2029,31 +2046,31 @@
         <v>24</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="T7" s="3">
         <v>3</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>33</v>
@@ -2065,7 +2082,7 @@
         <v>5</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2076,10 +2093,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>56</v>
@@ -2100,7 +2117,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>24</v>
@@ -2118,22 +2135,22 @@
         <v>26</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="T8" s="3">
         <v>4</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>33</v>
@@ -2145,40 +2162,121 @@
         <v>9</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46246.746229016208</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="T9" s="3">
+        <v>4</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{E29536BD-22BA-4D4A-B894-8F7490A52157}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{7E017801-0D52-46ED-A70D-82A9AEB5EE09}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{5115B7A9-9A0D-4AB8-BD01-973DAD17D50F}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{2D023C15-46CD-482F-AF5B-84F9A4519C91}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{C8CCBC35-B247-4467-959E-71228A520BDD}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{900B5C18-54A1-4936-933E-4C57AF2F212D}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{B49C1AE5-1CA1-42D6-8424-2F4CF7F9E870}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{187CED53-8A22-4D17-B9A7-864B2BE88286}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{C4231EE2-225B-45C9-B746-DC9FBF09A01A}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{25DB33BC-CF77-49A3-BC43-A81DA49A16D3}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{20BB0EE5-6687-4A61-9A9F-1A1CCD26B678}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{37AF6A1F-D79B-4AB7-AAE6-3B5FCF95F6DE}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{55414734-8555-4268-A5AB-26A52AE0085E}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{20E6C479-DCFA-410F-9D1F-F2A5C525FCA8}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{D5CF8C4C-E88D-4B73-8A9E-FCD7BA890C1A}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{B4908581-A4AF-47FE-B7BD-FEC258CFA399}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{4E90DEB7-8E00-4562-9BBA-38373DDBA8EC}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{58917473-CB6E-4031-9639-0E2BD165B5F5}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{6482190F-F05E-4A5E-8E71-E274537BF4E4}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{9AFD53CB-E99B-4BF1-9283-1792D9ABD9CE}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{D4FCE4C6-69C6-4FFC-8798-E17A8C63AA1E}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{095C23AD-063E-4571-AE12-F4CA242D0B95}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{8D85BF7D-66DA-4564-A78A-9B129D219D87}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{656B2AE2-976D-4D7A-8773-35C4398D5B0F}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{89B96F93-2346-49BE-8426-20724066CF10}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{ECB9C61F-F161-4F4A-8170-27A4409D389E}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{33077E7B-DE7E-454A-BAAC-81A5895A258E}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{DE0E521E-8044-40ED-85CD-8869A0434307}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{D00C0ECA-EC36-4F4E-A834-AF624BDBD56E}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{A3C67D97-DD1B-458B-9AC1-E1BE53FE8A36}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{84494448-15AA-4E08-B261-110E6530D767}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{902E075E-066C-4968-B01B-82B8EEAA71C2}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{D1FE0C9F-7EB6-4D45-833D-5C47127BFFE0}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{3DC0F4C9-5BFA-4993-A71C-0035B4302991}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{C79E6FE6-C1C6-49E7-B991-807333642073}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{9ABA903E-319A-46D8-99D8-58C990695080}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{F52A1039-4F1A-4E97-BA0F-3512963D8A14}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{36046C2B-5137-42F0-8CAC-F522D68941FC}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{CD9D35E1-E24D-41E7-8A27-D1A96256E556}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{2487864B-6356-4F12-9315-7FCA70BB13E6}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{74291270-3351-4828-A536-EFC37237DC27}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{53170AC8-3F8D-46F6-A487-32E75E7ED861}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{BC429F76-876A-485D-B4A4-1A7763A39E3E}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{F17665B3-2253-480E-ADBF-D75AA532B8CC}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{D77891B9-D28E-4348-BBC3-21FB38BEAAAD}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{F205C755-7267-4BC7-AA4F-F28A862427BA}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{9AE81CEA-003A-4FCA-8CF2-7AB993D2D2F4}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{105B5417-1443-4706-8201-B786A3352CBB}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{7882F5A2-112A-4170-BD56-BC50F467443F}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{C91E0FA6-3D58-449F-8EDE-BA7D700AF1CD}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{40BEB3D2-4D5F-40C0-9148-BE0EA03719E2}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{E0802AEB-7A06-44B7-8EE0-B6BBDDFC8C3B}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{171EECC2-3B25-4FD0-9CF6-07CE04850B59}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{E941E6C1-80FD-4B85-9204-4767B9AE5805}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId26"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,19 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B828D936-072D-4FF2-A845-10D509C6A055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F218AA-AB62-4CFD-8F33-35F5F3CCD097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
+    <sheet name="masa de trabajo" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="114">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -550,6 +564,9 @@
   </si>
   <si>
     <t>No limpia fibra con alcohol isopropilico fibra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre </t>
   </si>
 </sst>
 </file>
@@ -611,15 +628,33 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B3F86"/>
+        <bgColor rgb="FF5B3F86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -627,11 +662,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF5B3F86"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -652,11 +696,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="34">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1105,7 +1169,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1124,7 +1187,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1143,6 +1205,7 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1161,6 +1224,7 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1218,10 +1282,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="32"/>
-      <tableStyleElement type="headerRow" dxfId="31"/>
-      <tableStyleElement type="firstRowStripe" dxfId="30"/>
-      <tableStyleElement type="secondRowStripe" dxfId="29"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="33"/>
+      <tableStyleElement type="headerRow" dxfId="32"/>
+      <tableStyleElement type="firstRowStripe" dxfId="31"/>
+      <tableStyleElement type="secondRowStripe" dxfId="30"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1236,37 +1300,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE9" headerRowDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE9" headerRowDxfId="29">
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="4"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="2"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="1"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo."/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="13"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="11"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="6"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="5"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="4"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="3"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="2"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="1"/>
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?"/>
     <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones "/>
   </tableColumns>
@@ -1506,7 +1572,7 @@
     <col min="26" max="26" width="44.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="31.5546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="79.21875" customWidth="1"/>
-    <col min="29" max="29" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="31.109375" bestFit="1" customWidth="1"/>
     <col min="31" max="34" width="18.88671875" customWidth="1"/>
   </cols>
@@ -1596,7 +1662,7 @@
       <c r="AB1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="10" t="s">
         <v>51</v>
       </c>
       <c r="AD1" s="5" t="s">
@@ -1689,6 +1755,10 @@
       <c r="AB2" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AC2" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
     </row>
     <row r="3" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -1767,6 +1837,10 @@
       <c r="AB3" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="AC3" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
     </row>
     <row r="4" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1847,6 +1921,10 @@
       <c r="AB4" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="AC4" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
     </row>
     <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1927,6 +2005,10 @@
       <c r="AB5" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="AC5" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2013,6 +2095,10 @@
       <c r="AB6" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="AC6" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
     </row>
     <row r="7" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2084,6 +2170,10 @@
       <c r="AB7" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="AC7" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2164,6 +2254,10 @@
       <c r="AB8" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="AC8" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2240,6 +2334,10 @@
       </c>
       <c r="AB9" s="3" t="s">
         <v>112</v>
+      </c>
+      <c r="AC9" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2279,4 +2377,54 @@
     <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B86AD5-214A-4E29-8C3C-D28012B13A5F}">
+  <dimension ref="B1:D4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F218AA-AB62-4CFD-8F33-35F5F3CCD097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153245E5-548F-4C80-B0D6-88E943A6F527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="114">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -654,7 +654,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -671,11 +671,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF5B3F86"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -711,6 +720,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2007,7 +2019,7 @@
       </c>
       <c r="AC5" s="11" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>SI</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2337,7 +2349,7 @@
       </c>
       <c r="AC9" s="11" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>SI</v>
       </c>
     </row>
   </sheetData>
@@ -2381,7 +2393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B86AD5-214A-4E29-8C3C-D28012B13A5F}">
-  <dimension ref="B1:D4"/>
+  <dimension ref="B1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
@@ -2424,6 +2436,14 @@
         <v>26</v>
       </c>
     </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153245E5-548F-4C80-B0D6-88E943A6F527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DF6B93-30D9-4089-AC1B-5A49ECF12A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="114">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AC7" s="11" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>SI</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2393,7 +2393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B86AD5-214A-4E29-8C3C-D28012B13A5F}">
-  <dimension ref="B1:D5"/>
+  <dimension ref="B1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
@@ -2444,6 +2444,14 @@
         <v>26</v>
       </c>
     </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DF6B93-30D9-4089-AC1B-5A49ECF12A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235627BE-DB4A-4AEA-8DFD-09290B5EF2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="132">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -324,224 +324,6 @@
     <t>No instala pasa muros, cliente posee adaptador de red para decodificador por cobertura</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">DIRECCIÓN </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(Calle - Numero)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Instala Pasa-muros</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Roseta Óptica en norma y atornillada</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Deja Área de Trabajo Limpio</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Quien </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>ecibe en domicilio</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Fotografía Roseta  Óptica Atornillada</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Fotografías Pasa-muros</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Estado Auditoria</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Con que nota se evalúa al técnico</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Observaciones (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>detallar observaciones</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>1-3N38LO21</t>
   </si>
   <si>
@@ -567,6 +349,90 @@
   </si>
   <si>
     <t xml:space="preserve">Nombre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRECCIÓN (Calle - Numero) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instala Pasa-muros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roseta Óptica en norma y atornillada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deja Área de Trabajo Limpio </t>
+  </si>
+  <si>
+    <t>Quien recibe en domicilio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotografía Roseta  Óptica Atornillada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotografías Pasa-muros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado Auditoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con que nota se evalúa al técnico </t>
+  </si>
+  <si>
+    <t>Observaciones (detallar observaciones)</t>
+  </si>
+  <si>
+    <t>1-3N5HPGPG</t>
+  </si>
+  <si>
+    <t>LUIS ROBERTO BAIGORRIA CORDOVA</t>
+  </si>
+  <si>
+    <t>Jackson 785 torre Y depto. 201</t>
+  </si>
+  <si>
+    <t>Andrés Díaz y Sra.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1CSmuYQmqrvrMUUa4nf16cG0GkGD3SynA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1C7xbpqRZdhbFYfcF4iO3wNkPMuE8MDbR</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1I5m3DHoB2XXOa5jOrNIsndX1rQFjkuR3</t>
+  </si>
+  <si>
+    <t>Roseta con clavo , pilar del edificio concreto.</t>
+  </si>
+  <si>
+    <t>1-3N6QA80X</t>
+  </si>
+  <si>
+    <t>MARCO ALEXANDER BENITEZ FERNANDEZ</t>
+  </si>
+  <si>
+    <t>Rodolfo Mondolfo 6865, Quinta Normal</t>
+  </si>
+  <si>
+    <t>LEONARDO ENRIQUE ROLACK REBOLLEDO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1OP1hPRSdOrAR3cXLiyxw1o2ogy31xmuT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1OujuqSLPbgqHCXkRhnw6h9V5HL8K4Mfe</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1WN_3WV6vkXedBc7VCDP6LUrRSoYcekyB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HSK3BJ7Qx0WE7hATyxPl7JT9fsOOK1DZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roseta instalada fuera de norma a petición de cliente, técnico cumple protocolo según informado hoy a todo el plantel en reunión. Queda pendiente auditoria post instalación </t>
+  </si>
+  <si>
+    <t>Auque se nota una mejora, se realizara evantualemete seguimiento a los trabajos</t>
   </si>
 </sst>
 </file>
@@ -577,7 +443,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -609,23 +475,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1312,7 +1161,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE9" headerRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE11" headerRowDxfId="29">
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="27"/>
@@ -1553,7 +1402,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
@@ -1624,13 +1473,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>11</v>
@@ -1642,10 +1491,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="T1" s="7" t="s">
         <v>14</v>
@@ -1654,25 +1503,25 @@
         <v>15</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="X1" s="7" t="s">
         <v>16</v>
       </c>
       <c r="Y1" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="Z1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="AA1" s="6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="AC1" s="10" t="s">
         <v>51</v>
@@ -1853,6 +1702,12 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
+      <c r="AD3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="4" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1937,6 +1792,9 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
+      <c r="AD4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -2279,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>55</v>
@@ -2303,7 +2161,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>26</v>
@@ -2318,22 +2176,22 @@
         <v>26</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="T9" s="3">
         <v>4</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>33</v>
@@ -2345,11 +2203,177 @@
         <v>8</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AC9" s="11" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46247.535424652779</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T10" s="3">
+        <v>4</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC10" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46247.71862049769</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="T11" s="3">
+        <v>4</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC11" s="11" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2403,7 +2427,7 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>51</v>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235627BE-DB4A-4AEA-8DFD-09290B5EF2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C53054-2907-4891-9B23-2ABDFE197279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -58,15 +58,6 @@
   </si>
   <si>
     <t>Motivo de la derivación</t>
-  </si>
-  <si>
-    <t>AUDITORIA</t>
-  </si>
-  <si>
-    <t>ACTIVIDAD</t>
-  </si>
-  <si>
-    <t>REUTILIZA INSTALACIÓN</t>
   </si>
   <si>
     <t>Repetidor Cableado</t>
@@ -351,36 +342,6 @@
     <t xml:space="preserve">Nombre </t>
   </si>
   <si>
-    <t xml:space="preserve">DIRECCIÓN (Calle - Numero) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instala Pasa-muros </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roseta Óptica en norma y atornillada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deja Área de Trabajo Limpio </t>
-  </si>
-  <si>
-    <t>Quien recibe en domicilio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotografía Roseta  Óptica Atornillada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotografías Pasa-muros </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado Auditoria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con que nota se evalúa al técnico </t>
-  </si>
-  <si>
-    <t>Observaciones (detallar observaciones)</t>
-  </si>
-  <si>
     <t>1-3N5HPGPG</t>
   </si>
   <si>
@@ -433,17 +394,281 @@
   </si>
   <si>
     <t>Auque se nota una mejora, se realizara evantualemete seguimiento a los trabajos</t>
+  </si>
+  <si>
+    <t>Auditoria</t>
+  </si>
+  <si>
+    <t>Actividad</t>
+  </si>
+  <si>
+    <t>Instala drop con soportes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utiliza OneClick para realizar limpieza a conectores </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop se encuentra encuentra dentro de norma de instalaciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reutiliza Instalación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utiliza Alcohol isopropilico </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reutiliza Instalación de otra compañía </t>
+  </si>
+  <si>
+    <t>1-3N5LOYRR</t>
+  </si>
+  <si>
+    <t>BRAULIO DANILO DIAZ CORNEJO</t>
+  </si>
+  <si>
+    <t>Post Instalacion</t>
+  </si>
+  <si>
+    <t>San Francisco 32 efif.H</t>
+  </si>
+  <si>
+    <t>Graciela Toro</t>
+  </si>
+  <si>
+    <t>Instalación acorde a los procedimientos.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DIRECCIÓN </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Calle - Numero)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Instala Pasa-muros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Roseta Óptica en norma y atornillada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Deja Área de Trabajo Limpio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Quien recibe en domicilio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fotografía Roseta  Óptica Atornillada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fotografías Pasa-muros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Estado Auditoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Con que nota se evalúa al técnico</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Observaciones (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>detallar observaciones</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
+    <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -470,14 +695,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,6 +758,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
         <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -530,10 +793,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -548,19 +812,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -573,14 +828,39 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bueno" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -663,6 +943,96 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <u/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
@@ -1012,6 +1382,7 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1030,7 +1401,12 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1066,7 +1442,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1085,20 +1460,7 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1143,10 +1505,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="33"/>
-      <tableStyleElement type="headerRow" dxfId="32"/>
-      <tableStyleElement type="firstRowStripe" dxfId="31"/>
-      <tableStyleElement type="secondRowStripe" dxfId="30"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="38"/>
+      <tableStyleElement type="headerRow" dxfId="37"/>
+      <tableStyleElement type="firstRowStripe" dxfId="36"/>
+      <tableStyleElement type="secondRowStripe" dxfId="35"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1161,41 +1523,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AE11" headerRowDxfId="29">
-  <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="AUDITORIA" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ACTIVIDAD" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="REUTILIZA INSTALACIÓN" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="6"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="4"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="3"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="2"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="1"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ12" headerRowDxfId="0">
+  <tableColumns count="36">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="10"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="8"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="6"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="5"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="4"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="3"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="2"/>
+    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="1"/>
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="31" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?"/>
-    <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones "/>
+    <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno"/>
+    <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones " dataCellStyle="Bueno"/>
   </tableColumns>
   <tableStyleInfo name="Respuestas de formulario 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1402,138 +1769,159 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="34.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40.109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="67.77734375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="64.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="67.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="69.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="68.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="68.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="69.33203125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="44.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="79.21875" customWidth="1"/>
-    <col min="29" max="29" width="22.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="18.88671875" customWidth="1"/>
+    <col min="28" max="28" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="48.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="58.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="33" style="15" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="33.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="76" style="16" bestFit="1" customWidth="1"/>
+    <col min="37" max="39" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:36" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="O1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="P1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="Q1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="O1" s="7" t="s">
+      <c r="R1" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="T1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="U1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="V1" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="W1" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="X1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="T1" s="7" t="s">
+      <c r="Y1" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>53</v>
+      <c r="AA1" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB1" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AC1" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF1" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG1" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI1" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ1" s="16" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46238.96527310185</v>
       </c>
@@ -1541,87 +1929,92 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="T2" s="3">
         <v>4</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Y2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="W2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="Z2" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA2" s="3">
         <v>6</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC2" s="11" t="str">
+        <v>31</v>
+      </c>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46241.444909525468</v>
       </c>
@@ -1629,87 +2022,92 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="T3" s="3">
         <v>4</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="W3" s="3"/>
       <c r="X3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA3" s="3">
         <v>9</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC3" s="11" t="str">
+        <v>39</v>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AD3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>131</v>
+      <c r="AI3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ3" s="16" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46241.449800138886</v>
       </c>
@@ -1717,86 +2115,91 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3">
         <v>2</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T4" s="3">
         <v>4</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="W4" s="3"/>
       <c r="X4" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA4" s="3">
         <v>9</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC4" s="11" t="str">
+        <v>47</v>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AD4" t="s">
-        <v>26</v>
+      <c r="AI4" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46243.7506640625</v>
       </c>
@@ -1804,83 +2207,88 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="M5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P5" s="3">
         <v>3</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="T5" s="3">
         <v>3</v>
       </c>
       <c r="U5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="X5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="V5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="Y5" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA5" s="3">
         <v>7</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC5" s="11" t="str">
+        <v>61</v>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46244.901713009254</v>
       </c>
@@ -1888,89 +2296,94 @@
         <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="I6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="M6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P6" s="3">
         <v>1</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="T6" s="3">
         <v>4</v>
       </c>
       <c r="U6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="X6" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="V6" s="4" t="s">
+      <c r="Y6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="W6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="Z6" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AA6" s="3">
         <v>7</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC6" s="11" t="str">
+        <v>73</v>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46245.540172881942</v>
       </c>
@@ -1978,74 +2391,79 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="R7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="T7" s="3">
         <v>3</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AA7" s="3">
         <v>5</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC7" s="11" t="str">
+        <v>82</v>
+      </c>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46245.569448587965</v>
       </c>
@@ -2053,83 +2471,88 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="L8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="N8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P8" s="3">
         <v>2</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T8" s="3">
         <v>4</v>
       </c>
       <c r="U8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X8" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="V8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="Y8" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA8" s="3">
         <v>9</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC8" s="11" t="str">
+        <v>91</v>
+      </c>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46246.746229016208</v>
       </c>
@@ -2137,80 +2560,85 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="L9" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T9" s="3">
         <v>4</v>
       </c>
       <c r="U9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="X9" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="V9" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="Y9" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z9" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA9" s="3">
         <v>8</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC9" s="11" t="str">
+        <v>99</v>
+      </c>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46247.535424652779</v>
       </c>
@@ -2218,81 +2646,82 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="L10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" s="3"/>
       <c r="P10" s="3">
         <v>2</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="T10" s="3">
         <v>4</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="W10" s="4"/>
+        <v>106</v>
+      </c>
       <c r="X10" s="4" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA10" s="3">
         <v>6</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC10" s="11" t="str">
+        <v>108</v>
+      </c>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46247.71862049769</v>
       </c>
@@ -2300,117 +2729,202 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="L11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="T11" s="3">
         <v>4</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA11" s="3">
         <v>10</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AC11" s="11" t="str">
+        <v>117</v>
+      </c>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
     </row>
+    <row r="12" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46248.497756516204</v>
+      </c>
+      <c r="B12" s="12">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="T12" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH12" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{ECB9C61F-F161-4F4A-8170-27A4409D389E}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{33077E7B-DE7E-454A-BAAC-81A5895A258E}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{DE0E521E-8044-40ED-85CD-8869A0434307}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{D00C0ECA-EC36-4F4E-A834-AF624BDBD56E}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{A3C67D97-DD1B-458B-9AC1-E1BE53FE8A36}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{84494448-15AA-4E08-B261-110E6530D767}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{902E075E-066C-4968-B01B-82B8EEAA71C2}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{D1FE0C9F-7EB6-4D45-833D-5C47127BFFE0}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{3DC0F4C9-5BFA-4993-A71C-0035B4302991}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{C79E6FE6-C1C6-49E7-B991-807333642073}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{9ABA903E-319A-46D8-99D8-58C990695080}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{F52A1039-4F1A-4E97-BA0F-3512963D8A14}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{36046C2B-5137-42F0-8CAC-F522D68941FC}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{CD9D35E1-E24D-41E7-8A27-D1A96256E556}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{2487864B-6356-4F12-9315-7FCA70BB13E6}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{74291270-3351-4828-A536-EFC37237DC27}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{53170AC8-3F8D-46F6-A487-32E75E7ED861}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{BC429F76-876A-485D-B4A4-1A7763A39E3E}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{F17665B3-2253-480E-ADBF-D75AA532B8CC}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{D77891B9-D28E-4348-BBC3-21FB38BEAAAD}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{F205C755-7267-4BC7-AA4F-F28A862427BA}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{9AE81CEA-003A-4FCA-8CF2-7AB993D2D2F4}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{105B5417-1443-4706-8201-B786A3352CBB}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{7882F5A2-112A-4170-BD56-BC50F467443F}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{C91E0FA6-3D58-449F-8EDE-BA7D700AF1CD}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{40BEB3D2-4D5F-40C0-9148-BE0EA03719E2}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{E0802AEB-7A06-44B7-8EE0-B6BBDDFC8C3B}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{171EECC2-3B25-4FD0-9CF6-07CE04850B59}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{E941E6C1-80FD-4B85-9204-4767B9AE5805}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{928FDE32-70C3-4514-B10C-E03DE7280F3B}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{151DBCEA-EB7F-43AB-B2D3-EE359DDAF7A5}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{8CAA54A6-D51B-4B8F-9489-2CA1FDCCD204}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{FD369774-514E-4330-A162-2CF380FC0D8C}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{66825895-59A9-4857-9E65-2A6F4947221A}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{351BBDB2-6281-4D06-B9CC-90131F35FB00}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{28F84FA8-7CFA-4D16-84C1-95F48C88C7F7}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{2903E959-838A-49E3-AFD0-9922466215DA}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{40DDDEDA-8FA1-441C-A64D-830230FD4529}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{AE4489E0-A99B-424D-A6E4-0847DCD98E4F}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{DF7BB78F-3F7D-48A6-8834-AAC7EA93C394}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{61D20909-19B0-4D98-A7A3-8F7773A306D7}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{3A77D6AF-FD64-40D5-9EF2-49352B9E3866}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{CC2A48A6-23B5-442E-8E0B-4CAF6678820E}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{FE8D3104-1971-4B08-B91A-E5FF6029DF10}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{8B979D93-B2D1-498E-A182-87EFCF5421DB}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{3909D0BF-6FBC-414C-B7FD-9ADB117218F6}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{9549DEC7-F666-4852-9B25-6470722BF37C}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{DEDE8073-13F2-4C48-A9DC-2461C2738143}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{71BFD655-2964-4E32-B4D4-DBBB0682D808}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{E59C4930-9074-4806-99F2-72DE6912C981}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{78781CA2-D18A-4C89-B48F-744A256EB6D3}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{C561A2DD-6636-47CC-8938-F3E53B7B465D}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{F5B317B2-C5FB-4F08-8333-AB9B824B78E7}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{87167069-779D-46BC-99B1-9813D880545B}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{FBB22F16-EE85-4424-806D-89EB0760E407}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{C2593A24-94EC-4094-B40E-A55C114573D0}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{E99AF70E-19EE-4545-8336-E8FEB292C425}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{9669B9AE-BFBF-4BCF-AB30-4506F393DD43}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{7228D0D9-755A-4D91-9FD0-2426106D69D7}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{0C57C04C-6F97-402A-A743-E2B29F44B4FF}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{3812AA5E-BEFF-4C2D-8E46-7C03866D4AA2}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{B2EEA60B-E1EF-4A7D-880F-452B1CD56FC4}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{9172DBC0-4E0F-4D3F-8573-E26E35557872}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{4C9A883F-FA70-4CCB-9662-93CFBF505DCE}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{4C092C3E-47ED-400B-AEE5-4AC69AFE5B3A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId37"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2421,59 +2935,59 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>52</v>
+      <c r="B1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>26</v>
+      <c r="B2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>26</v>
+      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>26</v>
+      <c r="B4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>26</v>
+      <c r="B5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>26</v>
+      <c r="B6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C53054-2907-4891-9B23-2ABDFE197279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE398D8-1647-41C7-9B89-AA04E84CBFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="157">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -442,9 +442,8 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">DIRECCIÓN </t>
     </r>
@@ -452,18 +451,16 @@
       <rPr>
         <i/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Calle - Numero)</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -473,18 +470,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Instala Pasa-muros</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -494,18 +489,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Roseta Óptica en norma y atornillada</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -515,18 +508,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Deja Área de Trabajo Limpio</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -536,30 +527,45 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
-      <t>Quien recibe en domicilio</t>
+      <t xml:space="preserve">Quien </t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ecibe en domicilio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t>Fotografía Roseta  Óptica Atornillada</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -569,18 +575,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Fotografías Pasa-muros</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -590,18 +594,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Estado Auditoria</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -611,18 +613,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Con que nota se evalúa al técnico</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -632,18 +632,16 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Observaciones (</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>detallar observaciones</t>
     </r>
@@ -651,12 +649,53 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>1-3N2YU675</t>
+  </si>
+  <si>
+    <t>ANDRES EDUARDO RODRIGUEZ BERMEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Castellon 4081, Quinta Normal </t>
+  </si>
+  <si>
+    <t>Victor Yañez</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=13PPlqo63EbZRR7L89FEGqMnXDfQv8n-r</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=17d52t5PmTfXPB9_QbA6OqPf9kiImuzOs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1lDE3Am1y1Mw5GWKg_p9mLlaSQGqGgcXE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1yLJtRMHB524hoNw9q5pILGEoIKZRcthN</t>
+  </si>
+  <si>
+    <t>Falta instalar pasa muros, a realizar preguntas a cliente indica haber aclarado las dudas del funcionamiento de forma correcta.</t>
+  </si>
+  <si>
+    <t>1-3N5H0O6V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio backer 5632, Quinta Normal </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1MKp2JuTG6FLN0ueQHwBGFuQSkTp8nAcB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ECZb-tJbGDX2bKOxosQrZyrzym9KBxL2</t>
+  </si>
+  <si>
+    <t>Sin moradores en domicilio, se evidencia al exterior que no se instala soporte drop, pasa muro instalado sin perforación adecuada</t>
   </si>
 </sst>
 </file>
@@ -709,30 +748,26 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -797,7 +832,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -831,18 +866,15 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -852,18 +884,6 @@
   <dxfs count="39">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1461,6 +1481,18 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1523,42 +1555,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ12" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ14" headerRowDxfId="34">
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="32"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="8"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="6"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="5"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="4"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="3"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="2"/>
-    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="1"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="31" dataCellStyle="Bueno">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno"/>
@@ -1769,7 +1801,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -1805,119 +1837,119 @@
     <col min="31" max="31" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="33" style="15" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="33.44140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="76" style="16" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="33" style="13" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="33.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="76" style="14" bestFit="1" customWidth="1"/>
     <col min="37" max="39" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="V1" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="W1" s="13" t="s">
+      <c r="W1" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Y1" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="Z1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AB1" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="AC1" s="14" t="s">
+      <c r="AC1" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="AD1" s="14" t="s">
+      <c r="AD1" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="AE1" s="14" t="s">
+      <c r="AE1" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="AF1" s="14" t="s">
+      <c r="AF1" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="AG1" s="14" t="s">
+      <c r="AG1" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="AH1" s="15" t="s">
+      <c r="AH1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AI1" s="16" t="s">
+      <c r="AI1" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="AJ1" s="16" t="s">
+      <c r="AJ1" s="14" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2009,7 +2041,7 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
-      <c r="AH2" s="15" t="str">
+      <c r="AH2" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
@@ -2096,14 +2128,14 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
-      <c r="AH3" s="15" t="str">
+      <c r="AH3" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI3" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
+      <c r="AI3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ3" s="14" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2191,11 +2223,11 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
-      <c r="AH4" s="15" t="str">
+      <c r="AH4" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI4" s="16" t="s">
+      <c r="AI4" s="14" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2283,7 +2315,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
-      <c r="AH5" s="15" t="str">
+      <c r="AH5" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
@@ -2378,7 +2410,7 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
-      <c r="AH6" s="15" t="str">
+      <c r="AH6" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
@@ -2458,7 +2490,7 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
-      <c r="AH7" s="15" t="str">
+      <c r="AH7" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
@@ -2547,7 +2579,7 @@
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
-      <c r="AH8" s="15" t="str">
+      <c r="AH8" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
@@ -2633,7 +2665,7 @@
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
-      <c r="AH9" s="15" t="str">
+      <c r="AH9" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
@@ -2716,7 +2748,7 @@
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
-      <c r="AH10" s="15" t="str">
+      <c r="AH10" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
@@ -2802,7 +2834,7 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-      <c r="AH11" s="15" t="str">
+      <c r="AH11" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
@@ -2877,7 +2909,163 @@
       <c r="AG12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH12" s="17" t="str">
+      <c r="AH12" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46251.615196585648</v>
+      </c>
+      <c r="B13" s="12">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="T13" s="3">
+        <v>4</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH13" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46251.636683425924</v>
+      </c>
+      <c r="B14" s="12">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH14" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
@@ -2885,46 +3073,52 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{928FDE32-70C3-4514-B10C-E03DE7280F3B}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{151DBCEA-EB7F-43AB-B2D3-EE359DDAF7A5}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{8CAA54A6-D51B-4B8F-9489-2CA1FDCCD204}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{FD369774-514E-4330-A162-2CF380FC0D8C}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{66825895-59A9-4857-9E65-2A6F4947221A}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{351BBDB2-6281-4D06-B9CC-90131F35FB00}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{28F84FA8-7CFA-4D16-84C1-95F48C88C7F7}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{2903E959-838A-49E3-AFD0-9922466215DA}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{40DDDEDA-8FA1-441C-A64D-830230FD4529}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{AE4489E0-A99B-424D-A6E4-0847DCD98E4F}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{DF7BB78F-3F7D-48A6-8834-AAC7EA93C394}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{61D20909-19B0-4D98-A7A3-8F7773A306D7}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{3A77D6AF-FD64-40D5-9EF2-49352B9E3866}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{CC2A48A6-23B5-442E-8E0B-4CAF6678820E}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{FE8D3104-1971-4B08-B91A-E5FF6029DF10}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{8B979D93-B2D1-498E-A182-87EFCF5421DB}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{3909D0BF-6FBC-414C-B7FD-9ADB117218F6}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{9549DEC7-F666-4852-9B25-6470722BF37C}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{DEDE8073-13F2-4C48-A9DC-2461C2738143}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{71BFD655-2964-4E32-B4D4-DBBB0682D808}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{E59C4930-9074-4806-99F2-72DE6912C981}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{78781CA2-D18A-4C89-B48F-744A256EB6D3}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{C561A2DD-6636-47CC-8938-F3E53B7B465D}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{F5B317B2-C5FB-4F08-8333-AB9B824B78E7}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{87167069-779D-46BC-99B1-9813D880545B}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{FBB22F16-EE85-4424-806D-89EB0760E407}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{C2593A24-94EC-4094-B40E-A55C114573D0}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{E99AF70E-19EE-4545-8336-E8FEB292C425}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{9669B9AE-BFBF-4BCF-AB30-4506F393DD43}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{7228D0D9-755A-4D91-9FD0-2426106D69D7}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{0C57C04C-6F97-402A-A743-E2B29F44B4FF}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{3812AA5E-BEFF-4C2D-8E46-7C03866D4AA2}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{B2EEA60B-E1EF-4A7D-880F-452B1CD56FC4}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{9172DBC0-4E0F-4D3F-8573-E26E35557872}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{4C9A883F-FA70-4CCB-9662-93CFBF505DCE}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{4C092C3E-47ED-400B-AEE5-4AC69AFE5B3A}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{C18A7375-F57A-422D-945F-7652445D4CCE}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{2A979DEA-3080-4AA5-B5A3-E483DB524CBB}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{C99500B9-4A6D-4E09-AD46-1C226E856AFA}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{3FF78D23-AC73-4B7A-920C-D847D9B188F7}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{FD064F0A-1AE9-42F9-B45B-CF0290216B80}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{A2A48E77-6CEC-4A18-928F-CB1877A999E4}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{86425FBA-D9A1-4E84-8E95-1C8B90DBC5E6}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{1D775A94-640D-4D31-8C97-C0489893C997}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{2F8A25A9-32CF-4346-9BC5-867946046E0B}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{5CE6E976-FC32-459A-8A18-1D8AE172C3DB}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{BF51F43A-700D-439B-BE04-0054C99040FC}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{7F9C9555-117D-4F77-B68E-78DCD348B80F}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{28E39AD5-1037-4CD0-9604-E8CF53D533C9}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{B976C44F-313A-4657-96F8-56CF5EE21998}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{A989E8A4-85C3-46FF-B32C-26222C8D5C0E}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{8B9E0D49-1A8A-4CC0-838F-682F425C6A17}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{A9D9CDBF-200F-4288-A6D6-36EF63746511}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{6D54FE32-9EE9-427E-8827-903B91BA052F}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{848447D3-FA11-415E-9483-5F49A0492512}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{7441AF73-ACB2-4476-8735-9BB9FF7C3C1D}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{FFED7C71-2BC4-44B4-9FED-D34D188660C2}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{F8C6FB1F-EB38-4D70-91C4-B00CD358DDFA}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{A8E94985-AD2A-44CD-99DD-570A752D948A}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{BD3DF216-56D0-487F-A360-15CDFAE625C9}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{1ADB044A-9827-411C-8CD1-24DF9121F660}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{AA5EC54A-4478-4CCF-8DE1-9BAD90C95DB9}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{A237596D-EF47-4A8A-9FDF-11E08F3ACD5E}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{99238E96-A2DA-48F6-A5AF-4F83E2F44BA2}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{6C8A59C2-2655-4657-9092-7D0B228F1679}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{0BC70EED-E16D-4287-9412-5591FA62CC34}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{7C5FB4D1-58A7-4798-964F-46CFD17221AD}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{1147AA11-EC31-48C3-8352-8E240061B15A}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{9680D075-0EFA-4E7C-8000-CD9E92DB0ABE}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{96962707-8728-4844-896D-DF1C87160943}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{F7E667F7-D27C-4D3C-9538-FB6ABAD3C465}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{2462645B-2405-431E-B709-DF5E3E292940}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{1D77C4CA-BD59-48B5-9D38-5A376A3DEA25}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{9E996261-0B20-4630-8F1C-4AE388A96DE7}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{53FA2B1A-EA26-4F01-BEC0-3A77DE86A3FB}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{E73F2177-CEFC-4799-AF2F-AD20B01EFC77}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{08D2A5A4-EE69-42AD-84AC-AFF2966667D2}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{F79A5801-6BDC-4276-8D9F-DFE1B9E7ED9D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId37"/>
+    <tablePart r:id="rId43"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE398D8-1647-41C7-9B89-AA04E84CBFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4DB7E6-D002-4155-8F3B-6818082235C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28950" yWindow="2475" windowWidth="17280" windowHeight="11805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="205">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -696,6 +696,155 @@
   </si>
   <si>
     <t>Sin moradores en domicilio, se evidencia al exterior que no se instala soporte drop, pasa muro instalado sin perforación adecuada</t>
+  </si>
+  <si>
+    <t>1-3N7Q47LB</t>
+  </si>
+  <si>
+    <t>JUAN PABLO CACERES SOBARZO</t>
+  </si>
+  <si>
+    <t>Limonares 399</t>
+  </si>
+  <si>
+    <t>Armando Aravena</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Q8vNcuhdAz4joWsuGjDNyWvbEU-wJasi</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1wg6HKw0vboOMxwjSBYFMyCoNLjQe2glH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1eSKueiB7HIUFlR7czqRlTA0kS2ueqrBv</t>
+  </si>
+  <si>
+    <t>Quinto técnico q visita a cliente realizando la instalacion</t>
+  </si>
+  <si>
+    <t>1-3N728IGS</t>
+  </si>
+  <si>
+    <t>MARIN ORELLANA HERNAN TOMAS</t>
+  </si>
+  <si>
+    <t>Howard 10</t>
+  </si>
+  <si>
+    <t>Josefina Astete</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1VJeC8kIARVBAXRJhaBg-HWlg535qIcyR</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=19fja4M2CuNqJHfMYCUY4xkR30-WEqb0T</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1vu-Eev9UKvXcT1YJ8o4Tt9Y-UNmKsclY</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14TYRsLkplV2F4PgRT-NqLGyJXyvd-eYE</t>
+  </si>
+  <si>
+    <t>Orden no se termina problema de dB , técnico sin chicote y falta de guía omologada</t>
+  </si>
+  <si>
+    <t>1-3N3AEQ7U</t>
+  </si>
+  <si>
+    <t>ALVARO IVAN HERRERA SALINAS</t>
+  </si>
+  <si>
+    <t>No hay derivacion</t>
+  </si>
+  <si>
+    <t>CATEDRAL 4245 DEPTO 1806 QUINTAN NORMAL</t>
+  </si>
+  <si>
+    <t>Omar fuentes</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1NGfQlyzAFNPmEvRedGZsf2pxU2BwIdRG</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1F83yxxgfvVETwqxnxgE5y_AiZliJsXcR</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qYERsMZYaQUmpyStu7SKkCOMWtWdsSgj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza mesa de trabajo informando indicadores operacional
+Se verifica estado de kit fo con fusionadora encontrado cortadora de fibra en mal estado (falta tornillo)
+Se informa la importancia de uso one click en terreno y el autochequeo de estado de herramientas 
+Se realiza cambio de cortadora fo en buen estado
+Ademas de realiza inducción en la entrega de servicios BA-IPTV a nucleo familiar 
+Se realizara seguimiento en terreno para ver su evolución </t>
+  </si>
+  <si>
+    <t>1-3N94E2SQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Brisas 0804, Recoleta </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=15KDgPCFq3sfPmtt5xX54MeAKk9jAUKVI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1K-xGQrbagf4oW-D6DTh5YlQTXxo403UC</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=183JRK--xQWbxG4bkT39QAKRZBROukIUS</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1mT_0H1IUWykWAH58LpNzTr7AD2cAcUIN</t>
+  </si>
+  <si>
+    <t>No utiliza one click, cliente conforme</t>
+  </si>
+  <si>
+    <t>1-3N9FYITR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel de Quintana 428, Independencia </t>
+  </si>
+  <si>
+    <t>Miguel Morales</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=12wtFt_wPMKaaRNepL8OxbL8THTvW1rpz</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=11NCk5q4BXejTZqIpnwKMwpnaeKMX6obP</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1gY7a-UzONH12AZX1pFa3JgqUrQtTqrdB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1MnC4kw_8M8wT0rlU24_dE4d_Ds8izo_E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roseta fuera de norma a petición de cliente, cliente indica tener problemas de cobertura en un extremo de la casa, se recomienda solicitar repetidor de señal. Instalación de ont ubicada en lugar solicitado por cliente </t>
+  </si>
+  <si>
+    <t>1-3N6CTV6X</t>
+  </si>
+  <si>
+    <t>Las Bandurrias  14</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1-QRkO5YpAkz38prf9Y9Bw8G2tEzPwMOB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1o_Awr_qJTuOGbya23lKOgpt8Qe3P_lbn</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_umJ2T0gHpdeAPP5rTnZeH-iCcxKr8BQ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TzdMGzyYx5WTozjYRFT2uT4JAqQdxQS9</t>
+  </si>
+  <si>
+    <t>Sin pasamuro.</t>
   </si>
 </sst>
 </file>
@@ -832,7 +981,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -876,6 +1025,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bueno" xfId="1" builtinId="26"/>
@@ -1402,7 +1554,7 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="0&quot; / 26&quot;"/>
+      <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1555,7 +1707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ14" headerRowDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ20" headerRowDxfId="34">
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
@@ -1801,7 +1953,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -3070,55 +3222,644 @@
         <v/>
       </c>
     </row>
+    <row r="15" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46252.401138136571</v>
+      </c>
+      <c r="B15" s="12">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="T15" s="3">
+        <v>4</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="V15" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH15" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46252.407164965276</v>
+      </c>
+      <c r="B16" s="12">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="T16" s="3">
+        <v>3</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="V16" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="AC16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH16" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46252.439018576391</v>
+      </c>
+      <c r="B17" s="12">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="T17" s="3">
+        <v>4</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH17" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46252.569284895828</v>
+      </c>
+      <c r="B18" s="12">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P18" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" s="3">
+        <v>4</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH18" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46252.579421759263</v>
+      </c>
+      <c r="B19" s="12">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T19" s="3">
+        <v>4</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="AD19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH19" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46252.687401099538</v>
+      </c>
+      <c r="B20" s="12">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P20" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" s="3">
+        <v>3</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH20" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{C18A7375-F57A-422D-945F-7652445D4CCE}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{2A979DEA-3080-4AA5-B5A3-E483DB524CBB}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{C99500B9-4A6D-4E09-AD46-1C226E856AFA}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{3FF78D23-AC73-4B7A-920C-D847D9B188F7}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{FD064F0A-1AE9-42F9-B45B-CF0290216B80}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{A2A48E77-6CEC-4A18-928F-CB1877A999E4}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{86425FBA-D9A1-4E84-8E95-1C8B90DBC5E6}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{1D775A94-640D-4D31-8C97-C0489893C997}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{2F8A25A9-32CF-4346-9BC5-867946046E0B}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{5CE6E976-FC32-459A-8A18-1D8AE172C3DB}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{BF51F43A-700D-439B-BE04-0054C99040FC}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{7F9C9555-117D-4F77-B68E-78DCD348B80F}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{28E39AD5-1037-4CD0-9604-E8CF53D533C9}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{B976C44F-313A-4657-96F8-56CF5EE21998}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{A989E8A4-85C3-46FF-B32C-26222C8D5C0E}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{8B9E0D49-1A8A-4CC0-838F-682F425C6A17}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{A9D9CDBF-200F-4288-A6D6-36EF63746511}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{6D54FE32-9EE9-427E-8827-903B91BA052F}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{848447D3-FA11-415E-9483-5F49A0492512}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{7441AF73-ACB2-4476-8735-9BB9FF7C3C1D}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{FFED7C71-2BC4-44B4-9FED-D34D188660C2}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{F8C6FB1F-EB38-4D70-91C4-B00CD358DDFA}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{A8E94985-AD2A-44CD-99DD-570A752D948A}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{BD3DF216-56D0-487F-A360-15CDFAE625C9}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{1ADB044A-9827-411C-8CD1-24DF9121F660}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{AA5EC54A-4478-4CCF-8DE1-9BAD90C95DB9}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{A237596D-EF47-4A8A-9FDF-11E08F3ACD5E}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{99238E96-A2DA-48F6-A5AF-4F83E2F44BA2}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{6C8A59C2-2655-4657-9092-7D0B228F1679}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{0BC70EED-E16D-4287-9412-5591FA62CC34}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{7C5FB4D1-58A7-4798-964F-46CFD17221AD}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{1147AA11-EC31-48C3-8352-8E240061B15A}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{9680D075-0EFA-4E7C-8000-CD9E92DB0ABE}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{96962707-8728-4844-896D-DF1C87160943}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{F7E667F7-D27C-4D3C-9538-FB6ABAD3C465}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{2462645B-2405-431E-B709-DF5E3E292940}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{1D77C4CA-BD59-48B5-9D38-5A376A3DEA25}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{9E996261-0B20-4630-8F1C-4AE388A96DE7}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{53FA2B1A-EA26-4F01-BEC0-3A77DE86A3FB}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{E73F2177-CEFC-4799-AF2F-AD20B01EFC77}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{08D2A5A4-EE69-42AD-84AC-AFF2966667D2}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{F79A5801-6BDC-4276-8D9F-DFE1B9E7ED9D}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{F074B214-0FDD-4430-8369-A80789829250}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{51897A81-7A03-498C-A6ED-04902ACBF1D9}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{8AA81FA1-CF4E-4033-82B8-28C9863D8B64}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{A4900D35-1E25-4465-B670-F4D46F6E9823}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{1375EBD7-F756-49B0-AAA5-8FAAB2742F90}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{B5765204-9E57-4F05-ADE2-9BBABD3471E5}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{9B8E23E8-C92B-455E-91CE-17E036B71DF9}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{80222361-0113-4923-9E01-E160B1566324}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{7221892A-A072-4270-8F83-30A70AA59D83}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{AE0FE29F-DC86-47FA-BF9C-4DCEE7B0B590}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{52BB7359-0F4C-4908-8302-938A882D7F9D}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{17A7A774-EBBA-4C67-8BFF-89FF61816373}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{A7330C1F-AB04-4DC7-BDCE-8370E6355A89}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{936F27DA-9560-47F2-AD99-9C8EBC8E1403}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{0876899B-5AF7-460A-8ED6-7D8ED1360738}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{3D391D16-9FD7-402E-932A-22397B2F2703}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{CCE01667-3879-4FBC-B42A-403B9678E9E9}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{3524F751-F6CC-4426-B85C-9000147D8E8A}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{4E300D6F-8B71-4A0D-A000-09B2D7817BC1}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{995AF8D2-03C6-412F-A2FF-953ABC2AA9AB}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{5E6C08B1-1117-4DD4-85E5-421057A21A03}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{0E87E15C-B428-4144-9A15-BEAFDAFB1333}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{02695654-60CB-46E7-A10F-5370162BBE58}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{F9A21E2A-1015-4C75-9FD8-45C10421D74B}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{4287ACA1-70F6-4EBC-9E24-D5D06124B05F}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{7ACD76F2-F51A-4A7A-AAE2-93EFD57D5547}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{AB907F9C-B8EB-423B-9F03-3D79A2C60D02}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{382E706F-4319-43BA-84C6-AE20617AF411}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{713AA810-2848-4EA9-A95D-068C6EE1EF6A}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{6F4D8370-AFE9-4781-B453-CD4BCC2064B2}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{BDFB4352-A49B-484F-AE71-7FC8C4CED582}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{C116C187-C50C-4A39-8F67-D06093EDAED6}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{CD4882C6-A031-461E-A249-0D4469CFA149}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{8F8F15E9-E4BE-4E7A-B627-1256C76BAC94}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{5828E232-C150-4146-8D0B-E8C6A793617D}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{6F59784C-47CB-433C-8AB6-D54EECEFC313}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{0ED10CF2-5EA0-4765-A7C7-32E2E22D6EE6}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{A4CAEFE2-3326-499A-939A-46DF68737693}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{4106326F-ADC9-495E-88B4-90CE70E02463}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{E6F98F59-7179-461C-96E8-E8B102C0FC46}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{75868555-3834-431C-B11D-706B60D73FBB}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{CC8D38F7-29BA-4A47-A72C-050F780662D7}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{2B95B493-85C1-43FA-94B3-CD80F1F6EA35}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{66A9CE89-643E-413E-95F4-B92307BBBBC1}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{1C6ADCF8-5733-49B8-9DA4-2D11B02C39C6}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{14F5E993-2F14-494C-BEFE-8D7692E14E50}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{949B44E7-184A-4B79-972F-C54A309C168F}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{D8A32C4D-5322-487F-93B7-69951C910DE2}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{645432C4-09A5-4EDA-8A14-ED46F662B090}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{FD74786F-C7FB-4025-A07D-EADDC3D65259}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{6256A995-9C71-45CE-A690-883B7F859678}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{7C49CC00-1C76-4784-914B-6D79974810C4}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{7B66F924-C8BA-4ACE-825E-ADF4D35C89D1}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{09CDC4E5-FA8E-4F7B-A16B-2C64FE7A373A}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{2C5421D0-AAA0-4622-BF39-2A39A7212583}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{1387915E-05F9-4574-9083-E772CBC5B22A}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{54CB73A7-27E8-490F-AB92-55F73C573670}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{5BA448A3-7E60-4856-83E9-BDEAC820EE89}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{0DC04BE8-FABD-405E-8CC2-C5E92006EBF3}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{0BB244AC-3B20-4E83-BB94-C702F4737100}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{5D04C855-4FAE-4F46-B027-5F2BB6ED4DCE}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{2FFED5D4-B99F-4C7A-8D36-CA59845A4530}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{526B139D-CC46-451E-B2EC-713C2D9106F9}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{14DC1D3A-AF57-4F93-9440-88A18566055F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId43"/>
+    <tablePart r:id="rId65"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4DB7E6-D002-4155-8F3B-6818082235C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB2B505-9CFC-4A8E-B7DB-A2A7368112F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28950" yWindow="2475" windowWidth="17280" windowHeight="11805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="221">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -845,6 +845,56 @@
   </si>
   <si>
     <t>Sin pasamuro.</t>
+  </si>
+  <si>
+    <t>1-3N9IKPTH</t>
+  </si>
+  <si>
+    <t>SEVILLA 1403</t>
+  </si>
+  <si>
+    <t>PABLO AURELIO SALDAÑA SANDALLA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1po2Usoq_zwtjp4HX44MoKrgj60hav7UT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1zg-fW83tan2MPbaZRDYhDZomtXiQ6a_c</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=19H2kjEx3lwbXwq9aKGzDGUKndI7loOGq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-TECNICO NO UTILIZA ONE CLICK EN TODOS LOS EXTREMOS (JUMPER, CTO)
+-TECNICO NO CAPACITA SERVICIOS ENTREGADOS EN SU TOTALIDAD
+ </t>
+  </si>
+  <si>
+    <t>solo utiliza onde click en roseta optica no en su totalidad</t>
+  </si>
+  <si>
+    <t>1-3NA4KLE5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tres de mayo 2685 edificio A dpto 204, independencia </t>
+  </si>
+  <si>
+    <t>Aisneis Monte Leon</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1yh0RqesENYxgJioTiLC6eCgf_izZmf_X</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1UA9NOOfm_FUsc0sAasPLGcVIysznqYuP</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1CN6XrDQMMT9mjrjBPVLl49l3NvnzY1BA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1IxhwifcGKSW_i_kYEj89Mmqxd2QowsBE</t>
+  </si>
+  <si>
+    <t>Auditoria en acompañamiento destacando el uso de herramientas según procedimiento ambos one click</t>
   </si>
 </sst>
 </file>
@@ -1554,6 +1604,24 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1579,24 +1647,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1707,24 +1757,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ20" headerRowDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ22" headerRowDxfId="34">
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="24"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="18"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="17"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
@@ -1742,7 +1792,7 @@
     <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
     <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="31" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno"/>
@@ -1953,7 +2003,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -3789,77 +3839,276 @@
         <v/>
       </c>
     </row>
+    <row r="21" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46253.408800335645</v>
+      </c>
+      <c r="B21" s="12">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="T21" s="3">
+        <v>4</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH21" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46254.036589560186</v>
+      </c>
+      <c r="B22" s="12">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="T22" s="3">
+        <v>4</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{F074B214-0FDD-4430-8369-A80789829250}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{51897A81-7A03-498C-A6ED-04902ACBF1D9}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{8AA81FA1-CF4E-4033-82B8-28C9863D8B64}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{A4900D35-1E25-4465-B670-F4D46F6E9823}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{1375EBD7-F756-49B0-AAA5-8FAAB2742F90}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{B5765204-9E57-4F05-ADE2-9BBABD3471E5}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{9B8E23E8-C92B-455E-91CE-17E036B71DF9}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{80222361-0113-4923-9E01-E160B1566324}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{7221892A-A072-4270-8F83-30A70AA59D83}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{AE0FE29F-DC86-47FA-BF9C-4DCEE7B0B590}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{52BB7359-0F4C-4908-8302-938A882D7F9D}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{17A7A774-EBBA-4C67-8BFF-89FF61816373}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{A7330C1F-AB04-4DC7-BDCE-8370E6355A89}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{936F27DA-9560-47F2-AD99-9C8EBC8E1403}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{0876899B-5AF7-460A-8ED6-7D8ED1360738}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{3D391D16-9FD7-402E-932A-22397B2F2703}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{CCE01667-3879-4FBC-B42A-403B9678E9E9}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{3524F751-F6CC-4426-B85C-9000147D8E8A}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{4E300D6F-8B71-4A0D-A000-09B2D7817BC1}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{995AF8D2-03C6-412F-A2FF-953ABC2AA9AB}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{5E6C08B1-1117-4DD4-85E5-421057A21A03}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{0E87E15C-B428-4144-9A15-BEAFDAFB1333}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{02695654-60CB-46E7-A10F-5370162BBE58}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{F9A21E2A-1015-4C75-9FD8-45C10421D74B}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{4287ACA1-70F6-4EBC-9E24-D5D06124B05F}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{7ACD76F2-F51A-4A7A-AAE2-93EFD57D5547}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{AB907F9C-B8EB-423B-9F03-3D79A2C60D02}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{382E706F-4319-43BA-84C6-AE20617AF411}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{713AA810-2848-4EA9-A95D-068C6EE1EF6A}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{6F4D8370-AFE9-4781-B453-CD4BCC2064B2}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{BDFB4352-A49B-484F-AE71-7FC8C4CED582}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{C116C187-C50C-4A39-8F67-D06093EDAED6}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{CD4882C6-A031-461E-A249-0D4469CFA149}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{8F8F15E9-E4BE-4E7A-B627-1256C76BAC94}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{5828E232-C150-4146-8D0B-E8C6A793617D}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{6F59784C-47CB-433C-8AB6-D54EECEFC313}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{0ED10CF2-5EA0-4765-A7C7-32E2E22D6EE6}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{A4CAEFE2-3326-499A-939A-46DF68737693}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{4106326F-ADC9-495E-88B4-90CE70E02463}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{E6F98F59-7179-461C-96E8-E8B102C0FC46}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{75868555-3834-431C-B11D-706B60D73FBB}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{CC8D38F7-29BA-4A47-A72C-050F780662D7}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{2B95B493-85C1-43FA-94B3-CD80F1F6EA35}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{66A9CE89-643E-413E-95F4-B92307BBBBC1}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{1C6ADCF8-5733-49B8-9DA4-2D11B02C39C6}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{14F5E993-2F14-494C-BEFE-8D7692E14E50}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{949B44E7-184A-4B79-972F-C54A309C168F}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{D8A32C4D-5322-487F-93B7-69951C910DE2}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{645432C4-09A5-4EDA-8A14-ED46F662B090}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{FD74786F-C7FB-4025-A07D-EADDC3D65259}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{6256A995-9C71-45CE-A690-883B7F859678}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{7C49CC00-1C76-4784-914B-6D79974810C4}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{7B66F924-C8BA-4ACE-825E-ADF4D35C89D1}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{09CDC4E5-FA8E-4F7B-A16B-2C64FE7A373A}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{2C5421D0-AAA0-4622-BF39-2A39A7212583}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{1387915E-05F9-4574-9083-E772CBC5B22A}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{54CB73A7-27E8-490F-AB92-55F73C573670}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{5BA448A3-7E60-4856-83E9-BDEAC820EE89}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{0DC04BE8-FABD-405E-8CC2-C5E92006EBF3}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{0BB244AC-3B20-4E83-BB94-C702F4737100}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{5D04C855-4FAE-4F46-B027-5F2BB6ED4DCE}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{2FFED5D4-B99F-4C7A-8D36-CA59845A4530}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{526B139D-CC46-451E-B2EC-713C2D9106F9}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{14DC1D3A-AF57-4F93-9440-88A18566055F}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{B030C6E6-5034-4848-81CF-8641E7D7AFB2}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{AA239873-5BD6-4A56-B697-1D7259E5BC9A}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{D3AB0D5D-1485-472E-B2D8-CF7883FAD414}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{E6E671EC-D130-45A0-AB76-17F89A65ECB5}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{944AB49E-D883-49FF-9E30-53C53D96478F}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{007AF93E-3CB5-46B2-B662-0863DD8C1523}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{62B9CF7D-5035-4B7B-815E-7C0072EB3CF1}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{4D38BFE4-5DA4-4692-A268-FE5EEBC50606}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{FA3DE097-3478-4B8A-BFA2-0E07DD869D7D}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{D135DE62-DA5E-46E7-BB44-97BE1C29D9D1}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{24211EEA-A17D-427A-8757-084BA9A12713}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{E5F43807-6116-41F2-90EE-2504BCFF8EC9}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{9401DEA7-EB67-4947-AA33-0BFE898BA76A}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{95EBC258-9412-4265-85EA-980472FF9246}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{2F9A8E26-475E-433A-AE43-7597A0111516}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{9C26BDE0-3498-4526-AC31-FDD478397B9F}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{E520F075-C74C-4ADE-ACA0-5EBD65540EC3}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{32516A13-00D9-47F0-B8C7-4E212B8C24C5}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{4C7BD0D9-9D72-4BC1-896B-010B76373971}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{3E607FEE-B2DC-469A-94A5-2C3591104FF1}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{2D5DADD7-18FB-49B0-B84B-A5A50D64CE73}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{2D3E5172-B7B0-407D-B2F5-7AD996B6157C}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{99587D12-E810-4F2F-9900-B676D307A2DF}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{9EFE860E-D08D-447E-8FB4-ACE8EF9840A6}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{2C09AEFF-D7D6-473B-B8D3-3503FDC5CE27}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{06CEEE9E-5CAF-4278-8C87-C2C2A1A17D47}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{A94B5D46-B551-4649-A3C2-19EFA76FBE6B}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{0CB06836-ADFD-4884-A23C-B706901AD323}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{28A2EF19-E9B6-483E-ABB9-57A9909C2540}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{1D398A7D-D433-4EB1-B5D4-80056844B864}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{0F762563-F34B-4890-BC29-2293F03E3C1D}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{B9A4D43B-4B5B-460C-9F92-28A113B7A176}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{C8EACADF-D7E0-4830-9E22-7072AA50A290}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{C4F6FD81-231F-400A-9A08-DAB55CE655E3}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{6F59AEB0-0056-4140-A361-9122DCBBEBCF}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{6D5CB434-494C-41B9-84D1-EEB271BB532C}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{368B636D-4237-4451-B684-B25178C9DB91}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{19A78072-DFD7-4C4B-A700-00987A189629}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{712086C6-C597-4E39-BC3D-D9B0258274B4}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{8680BD73-14DA-4DE9-A397-FC39B1555892}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{372B0DB4-6CB8-448E-86F7-E89D4066A58B}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{80ADC741-0128-4E71-BC3F-8E582441C74E}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{D457F657-599C-4DA5-99BF-15F2DEB2AD3D}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{D9770A56-0AC3-4522-8A61-7D64A22C512C}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{7A33022E-9A5A-4D0D-843C-7B5359C4443D}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{4A1BC44A-7309-4F72-8860-12EAEA6D928F}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{8E1240B7-1FD7-459E-B0A9-05956C153C2D}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{D5D498F4-514D-4419-B1EC-FF36210B32F4}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{6C1D13BF-0A2B-43CB-BC6D-A3E4AB11B1DD}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{07643EF6-1048-4EF2-93AF-7F430ED614CE}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{504F305B-905A-4C6F-923A-2B011EBBF8AF}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{5A325967-35BD-48D7-B798-88CFBC2E3110}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{817F3998-9ED2-451A-9C74-C8DAEA1E940C}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{12B11535-5500-4890-A8B0-43D1DB017F4D}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{DA823AC1-FDB5-4D2F-85A5-251070536798}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{2AB38C60-F189-4065-A2BC-AC97361CFFCE}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{C16A1E7A-200A-4D46-A930-9BBE3087E3E9}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{A073A344-CC58-49F6-8F29-5754AAA8FB89}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{798E352F-6C56-47C3-ACD9-658E4D07DE2D}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{B369A136-3155-4E94-9060-E3A28FDBE28A}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{600BBBC8-F2C6-47FF-92D1-87070C86FFCD}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{E620F418-0E40-49E8-8349-BD44B0EDEB5D}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{F72D076B-C15D-4607-9165-219D4A69C523}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{661E681C-4CB7-4C98-8AEB-584EA87063A3}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{ABB96280-84BF-4252-891E-EA5723745E20}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{F0F981D5-5242-4186-9B08-C005350AF47B}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{B74FC0E9-0F61-41C6-9BA6-CCD8D2D069B9}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{196B1BED-AC02-43EE-AC07-7ECC3FBE9E11}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{80FB6471-903C-429C-99A7-5D445B918C0D}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{DCD56D82-C463-41C1-BD5C-96F73D3F74FA}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{ED2A1E6B-47D9-4D83-9567-1C08F1ECE05F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId65"/>
+    <tablePart r:id="rId72"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB2B505-9CFC-4A8E-B7DB-A2A7368112F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90594F48-B883-42CC-B430-90B1E710B19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="239">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -895,6 +895,61 @@
   </si>
   <si>
     <t>Auditoria en acompañamiento destacando el uso de herramientas según procedimiento ambos one click</t>
+  </si>
+  <si>
+    <t>1-3ND1S289</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO HUAMANI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recabarren 1584, Independencia </t>
+  </si>
+  <si>
+    <t>Guillermo Puebla</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1FK9Fm-hJrywhyAtb6KX6xUgQ95_L8DCb</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1c7K51__DBi4S5c0_jXLS82vJyErpdcEl</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=175wmetPS8lkwNiPqFoJHg0ClHU-Xlywv</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ib28GsSsZ6_D2UPnN34V44_vE4lMsjT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servicio instalado, solo se instala repetidor, si explica el funcionamiento del servicio </t>
+  </si>
+  <si>
+    <t>1-3NA7AZB4</t>
+  </si>
+  <si>
+    <t>ZINC 531</t>
+  </si>
+  <si>
+    <t>EMILCE DEL CARMEN PEREZ PEREZ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=16MzYbpU1T2i6yGDx9YltGMm5BWUqBy8I</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1pn2uyjHZOjP3PxgwzAGWRciKrmPfAeUp</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1eQH55jHKTpEu_X7G0R-3gu5NlgYfY15z</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1xs2ayM4xI8WCoz54-Cy2bCmBOVwH4tJE</t>
+  </si>
+  <si>
+    <t>DEBILIDADES-TECNICO NO  CUMPLE CON NORMAS DE INSTALACION-NO INSTALA SOPORTE DROP.-NO INSTALA PASAMUROS.-SOLO CAPACITA EN FORMA PARCIAL PRODUCTOS INSTALADOS-NO MUESTRA TEST DE VELOCIDAD Y REALIZA PRUEBAS DE COBERTURA WIFI-TECNICO NFORMA A QUIEN CAPACITA EN DOMICILIO EN TOA-TECNICO SALE 4 VECES DE DOMICILIO DE CLIENTE A BUSCAR MATERIALES O  EQUIPOS 
+NOTA: SE CITA A MESA DE TRABAJO PARA REFLEXIONAR EN APLICAR MEJORAS PARA SER APLICADAS EN TERRENO</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -1075,8 +1130,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1757,7 +1812,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ22" headerRowDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ24" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ24" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="29"/>
@@ -2003,7 +2059,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ22"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -2334,9 +2390,6 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI3" s="14" t="s">
-        <v>23</v>
-      </c>
       <c r="AJ3" s="14" t="s">
         <v>118</v>
       </c>
@@ -2429,9 +2482,6 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI4" s="14" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="5" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -2785,6 +2835,9 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
+      <c r="AI8" s="14" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="9" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2952,7 +3005,10 @@
       <c r="AG10" s="3"/>
       <c r="AH10" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>SI</v>
+      </c>
+      <c r="AI10" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3040,6 +3096,9 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
+      <c r="AI11" s="14" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="12" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3113,7 +3172,10 @@
       </c>
       <c r="AH12" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>SI</v>
+      </c>
+      <c r="AI12" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3203,7 +3265,7 @@
       </c>
       <c r="AH13" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>SI</v>
       </c>
     </row>
     <row r="14" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3269,7 +3331,7 @@
       </c>
       <c r="AH14" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>SI</v>
       </c>
     </row>
     <row r="15" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3357,9 +3419,12 @@
       <c r="AG15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH15" s="17" t="str">
+      <c r="AH15" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
+      </c>
+      <c r="AI15" s="14" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3450,12 +3515,15 @@
       <c r="AG16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH16" s="17" t="str">
+      <c r="AH16" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
+      <c r="AI16" s="14" t="s">
+        <v>238</v>
+      </c>
     </row>
-    <row r="17" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46252.439018576391</v>
       </c>
@@ -3552,12 +3620,15 @@
       <c r="AG17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH17" s="17" t="str">
+      <c r="AH17" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
+      <c r="AI17" s="14" t="s">
+        <v>238</v>
+      </c>
     </row>
-    <row r="18" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46252.569284895828</v>
       </c>
@@ -3648,474 +3719,677 @@
       <c r="AG18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH18" s="17" t="str">
+      <c r="AH18" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46252.579421759263</v>
+      </c>
+      <c r="B19" s="12">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T19" s="3">
+        <v>4</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="AD19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH19" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46252.687401099538</v>
+      </c>
+      <c r="B20" s="12">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P20" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" s="3">
+        <v>3</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH20" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI20" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46253.408800335645</v>
+      </c>
+      <c r="B21" s="12">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="T21" s="3">
+        <v>4</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH21" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
+      <c r="AI21" s="14" t="s">
+        <v>238</v>
+      </c>
     </row>
-    <row r="19" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>46252.579421759263</v>
-      </c>
-      <c r="B19" s="12">
-        <v>7</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="3" t="s">
+    <row r="22" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46254.036589560186</v>
+      </c>
+      <c r="B22" s="12">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="T19" s="3">
+      <c r="I22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="T22" s="3">
         <v>4</v>
       </c>
-      <c r="U19" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="X19" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y19" s="3" t="s">
+      <c r="U22" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Z19" s="3" t="s">
+      <c r="Z22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AA19" s="3">
-        <v>9</v>
-      </c>
-      <c r="AB19" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="AD19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH19" s="17" t="str">
+      <c r="AA22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH22" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>46252.687401099538</v>
-      </c>
-      <c r="B20" s="12">
-        <v>8</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="3" t="s">
+    <row r="23" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46254.792688402777</v>
+      </c>
+      <c r="B23" s="12">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P20" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="T20" s="3">
-        <v>3</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="V20" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="W20" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="X20" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z20" s="3" t="s">
+      <c r="J23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P23" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="T23" s="3">
+        <v>4</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="V23" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="X23" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AA20" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH20" s="17" t="str">
+      <c r="Z23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="AH23" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
+      <c r="AI23" s="14" t="s">
+        <v>238</v>
+      </c>
     </row>
-    <row r="21" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>46253.408800335645</v>
-      </c>
-      <c r="B21" s="12">
+    <row r="24" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46255.391508726854</v>
+      </c>
+      <c r="B24" s="12">
         <v>7</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="K24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P24" s="3">
         <v>4</v>
       </c>
-      <c r="U21" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="V21" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="X21" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y21" s="3" t="s">
+      <c r="Q24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="T24" s="3">
+        <v>4</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Z21" s="3" t="s">
+      <c r="Z24" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AA21" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH21" s="17" t="str">
+      <c r="AA24" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH24" s="13" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>46254.036589560186</v>
-      </c>
-      <c r="B22" s="12">
-        <v>9</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="T22" s="3">
-        <v>4</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="V22" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="W22" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="X22" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>10</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v>SI</v>
+      <c r="AI24" s="14" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{B030C6E6-5034-4848-81CF-8641E7D7AFB2}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{AA239873-5BD6-4A56-B697-1D7259E5BC9A}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{D3AB0D5D-1485-472E-B2D8-CF7883FAD414}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{E6E671EC-D130-45A0-AB76-17F89A65ECB5}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{944AB49E-D883-49FF-9E30-53C53D96478F}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{007AF93E-3CB5-46B2-B662-0863DD8C1523}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{62B9CF7D-5035-4B7B-815E-7C0072EB3CF1}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{4D38BFE4-5DA4-4692-A268-FE5EEBC50606}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{FA3DE097-3478-4B8A-BFA2-0E07DD869D7D}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{D135DE62-DA5E-46E7-BB44-97BE1C29D9D1}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{24211EEA-A17D-427A-8757-084BA9A12713}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{E5F43807-6116-41F2-90EE-2504BCFF8EC9}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{9401DEA7-EB67-4947-AA33-0BFE898BA76A}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{95EBC258-9412-4265-85EA-980472FF9246}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{2F9A8E26-475E-433A-AE43-7597A0111516}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{9C26BDE0-3498-4526-AC31-FDD478397B9F}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{E520F075-C74C-4ADE-ACA0-5EBD65540EC3}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{32516A13-00D9-47F0-B8C7-4E212B8C24C5}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{4C7BD0D9-9D72-4BC1-896B-010B76373971}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{3E607FEE-B2DC-469A-94A5-2C3591104FF1}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{2D5DADD7-18FB-49B0-B84B-A5A50D64CE73}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{2D3E5172-B7B0-407D-B2F5-7AD996B6157C}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{99587D12-E810-4F2F-9900-B676D307A2DF}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{9EFE860E-D08D-447E-8FB4-ACE8EF9840A6}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{2C09AEFF-D7D6-473B-B8D3-3503FDC5CE27}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{06CEEE9E-5CAF-4278-8C87-C2C2A1A17D47}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{A94B5D46-B551-4649-A3C2-19EFA76FBE6B}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{0CB06836-ADFD-4884-A23C-B706901AD323}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{28A2EF19-E9B6-483E-ABB9-57A9909C2540}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{1D398A7D-D433-4EB1-B5D4-80056844B864}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{0F762563-F34B-4890-BC29-2293F03E3C1D}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{B9A4D43B-4B5B-460C-9F92-28A113B7A176}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{C8EACADF-D7E0-4830-9E22-7072AA50A290}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{C4F6FD81-231F-400A-9A08-DAB55CE655E3}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{6F59AEB0-0056-4140-A361-9122DCBBEBCF}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{6D5CB434-494C-41B9-84D1-EEB271BB532C}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{368B636D-4237-4451-B684-B25178C9DB91}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{19A78072-DFD7-4C4B-A700-00987A189629}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{712086C6-C597-4E39-BC3D-D9B0258274B4}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{8680BD73-14DA-4DE9-A397-FC39B1555892}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{372B0DB4-6CB8-448E-86F7-E89D4066A58B}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{80ADC741-0128-4E71-BC3F-8E582441C74E}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{D457F657-599C-4DA5-99BF-15F2DEB2AD3D}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{D9770A56-0AC3-4522-8A61-7D64A22C512C}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{7A33022E-9A5A-4D0D-843C-7B5359C4443D}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{4A1BC44A-7309-4F72-8860-12EAEA6D928F}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{8E1240B7-1FD7-459E-B0A9-05956C153C2D}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{D5D498F4-514D-4419-B1EC-FF36210B32F4}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{6C1D13BF-0A2B-43CB-BC6D-A3E4AB11B1DD}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{07643EF6-1048-4EF2-93AF-7F430ED614CE}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{504F305B-905A-4C6F-923A-2B011EBBF8AF}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{5A325967-35BD-48D7-B798-88CFBC2E3110}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{817F3998-9ED2-451A-9C74-C8DAEA1E940C}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{12B11535-5500-4890-A8B0-43D1DB017F4D}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{DA823AC1-FDB5-4D2F-85A5-251070536798}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{2AB38C60-F189-4065-A2BC-AC97361CFFCE}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{C16A1E7A-200A-4D46-A930-9BBE3087E3E9}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{A073A344-CC58-49F6-8F29-5754AAA8FB89}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{798E352F-6C56-47C3-ACD9-658E4D07DE2D}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{B369A136-3155-4E94-9060-E3A28FDBE28A}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{600BBBC8-F2C6-47FF-92D1-87070C86FFCD}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{E620F418-0E40-49E8-8349-BD44B0EDEB5D}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{F72D076B-C15D-4607-9165-219D4A69C523}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{661E681C-4CB7-4C98-8AEB-584EA87063A3}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{ABB96280-84BF-4252-891E-EA5723745E20}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{F0F981D5-5242-4186-9B08-C005350AF47B}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{B74FC0E9-0F61-41C6-9BA6-CCD8D2D069B9}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{196B1BED-AC02-43EE-AC07-7ECC3FBE9E11}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{80FB6471-903C-429C-99A7-5D445B918C0D}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{DCD56D82-C463-41C1-BD5C-96F73D3F74FA}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{ED2A1E6B-47D9-4D83-9567-1C08F1ECE05F}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{CC1C6A4D-BA28-46A2-8E4D-672E5FFA9E62}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{467E3562-8855-4C4C-B1A2-F2BD34B7CF6E}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{9F439889-0453-4FBB-9090-225D60B6E0D6}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{A1E785DE-E19D-454C-9654-AAB98215D47F}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{1B01A0BE-2C3B-4EA0-95D3-443E08339BA4}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{3B12B92A-1C48-47A5-99C4-5B77CF6C447E}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{6853FFB3-0D51-401D-A6C6-7192C898D12B}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{47F0305E-2E45-4F1D-887E-499C44C9FD93}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{743DB7EF-6B71-4795-BC78-B65FB9971FC7}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{82DF363E-6EDD-42F3-B32C-AEC2FE9BA956}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{08149FB3-06EC-4ACE-9B82-FA8D457C878A}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{073178A6-660C-468D-8356-7E48996D6ED5}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{D3DFCCA8-D86C-4980-B28C-9423167208AE}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{8A0D39CA-2DCA-4661-A6F0-600520D0EE5A}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{7E2F0AF9-998A-4B85-98B7-5D0E0C2791EA}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{5188DFCD-DB81-4216-90C9-99038E48BBC5}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{0683FCCF-997C-4932-93A9-B735D9580186}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{4F12467F-3D8E-408E-A56A-073A22E83921}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{C6973E02-3A44-420D-B06D-EBD0E48B96A0}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{A29B68B8-61BE-4F55-878B-A036DB9E8FB6}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{2C9235CC-57F9-4AEA-9AAB-8B021B4A5D70}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{DA126C45-7F77-4B5C-9DDF-68BABCC9CD5B}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{4D70E14B-1D2A-43F4-B9DC-BE8A25AAE5FC}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{434DE8F7-782D-444E-84AC-85FF87A654E4}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{832E1101-A3B2-4549-8613-B435071DF57C}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{79EF42FB-7D91-496F-AE23-20BF058BB930}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{0F41E506-A1CB-4BEF-8AF7-7D63388770A7}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{B3337BD0-7B82-4D0A-B5B1-D7B31DFC5B5F}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{5EC0A322-147E-46EF-950D-AE2D5C60A661}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{7CCA28DD-B08C-41A3-A0F1-EF7530687DAE}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{6243B771-99F5-4096-8F2B-3FE8B61FE757}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{2ABCED60-ACB5-4E18-9557-9F423BA1CAB5}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{AC3715A9-D98D-4DAA-85E4-AE346CB3954F}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{32E9BFE2-A487-454A-942D-F8773BAE6F96}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{DC3E2882-B180-415E-AA3E-20610D3684BF}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{21DD9906-4DCE-40DE-9659-22CE1A90E3F9}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{3EC9EDAE-3CA6-46B5-8017-4E896B6A4705}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{E43433E4-EFE2-417F-9D6A-F9BA34CAD1D2}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{DD64F449-ED75-4C10-8376-8189CB30C32A}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{F0700026-1339-426F-A2D2-A57F9339E48E}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{BD805CCB-6296-499D-AA04-3A864D03086B}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{D363FF88-730B-401A-8716-240BF3B74707}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{12C455D8-C174-488E-B42A-818E7334D0C9}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{276A615F-3F26-498D-ABFE-24E759BB46A6}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{D0F5EA43-E5C4-41CA-A22D-754D3CEB7960}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{BAE22079-4BD4-4794-8C21-7D2CB9F96B8A}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{EAEFCB34-3505-4458-BE96-6DF08D0AAB75}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{7D8C6A82-D310-4913-AEBB-CD692BF6A62C}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{1A41E6A8-9AED-40DF-8B0B-4234A920F452}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{9C376644-0BDA-4FB1-9678-BD152D419ECF}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{9171CEB0-852F-422B-8B6A-B6DD5BAFD314}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{F3FAC681-29C1-4A30-96AE-7453423A2289}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{79624BB7-30EE-4EEB-B81E-E67F8D8C7C9A}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{56013000-B6FB-4504-B209-85D4F44E914F}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{284BF505-FF72-476F-9F10-21BECD2FAFD1}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{CEE7FBF6-3E9A-4883-92DB-64176232F061}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{4ABAB1AA-55C1-4EED-940B-002C57AA3AC7}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{090E857D-7FAE-4901-AD5B-316263A2399D}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{54A3C90D-4824-4EBD-90C7-A4E5D5E0726C}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{FB7A8DFF-C23F-42DB-A5A3-78629B52F47C}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{8F01E87C-D20A-4FED-8A0C-451E73151393}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{B4D74665-111D-46CA-8074-16C6D8C3D5A5}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{8DB6F779-E34D-44CC-BFBF-463767ACCEAF}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{60161F0D-C0E6-4C77-AA80-5F63B6356AFC}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{7EF6CE74-2B97-4266-9FE7-13023611711F}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{BDED6300-59D0-41B8-B5DC-743F56777573}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{4864D513-7584-4776-BD94-0A9DF3B752D3}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{E182FB80-E353-4EEC-8007-12274C6267F5}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{EE1A98D7-82F7-4FC3-9816-9EC6B21218EC}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{052152B1-ADED-49B4-9C46-6048250451BD}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{054742A8-FCB9-4F8F-B6FC-D45094800446}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{AD5EBA87-454F-4ED5-ADDA-ECF79C71B772}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{EF2BBB34-4551-4296-A7F7-301CCECD1B8B}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{4873F9C8-04B2-480A-833D-09B43ED97444}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{324A8663-89DF-4AD7-8DDD-3A484A9A4EF1}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{E60B94BA-F80A-41AA-A5A1-4418E88AB8FE}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{72592308-CAB3-4D84-BBFE-3FB3CD997CCD}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{D9313C82-806A-4D00-86FA-E8B625DC1754}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{A240B47A-151A-43EC-AE6B-D6F18F4C9927}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId72"/>
+    <tablePart r:id="rId80"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B86AD5-214A-4E29-8C3C-D28012B13A5F}">
-  <dimension ref="B1:D6"/>
+  <dimension ref="B1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
@@ -4174,6 +4448,36 @@
         <v>23</v>
       </c>
     </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90594F48-B883-42CC-B430-90B1E710B19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E2E9B1-AF59-45D8-BF84-E3E1CED17990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -1140,6 +1140,10 @@
   </cellStyles>
   <dxfs count="39">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1677,31 +1681,7 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1737,6 +1717,26 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1815,40 +1815,40 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ24" headerRowDxfId="34">
   <autoFilter ref="A1:AJ24" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
-    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="31" dataCellStyle="Bueno">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="10"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="8"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="6"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="5"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="4"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="3"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="2"/>
+    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="1"/>
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="0" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno"/>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E2E9B1-AF59-45D8-BF84-E3E1CED17990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AD7A8B-2B48-4110-83D1-892896E69129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="253">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -950,6 +950,48 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>1-3NEATX1M</t>
+  </si>
+  <si>
+    <t>Aviador bleriot 2561, Quinta Normal</t>
+  </si>
+  <si>
+    <t>Alfonso Covarrubias</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Y8Cfh87znZW3suakDsP6fLxmlQ9Phsz-</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1uWNsEPoQ08EeVH9plTgpasLN8u23Qn5D</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=18AfFhcfGEXSZpB-3buXrF1NwAMcyDqaB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No corta pestaña y no deja tolerancia en roseta, instalación al interior por ductos, no se requiere pasa muros </t>
+  </si>
+  <si>
+    <t>1-3NDSEUY5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasaje 16 norte 809, Independencia </t>
+  </si>
+  <si>
+    <t>Miriam Antognoni cervantes</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qAx-W3NPyL2fXx2ueK9w5kZj5_2GVa1W</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Ys6nt4mKfVNhwTJ1l5mGZmPtCDTs2wiD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_rR7gN5y9InaQxMnPBe41qRYzIVGu2lO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repetidor, a petición de cliente no se instala cable utp por estética servicio okey, no instala pasa muros al interior </t>
   </si>
 </sst>
 </file>
@@ -1140,10 +1182,6 @@
   </cellStyles>
   <dxfs count="39">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1699,24 +1737,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1737,6 +1757,28 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1812,43 +1854,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ24" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ24" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ26" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ26" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="8"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="6"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="5"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="4"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="3"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="2"/>
-    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="1"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="0" dataCellStyle="Bueno">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="32" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno"/>
@@ -2059,44 +2101,44 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ24"/>
+  <dimension ref="A1:AJ26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="36.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="40.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="69.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="68.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="68.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="69.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="69.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="70.21875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="69.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="33.77734375" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="48.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="58.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="33" style="13" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="33.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="60.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="37.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="35.6640625" style="14" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="76" style="14" bestFit="1" customWidth="1"/>
     <col min="37" max="39" width="18.88671875" customWidth="1"/>
   </cols>
@@ -2303,6 +2345,9 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
+      <c r="AI2" s="14" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -2390,6 +2435,9 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
+      <c r="AI3" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ3" s="14" t="s">
         <v>118</v>
       </c>
@@ -2482,6 +2530,9 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
+      <c r="AI4" s="14" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="5" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -2666,6 +2717,9 @@
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
+      <c r="AI6" s="14" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2831,12 +2885,11 @@
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
-      <c r="AH8" s="13" t="str">
-        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+      <c r="AH8" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="AI8" s="14" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3620,12 +3673,11 @@
       <c r="AG17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH17" s="13" t="str">
-        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+      <c r="AH17" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="AI17" s="14" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4184,12 +4236,11 @@
       <c r="AB23" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="AH23" s="13" t="str">
-        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+      <c r="AH23" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="AI23" s="14" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4297,92 +4348,280 @@
         <v>238</v>
       </c>
     </row>
+    <row r="25" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46258.603575879628</v>
+      </c>
+      <c r="B25" s="12">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P25" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="T25" s="3">
+        <v>4</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB25" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="AD25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH25" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46258.674336504628</v>
+      </c>
+      <c r="B26" s="12">
+        <v>7</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="T26" s="3">
+        <v>4</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI26" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{CC1C6A4D-BA28-46A2-8E4D-672E5FFA9E62}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{467E3562-8855-4C4C-B1A2-F2BD34B7CF6E}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{9F439889-0453-4FBB-9090-225D60B6E0D6}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{A1E785DE-E19D-454C-9654-AAB98215D47F}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{1B01A0BE-2C3B-4EA0-95D3-443E08339BA4}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{3B12B92A-1C48-47A5-99C4-5B77CF6C447E}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{6853FFB3-0D51-401D-A6C6-7192C898D12B}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{47F0305E-2E45-4F1D-887E-499C44C9FD93}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{743DB7EF-6B71-4795-BC78-B65FB9971FC7}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{82DF363E-6EDD-42F3-B32C-AEC2FE9BA956}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{08149FB3-06EC-4ACE-9B82-FA8D457C878A}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{073178A6-660C-468D-8356-7E48996D6ED5}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{D3DFCCA8-D86C-4980-B28C-9423167208AE}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{8A0D39CA-2DCA-4661-A6F0-600520D0EE5A}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{7E2F0AF9-998A-4B85-98B7-5D0E0C2791EA}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{5188DFCD-DB81-4216-90C9-99038E48BBC5}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{0683FCCF-997C-4932-93A9-B735D9580186}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{4F12467F-3D8E-408E-A56A-073A22E83921}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{C6973E02-3A44-420D-B06D-EBD0E48B96A0}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{A29B68B8-61BE-4F55-878B-A036DB9E8FB6}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{2C9235CC-57F9-4AEA-9AAB-8B021B4A5D70}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{DA126C45-7F77-4B5C-9DDF-68BABCC9CD5B}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{4D70E14B-1D2A-43F4-B9DC-BE8A25AAE5FC}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{434DE8F7-782D-444E-84AC-85FF87A654E4}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{832E1101-A3B2-4549-8613-B435071DF57C}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{79EF42FB-7D91-496F-AE23-20BF058BB930}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{0F41E506-A1CB-4BEF-8AF7-7D63388770A7}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{B3337BD0-7B82-4D0A-B5B1-D7B31DFC5B5F}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{5EC0A322-147E-46EF-950D-AE2D5C60A661}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{7CCA28DD-B08C-41A3-A0F1-EF7530687DAE}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{6243B771-99F5-4096-8F2B-3FE8B61FE757}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{2ABCED60-ACB5-4E18-9557-9F423BA1CAB5}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{AC3715A9-D98D-4DAA-85E4-AE346CB3954F}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{32E9BFE2-A487-454A-942D-F8773BAE6F96}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{DC3E2882-B180-415E-AA3E-20610D3684BF}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{21DD9906-4DCE-40DE-9659-22CE1A90E3F9}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{3EC9EDAE-3CA6-46B5-8017-4E896B6A4705}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{E43433E4-EFE2-417F-9D6A-F9BA34CAD1D2}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{DD64F449-ED75-4C10-8376-8189CB30C32A}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{F0700026-1339-426F-A2D2-A57F9339E48E}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{BD805CCB-6296-499D-AA04-3A864D03086B}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{D363FF88-730B-401A-8716-240BF3B74707}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{12C455D8-C174-488E-B42A-818E7334D0C9}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{276A615F-3F26-498D-ABFE-24E759BB46A6}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{D0F5EA43-E5C4-41CA-A22D-754D3CEB7960}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{BAE22079-4BD4-4794-8C21-7D2CB9F96B8A}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{EAEFCB34-3505-4458-BE96-6DF08D0AAB75}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{7D8C6A82-D310-4913-AEBB-CD692BF6A62C}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{1A41E6A8-9AED-40DF-8B0B-4234A920F452}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{9C376644-0BDA-4FB1-9678-BD152D419ECF}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{9171CEB0-852F-422B-8B6A-B6DD5BAFD314}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{F3FAC681-29C1-4A30-96AE-7453423A2289}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{79624BB7-30EE-4EEB-B81E-E67F8D8C7C9A}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{56013000-B6FB-4504-B209-85D4F44E914F}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{284BF505-FF72-476F-9F10-21BECD2FAFD1}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{CEE7FBF6-3E9A-4883-92DB-64176232F061}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{4ABAB1AA-55C1-4EED-940B-002C57AA3AC7}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{090E857D-7FAE-4901-AD5B-316263A2399D}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{54A3C90D-4824-4EBD-90C7-A4E5D5E0726C}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{FB7A8DFF-C23F-42DB-A5A3-78629B52F47C}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{8F01E87C-D20A-4FED-8A0C-451E73151393}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{B4D74665-111D-46CA-8074-16C6D8C3D5A5}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{8DB6F779-E34D-44CC-BFBF-463767ACCEAF}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{60161F0D-C0E6-4C77-AA80-5F63B6356AFC}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{7EF6CE74-2B97-4266-9FE7-13023611711F}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{BDED6300-59D0-41B8-B5DC-743F56777573}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{4864D513-7584-4776-BD94-0A9DF3B752D3}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{E182FB80-E353-4EEC-8007-12274C6267F5}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{EE1A98D7-82F7-4FC3-9816-9EC6B21218EC}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{052152B1-ADED-49B4-9C46-6048250451BD}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{054742A8-FCB9-4F8F-B6FC-D45094800446}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{AD5EBA87-454F-4ED5-ADDA-ECF79C71B772}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{EF2BBB34-4551-4296-A7F7-301CCECD1B8B}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{4873F9C8-04B2-480A-833D-09B43ED97444}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{324A8663-89DF-4AD7-8DDD-3A484A9A4EF1}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{E60B94BA-F80A-41AA-A5A1-4418E88AB8FE}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{72592308-CAB3-4D84-BBFE-3FB3CD997CCD}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{D9313C82-806A-4D00-86FA-E8B625DC1754}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{A240B47A-151A-43EC-AE6B-D6F18F4C9927}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{B1551F2E-D649-46F5-AD93-638AA9E3B08E}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{DD4AA109-D4E0-4189-B8D5-79C63C37BB8E}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{84EE56AE-6FCE-4B26-9CF5-9EE862644737}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{6DC17868-89DC-4434-83D7-79ECC90F3B3C}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{A7342910-D5AB-46DC-AA0C-D8122FE5EE46}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{90AC6B81-EEA5-42A8-B403-24448698BDD6}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{F1305FD7-526F-42C2-9664-D8B973D8523D}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{3FDF89CE-1E32-4653-B45B-8344B4146440}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{EE9AAC32-384B-4994-A1A9-20F936434D5F}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{F0BB17ED-0CF0-45F9-BF2E-C8902817679E}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{EE42CA78-96AB-4BA6-9830-2D119CED6B47}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{89476D36-08E6-43AC-A6A6-5E25B2F0F7E6}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{801F90C0-10FA-448F-96D3-D4AC29FCAE5C}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{B77B93A5-52EE-4D9D-A925-4AB9BDD3F4A6}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{86AB1A6C-2E34-4C17-A303-79D168A54174}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{600B2645-4E3B-40CA-82ED-156AB6A3BF24}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{01914915-EA05-4BB6-9C17-EBBDAE677F1D}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{3AE432B3-143C-4D41-904D-29DCBDC11CEE}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{9D02F5BC-318D-41CC-B2E2-189BBB74FA43}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{FD13387E-EF8D-4DA2-812B-96CF19810622}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{B5E8C417-657E-467A-A764-AAA0B3CAD9B5}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{E653D8B6-DC8A-405F-9DAA-051ED4A2D3A4}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{D33F5D56-D9BB-445B-B484-E502C0B78524}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{8FFBC49C-3E73-4C34-917A-E2E53BE5C83B}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{A185999A-270B-4694-AFE6-FFEAEA09C8AE}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{37F028C2-B48C-4219-A4F7-D948EF096C7C}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{AEB16D3A-569E-4AF3-9744-B6BDF3F6C66B}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{E153B778-861C-4233-B742-BF0D23812A49}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{08A56267-6F88-41E3-AD33-8FA1988EB652}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{A3C66853-B443-4573-BBEE-F7A9FC0E3E4C}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{D355CCD4-D3EF-43FD-BE5D-DF786CA363D3}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{009BFF2E-832A-4091-BF95-48C541BE711A}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{B404C202-07C7-46F5-AD38-81D3A575B227}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{1412230B-6013-4405-9D17-DD6F9D425DDE}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{63659DBB-91CB-412B-894A-FC2AE91719F1}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{6D08ACB8-034F-4FAF-8EA8-93737A6A02C3}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{E6D09014-BBDB-416F-889A-754FA998FB62}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{88DF3E2B-B34F-4476-A5E9-D16ECC7F84E9}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{500F88FC-B4BC-4878-B03E-DE1A73D7FF72}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{74FF0473-3D00-49B2-A813-A4459395E42A}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{37D03C8B-1001-4ECC-A5FF-ABBBE87AB1CC}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{D7E41FA7-DEAB-4D3B-9045-C60E0E6B4398}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{5F3835A8-DADF-4553-B455-8C1ADC4701F8}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{A30B44A4-BB86-4972-A7D1-BFB8E7726A13}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{A4D3B59A-9E32-4225-AF0E-3571B15C06A8}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{8E4AA709-4702-4DEC-B160-A100F7537877}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{73DC6F62-DDD3-45DA-87E9-6B0E3E1858CD}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{C09A8B7A-2BD8-4209-9CED-F238F24B4650}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{09FE1492-F3B9-45C2-9EBE-9E137A5D007B}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{02BE52A7-4984-46A8-97D6-4CD9E31D5F2F}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{C2297B2E-1711-4B89-95E8-23CAFA4E7B2D}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{B0B38DF1-E229-4B1C-8848-732B112ADD01}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{CB2EEFD0-C76D-484D-9286-710A2E399CDD}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{6DF33D9D-CCA2-444B-B2FB-13F607A3CB1E}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{D2162218-B785-4B7D-937A-CB8CAFECDF60}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{02C8552F-C08F-4DB4-B68E-279598EB11D5}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{E007F30F-7CDF-4A4B-8D5E-345C89313D4F}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{9C987BEA-8326-458B-ADB6-405FAEAFF82B}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{0C649EEF-8B96-4DF3-95B9-C0378855FCF7}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{D1035CF2-931E-49D3-B66E-9D0607DCD9CF}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{F0EE632C-748E-4206-BEBB-84D399A85E3A}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{23E32943-F8B3-40E9-A94D-0FB3D2226574}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{FD18E3C4-DF03-484D-95DC-281739FF11AF}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{E76E066A-724C-4BBF-ADFD-42401AAD37D4}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{6F99A369-B7C9-4A91-80D6-C5BE05C155CD}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{80662600-D5DC-42DB-8748-B1C3B00DB090}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{461DA23C-397E-4079-B103-AAE7EDCC5527}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{6DA3345C-A54D-4C2B-96D2-EB88CDF59D72}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{45D79305-E487-4174-8A97-E39A1D3BE405}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{57992DA1-1929-4316-806A-366999CA4630}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{0FC07824-DE31-4D80-B5FD-3041D39EAC65}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{0538E868-E8C4-459A-9798-DF8FDD2DAFF5}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{3A13F6B6-50D4-41B9-8A37-6AAE2E9C9DC7}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{BDFD3D68-738A-4D64-9A81-57CF83F20D2E}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{71799FE5-0005-4714-B1EB-A7D6A64B8F84}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{E2A940EA-C426-4225-9E36-686A3C0C3BAE}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{A22EE25C-3127-41EF-8671-1E4638355C62}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{37F0E4FF-CE66-445F-98F3-82C8774CFF24}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{B94023F8-BB9C-478B-A635-16BFDDA3CAFA}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{FDCAB3E4-723D-4052-8521-AB455D832395}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{CADA814C-CDF4-40F5-8649-D69C6418FFE5}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{45CD97DC-6DBA-41A8-8B61-DABB0026CAB1}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{2E84B6F4-E690-4212-97AD-DE21A0775A35}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{AC12EF29-419D-4967-8AED-A354AE40FD29}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{5F0B022C-D004-4B87-BBBE-69B306815BB8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId80"/>
+    <tablePart r:id="rId86"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AD7A8B-2B48-4110-83D1-892896E69129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C18F64-19A4-4E76-A1F2-C22763B2F0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="262">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -992,6 +992,33 @@
   </si>
   <si>
     <t xml:space="preserve">Repetidor, a petición de cliente no se instala cable utp por estética servicio okey, no instala pasa muros al interior </t>
+  </si>
+  <si>
+    <t>1-3NDWKZA0</t>
+  </si>
+  <si>
+    <t>HECTOR SANTIS MEZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emilio campodonico 6342, Quinta Normal </t>
+  </si>
+  <si>
+    <t>Cecilia Marquez</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PFip0B7ufHKKeHnUeTAxyWSdWMcEPu7-</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1VREyEW1L4QF6a_uVmfAOAewpVhgupzXp</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TETN7AcbomP8by1FR1jjvR6VlAhtKclC</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1m-eN6jCH8z1x3lEFlvmJ5RNYEoGDthmr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No retira pestaña en roseta, no gestiona repetidor de señal para aumentar producción </t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1175,6 +1202,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bueno" xfId="1" builtinId="26"/>
@@ -1316,42 +1346,6 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
         <u/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
@@ -1762,6 +1756,42 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1854,43 +1884,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ26" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ26" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ27" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ27" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="32"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="2"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="1"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="31"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="32" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno"/>
@@ -2101,7 +2131,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ26"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -4530,98 +4560,192 @@
         <v>23</v>
       </c>
     </row>
+    <row r="27" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46260.768395266205</v>
+      </c>
+      <c r="B27" s="12">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="T27" s="3">
+        <v>4</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="V27" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="W27" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="X27" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH27" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{B1551F2E-D649-46F5-AD93-638AA9E3B08E}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{DD4AA109-D4E0-4189-B8D5-79C63C37BB8E}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{84EE56AE-6FCE-4B26-9CF5-9EE862644737}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{6DC17868-89DC-4434-83D7-79ECC90F3B3C}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{A7342910-D5AB-46DC-AA0C-D8122FE5EE46}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{90AC6B81-EEA5-42A8-B403-24448698BDD6}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{F1305FD7-526F-42C2-9664-D8B973D8523D}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{3FDF89CE-1E32-4653-B45B-8344B4146440}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{EE9AAC32-384B-4994-A1A9-20F936434D5F}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{F0BB17ED-0CF0-45F9-BF2E-C8902817679E}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{EE42CA78-96AB-4BA6-9830-2D119CED6B47}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{89476D36-08E6-43AC-A6A6-5E25B2F0F7E6}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{801F90C0-10FA-448F-96D3-D4AC29FCAE5C}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{B77B93A5-52EE-4D9D-A925-4AB9BDD3F4A6}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{86AB1A6C-2E34-4C17-A303-79D168A54174}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{600B2645-4E3B-40CA-82ED-156AB6A3BF24}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{01914915-EA05-4BB6-9C17-EBBDAE677F1D}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{3AE432B3-143C-4D41-904D-29DCBDC11CEE}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{9D02F5BC-318D-41CC-B2E2-189BBB74FA43}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{FD13387E-EF8D-4DA2-812B-96CF19810622}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{B5E8C417-657E-467A-A764-AAA0B3CAD9B5}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{E653D8B6-DC8A-405F-9DAA-051ED4A2D3A4}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{D33F5D56-D9BB-445B-B484-E502C0B78524}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{8FFBC49C-3E73-4C34-917A-E2E53BE5C83B}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{A185999A-270B-4694-AFE6-FFEAEA09C8AE}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{37F028C2-B48C-4219-A4F7-D948EF096C7C}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{AEB16D3A-569E-4AF3-9744-B6BDF3F6C66B}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{E153B778-861C-4233-B742-BF0D23812A49}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{08A56267-6F88-41E3-AD33-8FA1988EB652}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{A3C66853-B443-4573-BBEE-F7A9FC0E3E4C}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{D355CCD4-D3EF-43FD-BE5D-DF786CA363D3}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{009BFF2E-832A-4091-BF95-48C541BE711A}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{B404C202-07C7-46F5-AD38-81D3A575B227}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{1412230B-6013-4405-9D17-DD6F9D425DDE}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{63659DBB-91CB-412B-894A-FC2AE91719F1}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{6D08ACB8-034F-4FAF-8EA8-93737A6A02C3}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{E6D09014-BBDB-416F-889A-754FA998FB62}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{88DF3E2B-B34F-4476-A5E9-D16ECC7F84E9}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{500F88FC-B4BC-4878-B03E-DE1A73D7FF72}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{74FF0473-3D00-49B2-A813-A4459395E42A}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{37D03C8B-1001-4ECC-A5FF-ABBBE87AB1CC}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{D7E41FA7-DEAB-4D3B-9045-C60E0E6B4398}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{5F3835A8-DADF-4553-B455-8C1ADC4701F8}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{A30B44A4-BB86-4972-A7D1-BFB8E7726A13}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{A4D3B59A-9E32-4225-AF0E-3571B15C06A8}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{8E4AA709-4702-4DEC-B160-A100F7537877}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{73DC6F62-DDD3-45DA-87E9-6B0E3E1858CD}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{C09A8B7A-2BD8-4209-9CED-F238F24B4650}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{09FE1492-F3B9-45C2-9EBE-9E137A5D007B}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{02BE52A7-4984-46A8-97D6-4CD9E31D5F2F}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{C2297B2E-1711-4B89-95E8-23CAFA4E7B2D}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{B0B38DF1-E229-4B1C-8848-732B112ADD01}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{CB2EEFD0-C76D-484D-9286-710A2E399CDD}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{6DF33D9D-CCA2-444B-B2FB-13F607A3CB1E}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{D2162218-B785-4B7D-937A-CB8CAFECDF60}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{02C8552F-C08F-4DB4-B68E-279598EB11D5}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{E007F30F-7CDF-4A4B-8D5E-345C89313D4F}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{9C987BEA-8326-458B-ADB6-405FAEAFF82B}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{0C649EEF-8B96-4DF3-95B9-C0378855FCF7}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{D1035CF2-931E-49D3-B66E-9D0607DCD9CF}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{F0EE632C-748E-4206-BEBB-84D399A85E3A}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{23E32943-F8B3-40E9-A94D-0FB3D2226574}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{FD18E3C4-DF03-484D-95DC-281739FF11AF}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{E76E066A-724C-4BBF-ADFD-42401AAD37D4}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{6F99A369-B7C9-4A91-80D6-C5BE05C155CD}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{80662600-D5DC-42DB-8748-B1C3B00DB090}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{461DA23C-397E-4079-B103-AAE7EDCC5527}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{6DA3345C-A54D-4C2B-96D2-EB88CDF59D72}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{45D79305-E487-4174-8A97-E39A1D3BE405}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{57992DA1-1929-4316-806A-366999CA4630}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{0FC07824-DE31-4D80-B5FD-3041D39EAC65}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{0538E868-E8C4-459A-9798-DF8FDD2DAFF5}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{3A13F6B6-50D4-41B9-8A37-6AAE2E9C9DC7}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{BDFD3D68-738A-4D64-9A81-57CF83F20D2E}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{71799FE5-0005-4714-B1EB-A7D6A64B8F84}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{E2A940EA-C426-4225-9E36-686A3C0C3BAE}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{A22EE25C-3127-41EF-8671-1E4638355C62}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{37F0E4FF-CE66-445F-98F3-82C8774CFF24}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{B94023F8-BB9C-478B-A635-16BFDDA3CAFA}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{FDCAB3E4-723D-4052-8521-AB455D832395}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{CADA814C-CDF4-40F5-8649-D69C6418FFE5}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{45CD97DC-6DBA-41A8-8B61-DABB0026CAB1}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{2E84B6F4-E690-4212-97AD-DE21A0775A35}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{AC12EF29-419D-4967-8AED-A354AE40FD29}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{5F0B022C-D004-4B87-BBBE-69B306815BB8}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{C46047FE-6FDF-4B10-ACC3-372FA701AF54}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{A9F0359E-3499-48AD-8789-F13DD00A89CD}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{D7887AB6-BEA0-46BC-9102-A373322D22E0}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{86E5ED47-C2F4-4974-AC2F-D0FF6627388F}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{CE4196D1-1D2B-4F08-80FB-007F341EE5F2}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{00CD2DAD-9356-4951-BC63-2FC1CD5142F1}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{08712822-BAA8-4C4B-A948-2B4135A2C032}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{1136D05A-81C8-46B7-917C-5ED64D03C793}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{8BDCFAC1-20BA-4442-82D7-6D0B1ED48964}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{35E1440C-A50C-4ACD-922A-A128798DD163}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{20E29210-A5A7-4843-8F50-36EC4B567708}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{F6091A51-38F1-4A6F-A95F-74009DFFBE49}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{82969E35-A7EB-4C15-B16D-32E19F2C03D4}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{4F7D3449-5381-41DF-9C2E-272D5F538086}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{C285FED6-5072-488D-8565-3C1895AD28CD}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{C736F243-E004-4F67-AE9A-FA9608FEE956}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{A99BCC34-FB6E-4C05-98E4-AC608DE9510A}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{426D3C2B-BDE3-49C7-BE83-58CB7E32D012}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{BEB19659-A74B-4AEE-87A5-6400A6EA34BD}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{A765D3B4-F9C9-4C9A-96A2-3C79AA3F93CE}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{FF17516F-1EB5-46C1-A7E9-E1603A42E464}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{C0F4A308-41B3-4341-8B32-D32B191D3187}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{87485E6F-E479-4D75-847F-4951E81343A8}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{7F29F0EC-BD91-4AC4-A853-027CF0CA16EC}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{B3AE5B2C-D7B2-43C4-B51F-A7E727220A31}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{474A85BB-4AFA-44D4-9344-CDF4CE3C806E}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{2FCE10DE-28E5-408B-88E2-C4363D7FE955}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{14B85F4C-FD65-44DF-885B-B050AA596172}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{6F603F8C-9295-4912-9AFA-EB2171449080}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{B769F7D4-F1F8-474A-A879-62983BCCD473}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{326AA313-DEB5-4879-9D8B-2EAD53DB0625}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{6E099570-738E-4DEE-8A71-28245294F6A2}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{FB406639-6F37-4639-8C51-AF24ED309D80}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{C37F461A-5AA7-4974-AF88-B2E6D2A2DD9E}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{CDF5A20F-548F-407B-B555-432435D99241}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{34324260-A7AE-455E-8D42-71EB83DA194A}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{9922CC91-0074-4F6C-8AB8-D1123CDD83A8}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{EB38EDA6-BF0E-4BD3-8413-C434011D9346}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{FC061DAA-98A4-40D4-9546-07F1A7316551}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{2533BD1F-5264-49AF-90E1-AA65B66C207F}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{345A57B6-2E27-4D8C-89D1-8996D04F7924}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{97E679C8-B082-4A39-A222-7B32F94F1DB9}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{DD25C007-0691-45F8-9D6F-C0DB62E48587}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{11745C11-95C1-4C84-86BD-4B9C5CD95AC3}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{436D3427-E585-4D62-9EF6-BEEA5D7E2B80}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{9BEEB1E9-2A81-4E18-80F9-614B6AB0114E}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{0D231033-D7B0-4A1C-BE5B-BC5C2E2054F4}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{25F7B397-1044-49BC-A522-F7CBB2EF8ED0}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{29BA59B5-BC24-4AA8-B819-587F5A04A33F}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{E13C20B1-668F-4BAC-B2B7-F66C61A3CEC4}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{FB3404BC-D478-44E3-962D-C5F2EF824156}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{9681854A-BD6F-4CD0-9CC8-F613BBFA0233}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{F45B0C37-4BA8-43F1-AF6C-038E76B21E3E}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{A27D9F4F-65D3-4601-B41A-1EA6118B943C}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{F3D8C36D-6805-4F1F-96CA-1558FCD563CB}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{51B3CFF6-D36D-4656-8473-E07FC963557B}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{711C7C91-AC17-4B84-ADE8-4BFF06E7F273}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{A0B053A1-32EC-411F-99D7-007D2C174647}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{36A43D0E-4313-445F-B80F-A47E2FAA2E3A}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{E30873AC-49E1-4967-BF4C-EB49E08051EC}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{0A103F9E-1907-407A-B0C3-DF7A5855B296}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{4AF27E35-ECBD-4993-A7A0-EA0645E52ACE}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{9A4BCA23-7D8E-4858-9A61-339CF3E5B26F}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{0A900B24-C198-40AA-B997-AB9856D5F7ED}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{E8E0BC24-4202-4E2F-ABF8-322C71D9FD1D}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{BC923A68-4DB7-441B-8A3F-6516855DB0FC}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{3AB3B249-6BBA-4B7B-833D-32DD77D2EE46}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{ABA44021-53F8-46A9-9DC1-B7D685C8F41C}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{2A0E1DFC-E482-42D6-95B0-AA28B58ECDCC}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{C729010F-E93E-4CA9-96BF-4382C3A3B421}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{97288453-FA11-49CB-966A-7F81BF671AA2}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{49A764EF-FA30-4DF2-80F6-23B1B29EE045}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{448287F5-5F69-4179-8BF4-8C1F8B238599}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{EE0AD88C-F76F-4D06-B375-23851411C3EF}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{7D41A8A4-F3A2-471A-B08F-61C63A39498E}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{0FD5F4B6-E358-450C-8A46-3BBC2EAB6752}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{5459AA78-A659-46DC-B8EB-9F43D6E60C3B}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{4EF77410-A624-404F-A8A1-BB034BEDF706}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{870D149A-F6E4-4E28-A9AC-BFA755403781}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{159638D6-8FCF-4CF3-A609-428F625A6FCF}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{AA1AAFFF-6EF7-46FA-8FFC-926833B9399C}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{7A0293A3-AC81-4D37-8161-2C138924891D}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{580ECB31-4014-48E4-8DEA-0577DCC21B45}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{E64A7AA5-2961-414A-BCA9-27E7B9196CBF}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{31B9B76E-097F-49E7-8EDB-B98716BA1C8B}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{20AA1317-E851-44B1-AD63-CB138B7555D2}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{AC4495A2-D24B-4AE1-81D0-3C7C76F1CE9F}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{DB87A161-C749-46AC-9D1E-ADCDAFB44497}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{989014DE-9BF1-4E40-B353-864011148892}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId86"/>
+    <tablePart r:id="rId90"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C18F64-19A4-4E76-A1F2-C22763B2F0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2278273C-015F-4A41-9FE1-B99DBE275B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="270">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1019,6 +1019,30 @@
   </si>
   <si>
     <t xml:space="preserve">No retira pestaña en roseta, no gestiona repetidor de señal para aumentar producción </t>
+  </si>
+  <si>
+    <t>1-3NHP2Q99</t>
+  </si>
+  <si>
+    <t>Alberdi 01549</t>
+  </si>
+  <si>
+    <t>Nicolas Nilo Jara</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Srw9ivWGChc4dxUZ3qKDvzJAoXfnwUL0</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1lggRjpO-1vj3C15DfSKMfH4QeuUpD_tr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Mevy94ij7-lC7sh8oT3i78qZD05q6nQB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1jHJg4Ti1HFMCdoVtovSQT6DcEg0-a5gp</t>
+  </si>
+  <si>
+    <t>Realiza instalación bajo los protocolos, uso de herramientas ambos one click correcto, retiro de pestaña en roseta okey</t>
   </si>
 </sst>
 </file>
@@ -1884,8 +1908,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ27" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ27" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ28" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ28" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
@@ -2131,7 +2155,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -4650,102 +4674,202 @@
         <v/>
       </c>
     </row>
+    <row r="28" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46261.683956793982</v>
+      </c>
+      <c r="B28" s="12">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="T28" s="3">
+        <v>4</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="V28" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="W28" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="X28" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>10</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH28" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{C46047FE-6FDF-4B10-ACC3-372FA701AF54}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{A9F0359E-3499-48AD-8789-F13DD00A89CD}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{D7887AB6-BEA0-46BC-9102-A373322D22E0}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{86E5ED47-C2F4-4974-AC2F-D0FF6627388F}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{CE4196D1-1D2B-4F08-80FB-007F341EE5F2}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{00CD2DAD-9356-4951-BC63-2FC1CD5142F1}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{08712822-BAA8-4C4B-A948-2B4135A2C032}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{1136D05A-81C8-46B7-917C-5ED64D03C793}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{8BDCFAC1-20BA-4442-82D7-6D0B1ED48964}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{35E1440C-A50C-4ACD-922A-A128798DD163}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{20E29210-A5A7-4843-8F50-36EC4B567708}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{F6091A51-38F1-4A6F-A95F-74009DFFBE49}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{82969E35-A7EB-4C15-B16D-32E19F2C03D4}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{4F7D3449-5381-41DF-9C2E-272D5F538086}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{C285FED6-5072-488D-8565-3C1895AD28CD}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{C736F243-E004-4F67-AE9A-FA9608FEE956}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{A99BCC34-FB6E-4C05-98E4-AC608DE9510A}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{426D3C2B-BDE3-49C7-BE83-58CB7E32D012}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{BEB19659-A74B-4AEE-87A5-6400A6EA34BD}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{A765D3B4-F9C9-4C9A-96A2-3C79AA3F93CE}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{FF17516F-1EB5-46C1-A7E9-E1603A42E464}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{C0F4A308-41B3-4341-8B32-D32B191D3187}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{87485E6F-E479-4D75-847F-4951E81343A8}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{7F29F0EC-BD91-4AC4-A853-027CF0CA16EC}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{B3AE5B2C-D7B2-43C4-B51F-A7E727220A31}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{474A85BB-4AFA-44D4-9344-CDF4CE3C806E}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{2FCE10DE-28E5-408B-88E2-C4363D7FE955}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{14B85F4C-FD65-44DF-885B-B050AA596172}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{6F603F8C-9295-4912-9AFA-EB2171449080}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{B769F7D4-F1F8-474A-A879-62983BCCD473}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{326AA313-DEB5-4879-9D8B-2EAD53DB0625}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{6E099570-738E-4DEE-8A71-28245294F6A2}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{FB406639-6F37-4639-8C51-AF24ED309D80}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{C37F461A-5AA7-4974-AF88-B2E6D2A2DD9E}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{CDF5A20F-548F-407B-B555-432435D99241}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{34324260-A7AE-455E-8D42-71EB83DA194A}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{9922CC91-0074-4F6C-8AB8-D1123CDD83A8}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{EB38EDA6-BF0E-4BD3-8413-C434011D9346}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{FC061DAA-98A4-40D4-9546-07F1A7316551}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{2533BD1F-5264-49AF-90E1-AA65B66C207F}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{345A57B6-2E27-4D8C-89D1-8996D04F7924}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{97E679C8-B082-4A39-A222-7B32F94F1DB9}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{DD25C007-0691-45F8-9D6F-C0DB62E48587}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{11745C11-95C1-4C84-86BD-4B9C5CD95AC3}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{436D3427-E585-4D62-9EF6-BEEA5D7E2B80}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{9BEEB1E9-2A81-4E18-80F9-614B6AB0114E}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{0D231033-D7B0-4A1C-BE5B-BC5C2E2054F4}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{25F7B397-1044-49BC-A522-F7CBB2EF8ED0}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{29BA59B5-BC24-4AA8-B819-587F5A04A33F}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{E13C20B1-668F-4BAC-B2B7-F66C61A3CEC4}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{FB3404BC-D478-44E3-962D-C5F2EF824156}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{9681854A-BD6F-4CD0-9CC8-F613BBFA0233}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{F45B0C37-4BA8-43F1-AF6C-038E76B21E3E}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{A27D9F4F-65D3-4601-B41A-1EA6118B943C}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{F3D8C36D-6805-4F1F-96CA-1558FCD563CB}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{51B3CFF6-D36D-4656-8473-E07FC963557B}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{711C7C91-AC17-4B84-ADE8-4BFF06E7F273}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{A0B053A1-32EC-411F-99D7-007D2C174647}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{36A43D0E-4313-445F-B80F-A47E2FAA2E3A}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{E30873AC-49E1-4967-BF4C-EB49E08051EC}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{0A103F9E-1907-407A-B0C3-DF7A5855B296}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{4AF27E35-ECBD-4993-A7A0-EA0645E52ACE}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{9A4BCA23-7D8E-4858-9A61-339CF3E5B26F}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{0A900B24-C198-40AA-B997-AB9856D5F7ED}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{E8E0BC24-4202-4E2F-ABF8-322C71D9FD1D}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{BC923A68-4DB7-441B-8A3F-6516855DB0FC}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{3AB3B249-6BBA-4B7B-833D-32DD77D2EE46}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{ABA44021-53F8-46A9-9DC1-B7D685C8F41C}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{2A0E1DFC-E482-42D6-95B0-AA28B58ECDCC}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{C729010F-E93E-4CA9-96BF-4382C3A3B421}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{97288453-FA11-49CB-966A-7F81BF671AA2}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{49A764EF-FA30-4DF2-80F6-23B1B29EE045}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{448287F5-5F69-4179-8BF4-8C1F8B238599}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{EE0AD88C-F76F-4D06-B375-23851411C3EF}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{7D41A8A4-F3A2-471A-B08F-61C63A39498E}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{0FD5F4B6-E358-450C-8A46-3BBC2EAB6752}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{5459AA78-A659-46DC-B8EB-9F43D6E60C3B}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{4EF77410-A624-404F-A8A1-BB034BEDF706}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{870D149A-F6E4-4E28-A9AC-BFA755403781}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{159638D6-8FCF-4CF3-A609-428F625A6FCF}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{AA1AAFFF-6EF7-46FA-8FFC-926833B9399C}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{7A0293A3-AC81-4D37-8161-2C138924891D}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{580ECB31-4014-48E4-8DEA-0577DCC21B45}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{E64A7AA5-2961-414A-BCA9-27E7B9196CBF}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{31B9B76E-097F-49E7-8EDB-B98716BA1C8B}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{20AA1317-E851-44B1-AD63-CB138B7555D2}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{AC4495A2-D24B-4AE1-81D0-3C7C76F1CE9F}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{DB87A161-C749-46AC-9D1E-ADCDAFB44497}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{989014DE-9BF1-4E40-B353-864011148892}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{8C64343C-526A-4B28-8576-E19E52B31658}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{9D653BA2-6F4A-4083-82FE-C7CE6C8427D0}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{8B2A39E4-BBC6-4526-B4C6-D84BA79D8123}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{4F4C22C6-238B-43C7-8657-F9AC85EA1DC3}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{09685320-B764-47A6-AA9A-6F7527FD6DA0}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{0BA08CE9-3749-48A8-A945-52281F4BE0F8}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{CD06B811-85FE-4802-97B8-76E8B8F961D3}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{2CDF3D2E-571D-4583-ACEB-F2AEB7F8BF3C}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{B5FE6F85-91AC-469F-BC6D-BB2713B2ABF3}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{72376204-8DA1-4612-A7C0-FC4A43E7E296}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{201FD048-2E62-4B01-BEAA-E7CD61FF88AA}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{4770188E-DEC4-4F8F-B9D6-FBA186156C82}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{3B5096CD-2A5A-46EB-B6E7-4591FB11B2F5}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{016F05EB-22E0-432E-8D45-DE074ED2643B}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{5003DA59-0CFC-4376-A633-8EEBFD160F28}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{0AC0789F-4D6B-457B-B1E7-23C0D58B412C}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{17DE89CB-51DA-4BEA-B5A0-03E525DAB18D}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{B2974A77-9DEB-4FB4-9255-AC6B02CB075B}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{55CAEB42-B519-41FD-8E03-26B54C127532}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{7318B7DB-F0C8-44FE-AF4B-EADD3AE654A5}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{6F82D06A-A23F-4556-87E5-445F82DC7DB0}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{CD018A83-D0E8-4AF6-8502-D892768E381D}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{9D3550E8-37AF-4BA4-92FA-85FCFA07E0F5}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{7372E730-DF81-4FDE-8B97-96C9FEE057D5}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{6B3B6F37-513F-4166-BDFC-ECB90F056EFF}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{B5D186C8-C32F-4B20-833C-5462706BA857}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{5F245F2C-E07C-4279-ABBE-9510854143A5}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{B84E79AE-B485-4619-B582-7DFDE18FFF9B}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{4DF5AA40-E5C6-4DCB-A642-85D8AD75E374}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{664D6622-56DF-4DA9-90ED-820FFA5A72F4}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{E4E659FD-DDB9-419F-92F3-8AA65F75BE1B}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{4067407B-79CE-4012-82C1-E81C2456DCED}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{B5262957-3D50-4EFA-B943-4B1918E2A203}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{EE5ED25B-DC15-43CB-A9A2-A89EA2B31804}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{05E6AF46-0BA9-42F4-8406-A45F711EAF51}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{BB62BC1F-3FFB-4722-BC39-0F4B0A6417C7}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{6FE7EEB5-F58C-45A1-9674-849E92C74DAF}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{7BD32E1A-C89E-4A7F-83B7-8DFDC6428E09}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{96E60C50-FC4B-48BA-9622-CE58440A9E7F}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{DD2006DB-5219-47F1-8616-B56BC30403BE}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{7076C65A-3953-4A04-82F7-456FA112AF31}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{AA9CC80A-3144-4E5A-9459-B39CF1EEAB23}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{7ECD10B9-8CC8-4205-AD76-89444A54AFA2}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{3A0DD20B-169A-4DC4-AA2E-5E92E6A2BE57}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{6312D9B0-2F6C-4658-9934-CF77100B3D10}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{FA99CB51-8827-42E3-BB59-AC9C0FA379B6}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{1444A9BF-B425-4B8F-94E7-B101AC9F8315}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{6139E2C1-FEDC-41BE-8FD9-B1B646B7237F}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{DD2E3866-AFD2-4C13-A50A-EF76CB6AC67D}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{161CFA81-9EFB-4502-B11C-DF233237B39A}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{160D2BC2-70C9-4409-86CE-53288F10E9C8}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{12F1043F-22F2-43CD-B193-17DB8C5D8322}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{CE01F050-B4DF-4452-9AA8-BFDB93AEF51A}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{A18169B3-5CD5-4B48-9E54-055567A1B322}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{54457CC4-387F-4FF0-9DBF-B3F425266519}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{DC91F789-1F7F-4144-838A-E1742BED271C}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{54AA98A0-CFF0-42B7-893E-D4C73DD5D80F}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{B1E865F5-13CD-4F9E-96D3-5E5905587858}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{AF25B50D-EE83-4B0A-BAA8-AC47779F75D9}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{F238C294-C13D-47C7-85D4-F8FE92E8291B}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{E8F47B23-0D4F-470F-96FF-4F768A4064B6}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{5B4E2EDE-D2B4-4CB0-A6B5-BAF8287676AB}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{E693DA2C-CC09-478E-8B13-42C11579299B}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{07163E49-7BBB-4542-A36E-66D18BDD5D23}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{D52EED16-54EF-4534-B9FF-6C4289308497}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{6DB32419-2C70-479C-BAB0-F6A962B2DEAA}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{0B158078-9C65-4FE7-BA1D-6D0D71BB7F4F}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{1377CC36-E4E0-4B23-BD4F-3ED9C1325740}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{86317182-A8E8-4B1A-8FA8-07F93F5BB629}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{E1B4E999-2DA5-4C3E-A573-A2609854154B}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{C348449F-1318-4DC5-BCFB-8FDCF766E5C3}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{FDE79ABD-F4C7-45FA-8948-8FDD482AEB18}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{18A97926-8B71-4B6C-943A-79CA418F4AAA}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{8D24532B-A17A-4CF8-AF6D-5F6E303626CF}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{3D9F784F-8E75-4A41-9177-789EC3A2419C}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{7B1F70A0-5E21-456E-9103-9352FB96BCF5}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{45CF8DB1-6158-48BF-8D83-8DF8DCB93B68}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{3D58CA53-E8F5-4AA2-9D10-ECD436CDE9C5}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{63EDAC7D-FF07-4CC0-9EF6-63D207482A1F}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{2CA8E5E1-8CF0-4E21-BEDF-A090EFE04CDA}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{435B8CEE-A262-4EB1-BE17-70AB20DC7E98}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{226F5BC3-433A-4681-AAD6-6C4654365FD8}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{46866D73-08F8-4553-8294-C6B4BEA99F6A}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{14195F61-AFA9-4AA0-9A5B-DA0D420888F6}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{4F777BDC-5D92-41BA-8591-90C57D6C0190}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{1D3281D3-4166-47E4-BC75-14B9C89CBBD4}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{606ADD54-D7C3-437E-B595-C9EDE7257A88}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{6E7154D6-744F-4CAD-91D2-C15725CD85BA}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{6DF965B6-03BB-4CB6-91D8-140EB0B11E39}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{B58DC89A-5323-42A5-B2B8-7420C7433323}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{C0D48A60-2C0D-409E-9F7F-C213B85E9EF1}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{F62F96C9-9E0E-42ED-8775-D48CCE86EC63}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{4DF60DB6-E54E-4C9D-AB7D-1581DA2ACC6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId90"/>
+    <tablePart r:id="rId94"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2278273C-015F-4A41-9FE1-B99DBE275B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D17CC9-9EC7-466B-A468-887C0991D667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="286">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1043,6 +1043,54 @@
   </si>
   <si>
     <t>Realiza instalación bajo los protocolos, uso de herramientas ambos one click correcto, retiro de pestaña en roseta okey</t>
+  </si>
+  <si>
+    <t>1-3NJBWJB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Prieto 1305, edif B dpto 1601, Independencia </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1x9PfM7oe68fI1GDoXZmw6oPmH0KIs1iA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1GuCx2Pc9bbIwqE8A8sCI7z2S0TmXENSx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1IeLpHza4qeddPc7YQ_ReX0Lwwm3ry54W</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1JvAgn13_aoCqozmenMDl3quKGXMoExO_</t>
+  </si>
+  <si>
+    <t>No retira pestaña en roseta, no utiliza one click</t>
+  </si>
+  <si>
+    <t>1-3NL4LLZO</t>
+  </si>
+  <si>
+    <t>JONATHAN DIAZ CALDERON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lircay 0370, Recoleta </t>
+  </si>
+  <si>
+    <t>Camila Ordenes</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1tEudZOft8xZpMDsQSQPQeCTefP2_pegg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=10Xlmjj0mBNKoHxU001e7vmmevZMvK43s</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1p2tAKq4wDWPhOmNrxcjgQkRnRmLP6JL9</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=142ZUGj9G7YSmqQj_PBMrNlHaoMghoHPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No utiliza one click </t>
   </si>
 </sst>
 </file>
@@ -1908,8 +1956,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ28" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ28" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ30" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ30" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
@@ -2155,7 +2203,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ28"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -4770,106 +4818,303 @@
         <v/>
       </c>
     </row>
+    <row r="29" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46266.650122476851</v>
+      </c>
+      <c r="B29" s="12">
+        <v>8</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T29" s="3">
+        <v>4</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="X29" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH29" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46266.829720358801</v>
+      </c>
+      <c r="B30" s="12">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P30" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="T30" s="3">
+        <v>4</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="V30" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="W30" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH30" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{8C64343C-526A-4B28-8576-E19E52B31658}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{9D653BA2-6F4A-4083-82FE-C7CE6C8427D0}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{8B2A39E4-BBC6-4526-B4C6-D84BA79D8123}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{4F4C22C6-238B-43C7-8657-F9AC85EA1DC3}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{09685320-B764-47A6-AA9A-6F7527FD6DA0}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{0BA08CE9-3749-48A8-A945-52281F4BE0F8}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{CD06B811-85FE-4802-97B8-76E8B8F961D3}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{2CDF3D2E-571D-4583-ACEB-F2AEB7F8BF3C}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{B5FE6F85-91AC-469F-BC6D-BB2713B2ABF3}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{72376204-8DA1-4612-A7C0-FC4A43E7E296}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{201FD048-2E62-4B01-BEAA-E7CD61FF88AA}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{4770188E-DEC4-4F8F-B9D6-FBA186156C82}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{3B5096CD-2A5A-46EB-B6E7-4591FB11B2F5}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{016F05EB-22E0-432E-8D45-DE074ED2643B}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{5003DA59-0CFC-4376-A633-8EEBFD160F28}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{0AC0789F-4D6B-457B-B1E7-23C0D58B412C}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{17DE89CB-51DA-4BEA-B5A0-03E525DAB18D}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{B2974A77-9DEB-4FB4-9255-AC6B02CB075B}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{55CAEB42-B519-41FD-8E03-26B54C127532}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{7318B7DB-F0C8-44FE-AF4B-EADD3AE654A5}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{6F82D06A-A23F-4556-87E5-445F82DC7DB0}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{CD018A83-D0E8-4AF6-8502-D892768E381D}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{9D3550E8-37AF-4BA4-92FA-85FCFA07E0F5}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{7372E730-DF81-4FDE-8B97-96C9FEE057D5}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{6B3B6F37-513F-4166-BDFC-ECB90F056EFF}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{B5D186C8-C32F-4B20-833C-5462706BA857}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{5F245F2C-E07C-4279-ABBE-9510854143A5}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{B84E79AE-B485-4619-B582-7DFDE18FFF9B}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{4DF5AA40-E5C6-4DCB-A642-85D8AD75E374}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{664D6622-56DF-4DA9-90ED-820FFA5A72F4}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{E4E659FD-DDB9-419F-92F3-8AA65F75BE1B}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{4067407B-79CE-4012-82C1-E81C2456DCED}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{B5262957-3D50-4EFA-B943-4B1918E2A203}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{EE5ED25B-DC15-43CB-A9A2-A89EA2B31804}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{05E6AF46-0BA9-42F4-8406-A45F711EAF51}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{BB62BC1F-3FFB-4722-BC39-0F4B0A6417C7}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{6FE7EEB5-F58C-45A1-9674-849E92C74DAF}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{7BD32E1A-C89E-4A7F-83B7-8DFDC6428E09}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{96E60C50-FC4B-48BA-9622-CE58440A9E7F}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{DD2006DB-5219-47F1-8616-B56BC30403BE}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{7076C65A-3953-4A04-82F7-456FA112AF31}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{AA9CC80A-3144-4E5A-9459-B39CF1EEAB23}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{7ECD10B9-8CC8-4205-AD76-89444A54AFA2}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{3A0DD20B-169A-4DC4-AA2E-5E92E6A2BE57}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{6312D9B0-2F6C-4658-9934-CF77100B3D10}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{FA99CB51-8827-42E3-BB59-AC9C0FA379B6}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{1444A9BF-B425-4B8F-94E7-B101AC9F8315}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{6139E2C1-FEDC-41BE-8FD9-B1B646B7237F}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{DD2E3866-AFD2-4C13-A50A-EF76CB6AC67D}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{161CFA81-9EFB-4502-B11C-DF233237B39A}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{160D2BC2-70C9-4409-86CE-53288F10E9C8}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{12F1043F-22F2-43CD-B193-17DB8C5D8322}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{CE01F050-B4DF-4452-9AA8-BFDB93AEF51A}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{A18169B3-5CD5-4B48-9E54-055567A1B322}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{54457CC4-387F-4FF0-9DBF-B3F425266519}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{DC91F789-1F7F-4144-838A-E1742BED271C}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{54AA98A0-CFF0-42B7-893E-D4C73DD5D80F}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{B1E865F5-13CD-4F9E-96D3-5E5905587858}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{AF25B50D-EE83-4B0A-BAA8-AC47779F75D9}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{F238C294-C13D-47C7-85D4-F8FE92E8291B}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{E8F47B23-0D4F-470F-96FF-4F768A4064B6}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{5B4E2EDE-D2B4-4CB0-A6B5-BAF8287676AB}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{E693DA2C-CC09-478E-8B13-42C11579299B}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{07163E49-7BBB-4542-A36E-66D18BDD5D23}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{D52EED16-54EF-4534-B9FF-6C4289308497}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{6DB32419-2C70-479C-BAB0-F6A962B2DEAA}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{0B158078-9C65-4FE7-BA1D-6D0D71BB7F4F}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{1377CC36-E4E0-4B23-BD4F-3ED9C1325740}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{86317182-A8E8-4B1A-8FA8-07F93F5BB629}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{E1B4E999-2DA5-4C3E-A573-A2609854154B}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{C348449F-1318-4DC5-BCFB-8FDCF766E5C3}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{FDE79ABD-F4C7-45FA-8948-8FDD482AEB18}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{18A97926-8B71-4B6C-943A-79CA418F4AAA}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{8D24532B-A17A-4CF8-AF6D-5F6E303626CF}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{3D9F784F-8E75-4A41-9177-789EC3A2419C}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{7B1F70A0-5E21-456E-9103-9352FB96BCF5}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{45CF8DB1-6158-48BF-8D83-8DF8DCB93B68}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{3D58CA53-E8F5-4AA2-9D10-ECD436CDE9C5}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{63EDAC7D-FF07-4CC0-9EF6-63D207482A1F}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{2CA8E5E1-8CF0-4E21-BEDF-A090EFE04CDA}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{435B8CEE-A262-4EB1-BE17-70AB20DC7E98}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{226F5BC3-433A-4681-AAD6-6C4654365FD8}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{46866D73-08F8-4553-8294-C6B4BEA99F6A}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{14195F61-AFA9-4AA0-9A5B-DA0D420888F6}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{4F777BDC-5D92-41BA-8591-90C57D6C0190}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{1D3281D3-4166-47E4-BC75-14B9C89CBBD4}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{606ADD54-D7C3-437E-B595-C9EDE7257A88}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{6E7154D6-744F-4CAD-91D2-C15725CD85BA}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{6DF965B6-03BB-4CB6-91D8-140EB0B11E39}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{B58DC89A-5323-42A5-B2B8-7420C7433323}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{C0D48A60-2C0D-409E-9F7F-C213B85E9EF1}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{F62F96C9-9E0E-42ED-8775-D48CCE86EC63}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{4DF60DB6-E54E-4C9D-AB7D-1581DA2ACC6E}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{C3398179-E14A-4E17-8FFC-6ACCCB689F4A}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{961F42DE-F743-449B-8C6B-1C6CFDD19AA0}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{72579DCA-D448-4C47-82C8-B0AB23878EDB}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{1E994168-23B1-47BF-901B-9814B4AD719B}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{478F8909-54F1-499F-A37A-BF8CD49C71AB}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{CE657149-97F9-4323-B42C-C349CEFA7C47}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{A6A80AC3-5B6D-40A1-953C-BFFDE6E7985F}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{81CA5791-62D6-4E69-81A5-2710ADEC198F}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{1D5E2E38-A5B1-447C-8623-E57C8B542DF6}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{037168E7-F52A-424E-A04D-F252BE8256D3}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{5E3BEDE7-9F5F-4DB4-B89A-6410DD67EF04}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{7D03715F-226C-4E76-9D5C-283AF0E2F51D}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{9AEEA453-1470-4118-B77E-B9CE53FE045B}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{7E2821B6-A246-432D-A40A-10768982F3E4}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{DFBADFA3-1669-44A1-BF7B-DE6B6BD1A8A7}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{78A67EB2-9FF3-4028-9B5E-31935BE7235A}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{87E755E5-6B9C-4F36-8F9A-A0DF2ECCC62A}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{27A1E740-F9CF-4B60-AA3A-21B5D7062D0F}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{AB5D6C31-BE66-40C4-A16A-9AAAA847D056}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{A443ABB8-0DDE-4FD1-A797-92C4731181C6}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{D4D2774D-BA05-4494-A0A7-8DF159B410F8}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{243D0618-8EAD-4ACE-BF7C-1F73F4FDBD06}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{685A66D7-CC70-4198-AAFE-430EF1F3BA8C}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{796F873A-E448-4202-ADC9-1471054CD784}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{03AFDC79-2443-4791-923E-8952821F2B27}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{9687B27D-002D-4318-A63F-8F4B230B20A7}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{EBB5C86E-9129-46D4-8052-52704670E9D7}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{57F1C619-ABD8-43D6-B716-30293B12662E}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{C9E9DD0E-71E4-4CCB-AA25-DFCA4FE14E77}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{7A914863-FFFD-4822-B9DB-DAB86BB43771}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{7A741E25-4BAD-46B2-8A6E-31C462A71131}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{5E71C113-F31E-486F-B5D0-CADDC6DF8C3E}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{54C66A14-2926-445C-A07E-953438C8DB9F}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{A389CEBB-E0BD-4D36-AD61-44A998A99E5A}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{1B1D8C55-5924-4E94-AB0C-8185620D9BA4}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{C2BCBB4D-A3DF-47B0-ABAE-4EFBB6F2B711}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{99E338BD-EE20-4F82-8505-8A3674C8C288}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{4698546F-829D-4B7E-B248-213A3EDE8952}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{283C70E2-C37B-4F8B-BEAA-6E3BA558FCF7}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{5AE9E2EF-ACF2-4641-909D-77BC5C443464}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{31202C86-48B8-4FFF-89DD-50BE95958F51}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{BDA44125-B306-4891-BBAD-3DF2F1474F8A}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{46CF5094-EB5C-451E-ACE6-7ECF4723B4BF}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{ED5FFBB0-0703-4B75-B7D0-0D242B864EAA}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{910C73BC-0D33-428D-97AB-5B4795833E34}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{A29ACFB2-57E3-4934-801A-4F9E9CC843E8}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{219B69E9-DD80-4CE1-94BF-52C1ACDB96FD}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{9AEEE8C8-6BA8-4632-8B97-31C6BEB80FE6}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{E5A3BDCA-3B26-4226-B302-F97A7E3E2B6C}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{FDF482E8-C02C-455F-B95F-75C20EF004CE}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{98672ABA-D23E-4CBA-87B1-CE7E4A47B6F2}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{351B8C9A-B163-4100-91FF-76EAB6E27B6E}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{8E6DABF2-32E1-4A20-B655-34BF4652A23F}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{31A1CD5B-A9BB-42D2-BC27-BADD4FB6FA7E}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{5FA6E86B-315F-4DDA-B864-B88195FA1B5A}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{3971F0D4-C448-49D5-BDA5-D101071BFA77}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{7D0F6B9D-1631-4ECC-81C1-F106540E6DD2}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{0161611D-EE20-4618-8F7E-484246B066FB}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{55ED5677-3FF0-421A-8DE3-0F0E51296861}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{DCE7EC62-0534-443D-9D76-6B368AA48C16}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{2286057C-536C-41DF-8F2F-09CA76203EC4}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{69500FDF-13C8-4959-B61D-51E33440F9C1}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{E30C8A6E-2FE9-40E2-8ABB-19146A4341F8}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{CA1FC0C1-0C3F-43AF-A808-600030068C07}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{6A78BAF1-32A0-49EA-9E93-35F322A97630}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{EBDABCBD-613B-4970-B85C-2530135AB303}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{D433FDC8-B9C4-4B8E-873C-E2D2E96A6EF3}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{4032CB8C-816E-4E06-A16E-570449C46336}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{AE3A4F22-1B62-4D49-BCEC-6112FFD25640}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{3CFF8757-12E7-4F0A-BD92-5310FB06A0A1}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{6E0EC77F-37F0-40B8-8FC6-53112A710D57}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{847032A7-B422-427B-A45E-CC8A8C94FBC3}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{12672C8C-B2C9-4D65-93EF-A32978D40AA2}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{0F06A070-1088-4468-A1B5-6DE8E01AB0AB}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{BDD2808D-AC23-435B-B5A7-69B27E354708}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{DE60EB59-A381-4AF2-A21C-D754F9F1D30A}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{956B585A-E091-4166-9F32-C25FC9A7B6C4}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{CE47AFD4-39C1-401D-9BF1-2447504248E3}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{44F8C7E1-4483-44A1-A5E1-4D766AAD094E}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{D1897B3A-5201-47A0-B6AC-C3E078E35D89}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{E41D15B9-6040-41F6-996B-2175EB4B224B}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{4607E52E-9617-497D-A864-13B8F956A560}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{96073EEC-49A6-44C9-AA5A-D064F753A4DF}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{94531339-04AE-4405-AEB2-E275E3AE5AD8}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{0CB12B7F-7EFC-4F40-98D1-DB901392EEBD}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{BBA69B48-C8D9-4CAA-AD9D-9C9AC4340C84}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{760BE3D4-6C6F-4826-BCA6-E27C8DFDA3A6}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{F821027A-7A00-4B47-BD6C-81F3DA529946}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{B04BD47D-408B-48AD-A35B-68DAC4B6249C}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{62EE5D98-AE25-4D8B-8D4C-7D366BA141F9}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{3CBDDB80-286F-48B9-9032-8A5154773770}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{2CECDE1C-B74F-4B50-9B81-B54B7F1020DC}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{64289C97-88DE-4507-95A6-B92F0B98DB62}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{D0520700-979D-4670-BB72-6084E037A7F2}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{8425E87A-8884-459D-960F-7FD82D0E837F}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{E0FDE2CD-6350-4C9A-8B85-76F0BBAAC5C0}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{33106826-ED39-4008-82F1-ADF0CA4A9BF5}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{769A8135-A6EA-4C77-99DD-416C3F62E60F}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{49E16167-F8DC-415E-962C-7EFDF6876C15}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{0A9AE504-7C47-454C-A240-073ABDDBFA5D}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{2E4272F7-3F8C-4B6B-B8FE-17031146415F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId94"/>
+    <tablePart r:id="rId102"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D17CC9-9EC7-466B-A468-887C0991D667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C68548-319A-4F22-AFF3-61310F99DEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="293">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1091,6 +1091,27 @@
   </si>
   <si>
     <t xml:space="preserve">No utiliza one click </t>
+  </si>
+  <si>
+    <t>1-3NLYBW1U</t>
+  </si>
+  <si>
+    <t>Membrillar 5728, Quinta Normal</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1r0QOTrD_EHj73uRDoPT5l74DoIWcc3wT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14MxsC3C0f207VMLAOa5bWYleWv216rnN</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1flZwOSfHLNBkFuA2mrKyCbnSD5a4EfU0</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Hg3v8SkyQN2WJQTNtfEU-LeIj27gEi1X</t>
+  </si>
+  <si>
+    <t>A petición de cliente se instala roseta fuera de norma</t>
   </si>
 </sst>
 </file>
@@ -1418,6 +1439,42 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <u/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
@@ -1478,42 +1535,6 @@
         <color rgb="FF0000FF"/>
         <name val="Roboto"/>
         <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1956,8 +1977,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ30" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ30" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ31" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ31" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
@@ -1973,24 +1994,24 @@
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="18"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="9"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="8"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="7"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="32"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="1"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="31"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
     <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
@@ -2203,7 +2224,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -5007,114 +5028,211 @@
         <v/>
       </c>
     </row>
+    <row r="31" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46267.696003368052</v>
+      </c>
+      <c r="B31" s="12">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T31" s="3">
+        <v>4</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="V31" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="W31" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="X31" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="Y31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="AC31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH31" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{C3398179-E14A-4E17-8FFC-6ACCCB689F4A}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{961F42DE-F743-449B-8C6B-1C6CFDD19AA0}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{72579DCA-D448-4C47-82C8-B0AB23878EDB}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{1E994168-23B1-47BF-901B-9814B4AD719B}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{478F8909-54F1-499F-A37A-BF8CD49C71AB}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{CE657149-97F9-4323-B42C-C349CEFA7C47}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{A6A80AC3-5B6D-40A1-953C-BFFDE6E7985F}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{81CA5791-62D6-4E69-81A5-2710ADEC198F}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{1D5E2E38-A5B1-447C-8623-E57C8B542DF6}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{037168E7-F52A-424E-A04D-F252BE8256D3}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{5E3BEDE7-9F5F-4DB4-B89A-6410DD67EF04}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{7D03715F-226C-4E76-9D5C-283AF0E2F51D}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{9AEEA453-1470-4118-B77E-B9CE53FE045B}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{7E2821B6-A246-432D-A40A-10768982F3E4}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{DFBADFA3-1669-44A1-BF7B-DE6B6BD1A8A7}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{78A67EB2-9FF3-4028-9B5E-31935BE7235A}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{87E755E5-6B9C-4F36-8F9A-A0DF2ECCC62A}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{27A1E740-F9CF-4B60-AA3A-21B5D7062D0F}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{AB5D6C31-BE66-40C4-A16A-9AAAA847D056}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{A443ABB8-0DDE-4FD1-A797-92C4731181C6}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{D4D2774D-BA05-4494-A0A7-8DF159B410F8}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{243D0618-8EAD-4ACE-BF7C-1F73F4FDBD06}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{685A66D7-CC70-4198-AAFE-430EF1F3BA8C}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{796F873A-E448-4202-ADC9-1471054CD784}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{03AFDC79-2443-4791-923E-8952821F2B27}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{9687B27D-002D-4318-A63F-8F4B230B20A7}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{EBB5C86E-9129-46D4-8052-52704670E9D7}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{57F1C619-ABD8-43D6-B716-30293B12662E}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{C9E9DD0E-71E4-4CCB-AA25-DFCA4FE14E77}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{7A914863-FFFD-4822-B9DB-DAB86BB43771}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{7A741E25-4BAD-46B2-8A6E-31C462A71131}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{5E71C113-F31E-486F-B5D0-CADDC6DF8C3E}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{54C66A14-2926-445C-A07E-953438C8DB9F}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{A389CEBB-E0BD-4D36-AD61-44A998A99E5A}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{1B1D8C55-5924-4E94-AB0C-8185620D9BA4}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{C2BCBB4D-A3DF-47B0-ABAE-4EFBB6F2B711}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{99E338BD-EE20-4F82-8505-8A3674C8C288}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{4698546F-829D-4B7E-B248-213A3EDE8952}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{283C70E2-C37B-4F8B-BEAA-6E3BA558FCF7}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{5AE9E2EF-ACF2-4641-909D-77BC5C443464}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{31202C86-48B8-4FFF-89DD-50BE95958F51}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{BDA44125-B306-4891-BBAD-3DF2F1474F8A}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{46CF5094-EB5C-451E-ACE6-7ECF4723B4BF}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{ED5FFBB0-0703-4B75-B7D0-0D242B864EAA}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{910C73BC-0D33-428D-97AB-5B4795833E34}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{A29ACFB2-57E3-4934-801A-4F9E9CC843E8}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{219B69E9-DD80-4CE1-94BF-52C1ACDB96FD}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{9AEEE8C8-6BA8-4632-8B97-31C6BEB80FE6}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{E5A3BDCA-3B26-4226-B302-F97A7E3E2B6C}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{FDF482E8-C02C-455F-B95F-75C20EF004CE}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{98672ABA-D23E-4CBA-87B1-CE7E4A47B6F2}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{351B8C9A-B163-4100-91FF-76EAB6E27B6E}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{8E6DABF2-32E1-4A20-B655-34BF4652A23F}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{31A1CD5B-A9BB-42D2-BC27-BADD4FB6FA7E}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{5FA6E86B-315F-4DDA-B864-B88195FA1B5A}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{3971F0D4-C448-49D5-BDA5-D101071BFA77}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{7D0F6B9D-1631-4ECC-81C1-F106540E6DD2}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{0161611D-EE20-4618-8F7E-484246B066FB}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{55ED5677-3FF0-421A-8DE3-0F0E51296861}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{DCE7EC62-0534-443D-9D76-6B368AA48C16}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{2286057C-536C-41DF-8F2F-09CA76203EC4}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{69500FDF-13C8-4959-B61D-51E33440F9C1}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{E30C8A6E-2FE9-40E2-8ABB-19146A4341F8}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{CA1FC0C1-0C3F-43AF-A808-600030068C07}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{6A78BAF1-32A0-49EA-9E93-35F322A97630}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{EBDABCBD-613B-4970-B85C-2530135AB303}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{D433FDC8-B9C4-4B8E-873C-E2D2E96A6EF3}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{4032CB8C-816E-4E06-A16E-570449C46336}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{AE3A4F22-1B62-4D49-BCEC-6112FFD25640}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{3CFF8757-12E7-4F0A-BD92-5310FB06A0A1}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{6E0EC77F-37F0-40B8-8FC6-53112A710D57}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{847032A7-B422-427B-A45E-CC8A8C94FBC3}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{12672C8C-B2C9-4D65-93EF-A32978D40AA2}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{0F06A070-1088-4468-A1B5-6DE8E01AB0AB}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{BDD2808D-AC23-435B-B5A7-69B27E354708}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{DE60EB59-A381-4AF2-A21C-D754F9F1D30A}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{956B585A-E091-4166-9F32-C25FC9A7B6C4}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{CE47AFD4-39C1-401D-9BF1-2447504248E3}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{44F8C7E1-4483-44A1-A5E1-4D766AAD094E}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{D1897B3A-5201-47A0-B6AC-C3E078E35D89}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{E41D15B9-6040-41F6-996B-2175EB4B224B}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{4607E52E-9617-497D-A864-13B8F956A560}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{96073EEC-49A6-44C9-AA5A-D064F753A4DF}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{94531339-04AE-4405-AEB2-E275E3AE5AD8}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{0CB12B7F-7EFC-4F40-98D1-DB901392EEBD}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{BBA69B48-C8D9-4CAA-AD9D-9C9AC4340C84}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{760BE3D4-6C6F-4826-BCA6-E27C8DFDA3A6}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{F821027A-7A00-4B47-BD6C-81F3DA529946}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{B04BD47D-408B-48AD-A35B-68DAC4B6249C}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{62EE5D98-AE25-4D8B-8D4C-7D366BA141F9}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{3CBDDB80-286F-48B9-9032-8A5154773770}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{2CECDE1C-B74F-4B50-9B81-B54B7F1020DC}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{64289C97-88DE-4507-95A6-B92F0B98DB62}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{D0520700-979D-4670-BB72-6084E037A7F2}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{8425E87A-8884-459D-960F-7FD82D0E837F}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{E0FDE2CD-6350-4C9A-8B85-76F0BBAAC5C0}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{33106826-ED39-4008-82F1-ADF0CA4A9BF5}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{769A8135-A6EA-4C77-99DD-416C3F62E60F}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{49E16167-F8DC-415E-962C-7EFDF6876C15}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{0A9AE504-7C47-454C-A240-073ABDDBFA5D}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{2E4272F7-3F8C-4B6B-B8FE-17031146415F}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{691686FE-A6DC-4EA2-82A5-DA56CB735325}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{79028496-E1A0-4C7E-882A-71BF59D1EDD7}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{FCCC107B-E771-4090-96E1-5A21CEE14047}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{985E5354-8C37-4B19-AC67-25781D6303B9}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{4A05189B-821B-4691-8FA7-481B797998EF}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{A4DBFD02-2CA9-429F-A7B7-3F6D0CB5AB0C}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{685A1F0A-0782-4E1E-ADEE-952D1F5BE290}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{67BE10A8-C142-4F16-A928-32A84C95C0BA}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{C49B0A15-6386-4196-8CAE-3C7A86E4D11B}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{E232F70F-70D9-4ECA-AEF8-6A494641DAFC}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{5BBCB4B4-07EA-43BB-BCDD-C3FFA7EFEB04}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{5F32DECA-7E87-4A13-B591-46F6941644D6}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{8D23B866-D7C0-44CA-A36D-E0ABA35A77C0}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{78628546-2596-4665-B14A-E08DA412693B}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{11001CCB-DB5A-4620-91BC-F85341F23CB0}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{934AECD0-2782-4EF5-8667-E70C75844D45}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{AD51591B-020D-488D-82C7-471D4D6EB2C5}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{5A6A3C3F-FD21-471F-9AFF-0F131BDE3B44}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{ED7E7929-21AB-47CB-9C4E-393403B94D13}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{D8DFDA83-E807-4C22-8CDA-D9EDFDFD3FCC}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{872936F1-9EFE-4A27-B1E4-C7BE885047C6}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{77E374C6-FF0E-4814-AC7E-574828CBBF94}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{563E09BD-9FE9-45BD-A04C-7818BFDAE93B}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{CCE6CAE2-8EED-4F44-A824-BE2FF93A5091}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{BF9F4C1A-1D11-41E5-AEC7-AB941397FD33}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{35AC36E5-AA05-4EE8-B888-26ECEAF859BC}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{F0D9C2D5-4F96-4CB1-AB6D-F9803CFA73AC}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{6D06C61A-D9A8-48D8-933F-33CAED328B7B}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{0682EFA8-BBB5-40CC-AD64-5B66219C2C83}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{1232E332-536B-4A64-9D8D-0685E1E82996}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{E757DF98-F70C-4170-AC18-5904F70B52E9}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{CBB9E110-6805-4718-A8B2-ACAEEB187DD4}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{99F3C5A2-A086-4F00-B8D2-020961F4773C}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{14E319D2-A75B-4E42-8B61-F0EF83FBCBDE}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{5EA4101B-53D6-4F80-9D4B-A47B44BB7ED1}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{50B0B1E2-1DF3-4BFB-8704-F313506CC4B7}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{14F127C3-A9B9-4BD9-8FDB-242FC31F863C}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{2CC2AF95-C4DE-4912-BBE6-41A0CAF30667}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{DC5D97CE-CE6D-4FBD-8667-64FDBC6547CF}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{BD27A5BB-FD76-4289-812E-40A96BEF0A6A}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{1C865C04-2E77-4DCA-B621-8A54D539A4FA}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{F3921083-7D09-46F1-B32A-9050F0962688}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{D9955A22-4928-4222-ADAF-E5FFB3FB6268}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{D53385A7-6840-42F2-AAE3-E9CA7A8E2529}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{5AA419C6-0A07-497A-B89E-FAD678E11C67}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{32C2691E-CE67-44FA-BA46-D19C6A75CA0C}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{E97C843A-1EA2-4BE9-928F-94B1CF929EFC}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{97923530-8DBE-4F01-88C7-3688131981FD}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{5C845274-2CEC-4615-A93B-F511C03235FF}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{FEF8C77C-6EFF-4A8B-9A41-DAA5C232689E}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{4451231F-E4A2-4AF0-9793-59A66BADB8D9}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{B456A6FD-A31A-42AC-9A47-4C86EB7258A1}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{7E94CBB1-03CE-4865-A97A-CF8E67A8C545}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{D37ED088-E6A4-41F6-AFE2-A295D3E7A165}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{77F4589C-E902-4E4E-845F-B9B0E069F5AC}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{B9380AEE-DDF3-4CAF-8B07-51FDC3C59C71}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{5440AF96-99CF-42AB-8426-FCD542257444}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{133AEE6C-5681-4B51-A3A0-86F2DDD79A94}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{E0F2002C-9619-4ECE-9B46-2B16DF520334}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{D3B583FD-1196-479F-9E5E-8F7C09C6C39E}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{BB8073C6-F5EA-4FF1-AA17-7668D149A6AC}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{3F31BD51-A3F3-499F-AE0A-F38726B3B810}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{DA1BADF7-0263-418B-9439-CA342B90DE5B}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{8163501B-BE15-414A-83D3-E4FF3B326469}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{3A846CFA-CB02-4BA2-B5E9-C797DD4A738C}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{7AE70CBC-A99A-41C3-9E47-536BD3E0F922}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{CAECD4D3-AE5F-45BA-AB87-F42BA737D99C}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{D94FEEB0-E662-405C-BEB3-7319CEB6C0FA}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{C2F81650-8038-4D44-9E04-B81FC154CAFB}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{A51F4B25-8FF3-49DE-A3F3-06DCF34B1698}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{325318B0-2D72-4C16-BEA6-55AF468F652A}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{15FEC43B-B45F-4C90-8D3A-4905EC300DE5}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{246015E9-CDBB-4A06-B2FF-3A9BB6B1ACA7}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{123A99DD-E3B4-4F69-B1DA-EBE78B98DAB5}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{428269D0-3336-4B70-974B-05034F7022E0}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{E2316E22-CA8F-470E-850D-B87915471021}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{A96DA6C4-8781-45C2-AE78-A29A5B25190A}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{15D4975E-2876-4642-B652-E4915A3A5212}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{B7BEB65D-D62F-47F8-8621-8574E75535F1}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{0E1481E4-86F3-4147-9900-915314A33C2E}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{0F370CBD-AC51-4889-A4CC-1A7A7201A6ED}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{039AD173-5489-410F-B2E7-122D4C2AF252}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{37D46E71-6CB4-4CE5-8AA6-2152C9C6A3C1}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{7C6BA213-1441-47E2-81F2-384A935655E7}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{04972711-CED1-4D17-9038-7C749D18ED76}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{62451315-F16A-4AC7-A97F-DF5674278B9D}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{41797CE5-444E-4468-8124-904BAF42936A}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{5FEB18F1-2E6D-4E39-B832-7124B9634446}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{A684A6B9-407E-485E-9643-2997F08D86A9}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{5D789503-F0DF-4842-BADC-7B0AE781A810}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{E439D470-3850-46AA-BECB-82D715778286}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{D5B78641-A114-4FF8-857A-0C391D627012}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{3BF0C029-13F4-4E90-AAE3-BC76B5A0CB6D}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{552CE628-CDA2-4140-8A03-0A10BA7D2B5B}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{FDF2FBD0-19DC-41C4-8CAC-5538305DA291}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{1C7F8AB5-04CE-40AE-A01D-14CFD5805688}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{009C9530-890E-4AB2-BE25-753A30092512}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{FEAEA693-0A5F-4A90-828C-8958295A2602}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{45DF29D5-AD6F-4C6A-AF59-78499EB95528}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{C6A6C109-5769-4066-A3F0-A0CABE595E48}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{6EFB6386-9CB7-4852-B2FE-09DB2701EED3}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{7BF389E6-FDD8-407E-8F98-283FD15E8698}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{77D4284B-1D09-45B8-8ADD-4CAFE5CB3725}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{DDA7EA77-C40B-4FFF-BD48-203A3F3D3D88}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{D71494B6-F8F6-43A9-A224-808A81F61DA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId102"/>
+    <tablePart r:id="rId106"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C68548-319A-4F22-AFF3-61310F99DEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31D700D-CA3C-4BDB-B79E-82D53829294A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="301">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1112,6 +1112,30 @@
   </si>
   <si>
     <t>A petición de cliente se instala roseta fuera de norma</t>
+  </si>
+  <si>
+    <t>1-3NN9AV8Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo Urzua 1559, Independencia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilman Hernandez </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=12oZ5C6nPLv6t7TKKaCG0GUD4Ii-9w7z0</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1FMERhxTFgD1yrm9IjxJ7kFwgXiUbnAg_</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qQa-IfAV_dLOsGZNC17MNWWzKIc7SkUQ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1VBmcxDYN7guoxYGYj5s7TrynjAfkJBDw</t>
+  </si>
+  <si>
+    <t>A petición de cliente roseta se instala fuera de norma, si cumple con el corte en pestaña de roseta</t>
   </si>
 </sst>
 </file>
@@ -1977,8 +2001,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ31" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ31" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ32" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ32" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
@@ -2224,7 +2248,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -5121,118 +5145,212 @@
         <v/>
       </c>
     </row>
+    <row r="32" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46268.671411990741</v>
+      </c>
+      <c r="B32" s="12">
+        <v>6</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="T32" s="3">
+        <v>4</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="X32" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH32" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{691686FE-A6DC-4EA2-82A5-DA56CB735325}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{79028496-E1A0-4C7E-882A-71BF59D1EDD7}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{FCCC107B-E771-4090-96E1-5A21CEE14047}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{985E5354-8C37-4B19-AC67-25781D6303B9}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{4A05189B-821B-4691-8FA7-481B797998EF}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{A4DBFD02-2CA9-429F-A7B7-3F6D0CB5AB0C}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{685A1F0A-0782-4E1E-ADEE-952D1F5BE290}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{67BE10A8-C142-4F16-A928-32A84C95C0BA}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{C49B0A15-6386-4196-8CAE-3C7A86E4D11B}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{E232F70F-70D9-4ECA-AEF8-6A494641DAFC}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{5BBCB4B4-07EA-43BB-BCDD-C3FFA7EFEB04}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{5F32DECA-7E87-4A13-B591-46F6941644D6}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{8D23B866-D7C0-44CA-A36D-E0ABA35A77C0}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{78628546-2596-4665-B14A-E08DA412693B}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{11001CCB-DB5A-4620-91BC-F85341F23CB0}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{934AECD0-2782-4EF5-8667-E70C75844D45}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{AD51591B-020D-488D-82C7-471D4D6EB2C5}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{5A6A3C3F-FD21-471F-9AFF-0F131BDE3B44}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{ED7E7929-21AB-47CB-9C4E-393403B94D13}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{D8DFDA83-E807-4C22-8CDA-D9EDFDFD3FCC}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{872936F1-9EFE-4A27-B1E4-C7BE885047C6}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{77E374C6-FF0E-4814-AC7E-574828CBBF94}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{563E09BD-9FE9-45BD-A04C-7818BFDAE93B}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{CCE6CAE2-8EED-4F44-A824-BE2FF93A5091}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{BF9F4C1A-1D11-41E5-AEC7-AB941397FD33}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{35AC36E5-AA05-4EE8-B888-26ECEAF859BC}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{F0D9C2D5-4F96-4CB1-AB6D-F9803CFA73AC}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{6D06C61A-D9A8-48D8-933F-33CAED328B7B}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{0682EFA8-BBB5-40CC-AD64-5B66219C2C83}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{1232E332-536B-4A64-9D8D-0685E1E82996}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{E757DF98-F70C-4170-AC18-5904F70B52E9}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{CBB9E110-6805-4718-A8B2-ACAEEB187DD4}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{99F3C5A2-A086-4F00-B8D2-020961F4773C}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{14E319D2-A75B-4E42-8B61-F0EF83FBCBDE}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{5EA4101B-53D6-4F80-9D4B-A47B44BB7ED1}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{50B0B1E2-1DF3-4BFB-8704-F313506CC4B7}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{14F127C3-A9B9-4BD9-8FDB-242FC31F863C}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{2CC2AF95-C4DE-4912-BBE6-41A0CAF30667}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{DC5D97CE-CE6D-4FBD-8667-64FDBC6547CF}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{BD27A5BB-FD76-4289-812E-40A96BEF0A6A}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{1C865C04-2E77-4DCA-B621-8A54D539A4FA}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{F3921083-7D09-46F1-B32A-9050F0962688}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{D9955A22-4928-4222-ADAF-E5FFB3FB6268}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{D53385A7-6840-42F2-AAE3-E9CA7A8E2529}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{5AA419C6-0A07-497A-B89E-FAD678E11C67}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{32C2691E-CE67-44FA-BA46-D19C6A75CA0C}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{E97C843A-1EA2-4BE9-928F-94B1CF929EFC}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{97923530-8DBE-4F01-88C7-3688131981FD}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{5C845274-2CEC-4615-A93B-F511C03235FF}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{FEF8C77C-6EFF-4A8B-9A41-DAA5C232689E}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{4451231F-E4A2-4AF0-9793-59A66BADB8D9}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{B456A6FD-A31A-42AC-9A47-4C86EB7258A1}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{7E94CBB1-03CE-4865-A97A-CF8E67A8C545}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{D37ED088-E6A4-41F6-AFE2-A295D3E7A165}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{77F4589C-E902-4E4E-845F-B9B0E069F5AC}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{B9380AEE-DDF3-4CAF-8B07-51FDC3C59C71}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{5440AF96-99CF-42AB-8426-FCD542257444}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{133AEE6C-5681-4B51-A3A0-86F2DDD79A94}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{E0F2002C-9619-4ECE-9B46-2B16DF520334}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{D3B583FD-1196-479F-9E5E-8F7C09C6C39E}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{BB8073C6-F5EA-4FF1-AA17-7668D149A6AC}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{3F31BD51-A3F3-499F-AE0A-F38726B3B810}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{DA1BADF7-0263-418B-9439-CA342B90DE5B}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{8163501B-BE15-414A-83D3-E4FF3B326469}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{3A846CFA-CB02-4BA2-B5E9-C797DD4A738C}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{7AE70CBC-A99A-41C3-9E47-536BD3E0F922}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{CAECD4D3-AE5F-45BA-AB87-F42BA737D99C}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{D94FEEB0-E662-405C-BEB3-7319CEB6C0FA}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{C2F81650-8038-4D44-9E04-B81FC154CAFB}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{A51F4B25-8FF3-49DE-A3F3-06DCF34B1698}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{325318B0-2D72-4C16-BEA6-55AF468F652A}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{15FEC43B-B45F-4C90-8D3A-4905EC300DE5}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{246015E9-CDBB-4A06-B2FF-3A9BB6B1ACA7}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{123A99DD-E3B4-4F69-B1DA-EBE78B98DAB5}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{428269D0-3336-4B70-974B-05034F7022E0}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{E2316E22-CA8F-470E-850D-B87915471021}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{A96DA6C4-8781-45C2-AE78-A29A5B25190A}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{15D4975E-2876-4642-B652-E4915A3A5212}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{B7BEB65D-D62F-47F8-8621-8574E75535F1}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{0E1481E4-86F3-4147-9900-915314A33C2E}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{0F370CBD-AC51-4889-A4CC-1A7A7201A6ED}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{039AD173-5489-410F-B2E7-122D4C2AF252}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{37D46E71-6CB4-4CE5-8AA6-2152C9C6A3C1}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{7C6BA213-1441-47E2-81F2-384A935655E7}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{04972711-CED1-4D17-9038-7C749D18ED76}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{62451315-F16A-4AC7-A97F-DF5674278B9D}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{41797CE5-444E-4468-8124-904BAF42936A}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{5FEB18F1-2E6D-4E39-B832-7124B9634446}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{A684A6B9-407E-485E-9643-2997F08D86A9}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{5D789503-F0DF-4842-BADC-7B0AE781A810}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{E439D470-3850-46AA-BECB-82D715778286}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{D5B78641-A114-4FF8-857A-0C391D627012}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{3BF0C029-13F4-4E90-AAE3-BC76B5A0CB6D}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{552CE628-CDA2-4140-8A03-0A10BA7D2B5B}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{FDF2FBD0-19DC-41C4-8CAC-5538305DA291}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{1C7F8AB5-04CE-40AE-A01D-14CFD5805688}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{009C9530-890E-4AB2-BE25-753A30092512}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{FEAEA693-0A5F-4A90-828C-8958295A2602}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{45DF29D5-AD6F-4C6A-AF59-78499EB95528}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{C6A6C109-5769-4066-A3F0-A0CABE595E48}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{6EFB6386-9CB7-4852-B2FE-09DB2701EED3}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{7BF389E6-FDD8-407E-8F98-283FD15E8698}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{77D4284B-1D09-45B8-8ADD-4CAFE5CB3725}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{DDA7EA77-C40B-4FFF-BD48-203A3F3D3D88}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{D71494B6-F8F6-43A9-A224-808A81F61DA6}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{BAA3B567-023E-437B-8424-37C4D77E1579}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{8412DC1E-6721-4A41-BFE0-585CDF96F9F8}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{CC168C4E-7365-444C-8DDF-5ED046BDE7FD}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{70734598-5382-4BEE-BFD1-2943D5B22768}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{862677B7-3E9B-4652-ABDF-B43C377A9380}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{1468DD04-8972-4DCC-BEA5-9B0F692D612E}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{7465EADD-F15C-4920-BDD7-4B3B95659CC5}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{C0FD9221-7638-4472-82BA-6EDF120A327D}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{3EBD63ED-1361-4BA1-B895-86352553A17E}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{D3FE2140-E49E-423F-BDC7-78DD3470F627}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{3CC0E442-FE79-4A3B-BF4B-0005CB9F3756}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{A400B497-088A-4E3E-A9E2-5AD23AF896D1}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{72CD49A6-5398-4336-9C7E-0EAC4AB04438}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{E2134C37-8730-4F12-A2C5-328C05FF113B}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{BD8E0E4B-E2FE-4964-8E30-B22DCEB3E2DC}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{0F5602D1-5169-4F82-9BF8-AB84A1839161}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{AA71FF69-8BFF-4BC4-92B8-4318E8596016}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{C37E095E-F97B-4AAD-B00F-055363FC9FB2}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{5240E4C9-4806-4705-808B-42A8EC2856CB}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{095D6781-E9FE-4ED4-9007-50B9FBC303E6}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{55AD9A79-E709-4743-A45F-3D7EDB59115C}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{F6111FD8-7DD5-4011-BBA7-63EC12F7C547}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{12095888-9DB9-4ECE-915D-36A3A2E41C00}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{943BC349-32A6-49AB-8C3C-85360AE62E78}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{BC61A4A9-3A30-4AC1-B667-5A7A6D8E3224}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{11358CA5-1875-42AB-9305-0E11B7EAD27B}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{235C136B-F705-4D08-A1A2-724DAF41BE56}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{54C8BAFC-86D3-4FC5-B7BE-07E43545D644}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{E44415B2-8A6B-4BE7-B621-D02AAB218A29}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{195CF044-F782-4C6B-9F16-1090B82842C0}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{AA9F0B4C-848A-4490-8C03-21117828CD3E}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{13D193A4-EF5F-4D12-80FA-B63081B03A52}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{6BBDD8D0-177C-422F-8930-11C9D739205D}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{4AA30294-EA3A-4F73-930F-360EDC492588}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{6E9580E0-CF31-4699-A83D-BF21904030FB}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{6484F7F7-09AC-4690-AB34-95F264A1F7AC}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{94792A26-2980-4E5E-84BF-B0CDD5CA7148}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{4A96C99B-CAF8-4496-8881-47413535EB65}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{B5AEF840-3721-4119-B2B0-6C9A0269A592}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{4E5E3D13-56D8-4019-BDC2-4606D7CF4BC4}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{BACBD696-0EA5-414A-95F0-047D2567E72A}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{2244DC10-D6F2-4ECC-BD8C-B12F9FA99ACA}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{0A62598F-08AF-4A04-9949-9B20CA512DA9}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{573B6498-E735-41F7-B5EA-24B82BC88AF7}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{428D1D4B-4D82-4E11-AB46-31D699A608BA}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{D0333E50-14BE-460E-933F-B7E09A53A413}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{438C199B-0AF9-44C4-AD64-A8A92D5AFF9E}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{2B57520E-2A55-4E9A-8080-F86907DFB3E4}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{DD72801B-8434-4977-A06F-2B053DC72C29}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{2E35C290-0215-4D72-A95C-D2F9FE9F3CF4}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{04B34A97-E636-42BA-8C74-1AAB00501EAF}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{DD432357-798C-486D-ADFC-9E874D7F423C}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{978FE173-766E-45D9-A96B-27D6CAE9CB06}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{59FE7AEA-4C25-4E6D-B838-62581B3AFD64}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{9DAC340A-6CB2-4733-85D4-226D6ECCF6E0}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{19149D18-F596-4F8D-A1D8-39FD40F3D552}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{5F6DD265-0A65-49BF-9B8B-29061E3BC99C}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{BB6E1263-DEE8-498A-A032-CD870E4AFD83}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{6549ADC7-59ED-4861-9212-54C4DB15609D}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{D4523349-F1D7-42BE-B03E-33F49BD70089}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{960F1F17-6835-4363-B19E-EFD5D154C207}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{0285EE24-BDA5-4E16-9C06-4891E2A9D292}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{91DDAACB-8C27-4132-82A9-17492945CC8C}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{CBAEF320-3B59-4CA0-8A96-A7E1E6F07A0B}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{675FC99C-A7D1-4079-8AFC-D925682F9372}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{40B08459-1B61-47BA-B71E-4379D143CE0C}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{69E0B6F0-389E-4991-94DF-61595CBBBF29}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{9D671574-DCD4-4B05-8C85-E256907ECAA8}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{DF40DFF8-AAB1-4594-9C12-02C4722728F5}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{3353E644-9342-45CA-8D2E-AA743B7FC67C}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{C98D222A-59A8-4BD3-9BFA-C78A27DCFC0F}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{DF78361B-894B-4DE1-89D0-C652BB53AC85}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{281F6DE8-3BA3-4D1B-B8EA-7D4C466A7092}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{86442B54-A6CD-4292-971D-F5913D1CC86E}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{30A51694-0BD6-4DDD-BBF6-B71252C0C7B9}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{44B948CE-38D7-413A-AB91-A1D1C7D29F6B}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{5A6C3AC2-D307-4EAE-A53C-A5A826A95750}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{D4588F3B-B0A8-489B-B0AD-2B7A3C19D632}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{603CFE32-CA51-4A70-9ECD-4D79CAB9B992}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{31340E92-4CC8-409E-85D5-3AC70D908CE5}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{CCE53585-D529-4F99-9AAE-ECE3B7EEB970}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{1276FFB3-7299-4C03-8997-FD1AEEDF262A}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{DAF63189-C82A-4D04-9B27-E479AB192914}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{19EF2D9D-AB8A-4965-A896-81560B61D63B}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{A14C5EE2-3205-4B24-BF4D-A031FF80E7A4}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{2B0A5046-CD7B-4F7E-9D40-F0380850832D}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{4719FEB2-C711-4ABF-9015-8ED3820426D2}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{61DC9863-6759-4B8C-A5AC-E37E4EFFA198}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{DF7AF787-6186-40CD-9E16-031B70FA6B80}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{E7DE7E37-7237-466A-BDB7-1BE121F37FD8}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{0E29B912-7039-4A28-B0C7-A141153FB735}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{F0FCD770-451C-406F-B14D-FFED2B0A0100}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{FFF9CE35-B5CF-4F1E-8CA2-930647C64B97}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{899BE2C4-A06A-4325-88C9-861B017C12EB}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{3A418C3C-20C4-450C-A21A-12AEE7C8E47D}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{7B592699-A3F7-495E-8090-58463357802E}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{5AFB8BF0-760D-4816-B7CB-33E4FEC932E0}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{4B253C5E-5DDC-4F24-B313-D1B7D1F3E5BB}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{D97417EC-5ADD-4C08-945D-E1228B0AA6F8}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{4617FA53-E342-4AC3-8E31-89D9AA85F47E}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{3EDA86F0-9EE1-4C03-9304-35762B912DC6}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{8DD8DB20-BA47-48E5-B2F1-F5762C49CA7D}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{6581215D-9DB2-443C-96F0-5B1324BCA67B}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{7761D34E-97BE-428D-B210-8F1B6D7E9073}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{2C2073B3-B8B3-440B-A370-F7470D201E3E}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{167DCD94-18EF-4633-A21B-322A34A494DA}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{82D35AE3-AB28-478D-8CF5-373AD39280DF}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{C182967C-518F-4AF7-A07D-02C47AF1FF1A}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{82AC42E6-4A4F-429E-8A4B-C987F31D052A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId106"/>
+    <tablePart r:id="rId110"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31D700D-CA3C-4BDB-B79E-82D53829294A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04048379-775A-4192-8CA8-83B02D135F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="364">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1136,6 +1136,195 @@
   </si>
   <si>
     <t>A petición de cliente roseta se instala fuera de norma, si cumple con el corte en pestaña de roseta</t>
+  </si>
+  <si>
+    <t>1-3NNJY7KN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Extremadura 5372, Quinta Normal </t>
+  </si>
+  <si>
+    <t>Carlos Flores</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1k7NrqxzILvpaTm4qWKGA0--kvvfmIIPD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1KEgvIgqv-ptL598vs8XqqQyy3OhdPw6S</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=18eY7uINq6UqqU6StJ9GOuPT_sbq1-Zdo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=15WtN5v6Aw0eRGykvQp2rGSm_0U6UaInr</t>
+  </si>
+  <si>
+    <t>No retira pestaña en roseta, utiliza herramientas de ambos one click</t>
+  </si>
+  <si>
+    <t>1-3ND4KOAK</t>
+  </si>
+  <si>
+    <t>Pasaje C 68</t>
+  </si>
+  <si>
+    <t>Daniela Segovia</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ZHmYxeoFOC5phCiVio592U7rhVZ0tYXy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1egI1lxqhCpkbi4T4tixnLNGbMi8mvw1h</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=15AlcG5YugrRMwnS_TVvHf372kGJ9nrqg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1KDROq1VK7guj15eYPcVTBxTS5UbN_JpJ</t>
+  </si>
+  <si>
+    <t>Técnico cumple con las normas.</t>
+  </si>
+  <si>
+    <t>1-3NFDRCY3</t>
+  </si>
+  <si>
+    <t>Cotacotani 34</t>
+  </si>
+  <si>
+    <t>Erick Arrue</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_dnXHFhbI_rHIPquJovLBhU46yIrAZ3n</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1mNdABhyD-BWi_0xnmvqaCeLnpVpDiURR</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Vk1aFMxBIdlXyYBKm1PRsmfCVwtQMPsV</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1JyPmA8uNhOVvTRycpVmimBTyYoXMHg0y</t>
+  </si>
+  <si>
+    <t>Técnico cumple con las normas</t>
+  </si>
+  <si>
+    <t>1-3NEG6VRC</t>
+  </si>
+  <si>
+    <t>Las Maravillas 315</t>
+  </si>
+  <si>
+    <t>Katherine Rodriguez</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1pc_PLk8xNWHcoYORgNdryoio50_OJRe6</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1wsYwrN88WDFb7NWHf8osRL8GnpzbB1e_</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=16tLU2tsRGSZYpel88kvrTizbREZsrQ7x</t>
+  </si>
+  <si>
+    <t>Reparación reset de equipos , pruebas de cobertura test de velocidad</t>
+  </si>
+  <si>
+    <t>1-3NG18R4J</t>
+  </si>
+  <si>
+    <t>Carlos Pezoa Véliz 160</t>
+  </si>
+  <si>
+    <t>Susana Salinas</t>
+  </si>
+  <si>
+    <t>2, 4</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cD1N6AEKr1vU2RtVlCAUekMeFW0jONZc</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1LdvtDzcg_Id4QqvHWSPg28VYwtyzhbnq</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1OeTk1d8S6gK4Pi9SvrmwXAB_UlGSOg3H</t>
+  </si>
+  <si>
+    <t>Reparación , se cambia conector cortado en roseta.</t>
+  </si>
+  <si>
+    <t>1-3NJAI727</t>
+  </si>
+  <si>
+    <t>GUERRERO LEIVA ELADIO ANDRES</t>
+  </si>
+  <si>
+    <t>Pasaje E 32</t>
+  </si>
+  <si>
+    <t>Jorge Caamaño</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1KCRYVed39OkGvsCk0Um8ai5Fp51O9jAO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qfFagTsqYMPvdSUFin5YtdOKQ0tlmQiT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1isoAII7ef9vNpSjclPMVQR5qOtG59WxP</t>
+  </si>
+  <si>
+    <t>Reparación drop levantado en CTO.</t>
+  </si>
+  <si>
+    <t>1-3NNEKWHY</t>
+  </si>
+  <si>
+    <t>HECTOR DAVID REYES OLMOS</t>
+  </si>
+  <si>
+    <t>Parinacota 50 depto 21</t>
+  </si>
+  <si>
+    <t>Mama de titular</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14SFHycDeSjKPiGhW0C0rxgm3MRz-nqXT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1knpkTpAujRFTgyyCdsXBosb0UgOFoN2E</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1wFF803e-lPpln5LWOzqcWBALjxkJ23cK</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1MwSEkrsBBQvBBAIH6sUjmiE0-F2pEfCp</t>
+  </si>
+  <si>
+    <t>Instalación , técnico reutiliza drop a petición de cliente el dormitorio lo había forrado palmetas de pluma voy con diseños.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3N7Q47LB </t>
+  </si>
+  <si>
+    <t>Los Limonares 399 casa 19</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ifMagLDjS7-z44QC25L9EwxBgIJHujRK</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=15udke8hsV9VTpZEmGDtbrUO7CrcGQMlP</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1vmgil_WaQ0xuPdmdkg1EXsUweEWPvmfe</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=17dCwfUXA9AI7eeNFUBE4rabzbj9TBekH</t>
+  </si>
+  <si>
+    <t>Instalación por cámaras.</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1461,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1321,6 +1510,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2001,8 +2193,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ32" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ32" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ40" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ40" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
@@ -2248,7 +2440,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ32"/>
+  <dimension ref="A1:AJ40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -5235,122 +5427,871 @@
         <v/>
       </c>
     </row>
+    <row r="33" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46269.998554641206</v>
+      </c>
+      <c r="B33" s="12">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P33" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="T33" s="3">
+        <v>4</v>
+      </c>
+      <c r="U33" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="V33" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="W33" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="X33" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH33" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46271.900488796295</v>
+      </c>
+      <c r="B34" s="12">
+        <v>10</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="T34" s="3">
+        <v>4</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="V34" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="W34" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="X34" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="Y34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB34" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AC34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH34" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46271.909165335645</v>
+      </c>
+      <c r="B35" s="12">
+        <v>9</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P35" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="T35" s="3">
+        <v>4</v>
+      </c>
+      <c r="U35" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="V35" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="W35" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="X35" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB35" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH35" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46271.929969872683</v>
+      </c>
+      <c r="B36" s="12">
+        <v>6</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="T36" s="3">
+        <v>4</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="V36" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="X36" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="Y36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB36" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH36" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46271.935383136573</v>
+      </c>
+      <c r="B37" s="12">
+        <v>8</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P37" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="T37" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="V37" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="X37" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="Y37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA37" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB37" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH37" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46271.948370185186</v>
+      </c>
+      <c r="B38" s="12">
+        <v>8</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="T38" s="3">
+        <v>4</v>
+      </c>
+      <c r="U38" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="V38" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="X38" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA38" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB38" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="AC38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH38" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46271.955678379629</v>
+      </c>
+      <c r="B39" s="12">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P39" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="T39" s="3">
+        <v>3</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="V39" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="W39" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="X39" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="Y39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z39" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA39" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB39" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="AC39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH39" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46271.963903287033</v>
+      </c>
+      <c r="B40" s="12">
+        <v>8</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="T40" s="3">
+        <v>4</v>
+      </c>
+      <c r="U40" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="V40" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="W40" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="X40" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA40" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB40" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="AC40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH40" s="18" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{BAA3B567-023E-437B-8424-37C4D77E1579}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{8412DC1E-6721-4A41-BFE0-585CDF96F9F8}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{CC168C4E-7365-444C-8DDF-5ED046BDE7FD}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{70734598-5382-4BEE-BFD1-2943D5B22768}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{862677B7-3E9B-4652-ABDF-B43C377A9380}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{1468DD04-8972-4DCC-BEA5-9B0F692D612E}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{7465EADD-F15C-4920-BDD7-4B3B95659CC5}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{C0FD9221-7638-4472-82BA-6EDF120A327D}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{3EBD63ED-1361-4BA1-B895-86352553A17E}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{D3FE2140-E49E-423F-BDC7-78DD3470F627}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{3CC0E442-FE79-4A3B-BF4B-0005CB9F3756}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{A400B497-088A-4E3E-A9E2-5AD23AF896D1}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{72CD49A6-5398-4336-9C7E-0EAC4AB04438}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{E2134C37-8730-4F12-A2C5-328C05FF113B}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{BD8E0E4B-E2FE-4964-8E30-B22DCEB3E2DC}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{0F5602D1-5169-4F82-9BF8-AB84A1839161}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{AA71FF69-8BFF-4BC4-92B8-4318E8596016}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{C37E095E-F97B-4AAD-B00F-055363FC9FB2}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{5240E4C9-4806-4705-808B-42A8EC2856CB}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{095D6781-E9FE-4ED4-9007-50B9FBC303E6}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{55AD9A79-E709-4743-A45F-3D7EDB59115C}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{F6111FD8-7DD5-4011-BBA7-63EC12F7C547}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{12095888-9DB9-4ECE-915D-36A3A2E41C00}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{943BC349-32A6-49AB-8C3C-85360AE62E78}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{BC61A4A9-3A30-4AC1-B667-5A7A6D8E3224}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{11358CA5-1875-42AB-9305-0E11B7EAD27B}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{235C136B-F705-4D08-A1A2-724DAF41BE56}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{54C8BAFC-86D3-4FC5-B7BE-07E43545D644}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{E44415B2-8A6B-4BE7-B621-D02AAB218A29}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{195CF044-F782-4C6B-9F16-1090B82842C0}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{AA9F0B4C-848A-4490-8C03-21117828CD3E}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{13D193A4-EF5F-4D12-80FA-B63081B03A52}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{6BBDD8D0-177C-422F-8930-11C9D739205D}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{4AA30294-EA3A-4F73-930F-360EDC492588}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{6E9580E0-CF31-4699-A83D-BF21904030FB}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{6484F7F7-09AC-4690-AB34-95F264A1F7AC}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{94792A26-2980-4E5E-84BF-B0CDD5CA7148}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{4A96C99B-CAF8-4496-8881-47413535EB65}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{B5AEF840-3721-4119-B2B0-6C9A0269A592}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{4E5E3D13-56D8-4019-BDC2-4606D7CF4BC4}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{BACBD696-0EA5-414A-95F0-047D2567E72A}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{2244DC10-D6F2-4ECC-BD8C-B12F9FA99ACA}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{0A62598F-08AF-4A04-9949-9B20CA512DA9}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{573B6498-E735-41F7-B5EA-24B82BC88AF7}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{428D1D4B-4D82-4E11-AB46-31D699A608BA}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{D0333E50-14BE-460E-933F-B7E09A53A413}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{438C199B-0AF9-44C4-AD64-A8A92D5AFF9E}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{2B57520E-2A55-4E9A-8080-F86907DFB3E4}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{DD72801B-8434-4977-A06F-2B053DC72C29}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{2E35C290-0215-4D72-A95C-D2F9FE9F3CF4}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{04B34A97-E636-42BA-8C74-1AAB00501EAF}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{DD432357-798C-486D-ADFC-9E874D7F423C}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{978FE173-766E-45D9-A96B-27D6CAE9CB06}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{59FE7AEA-4C25-4E6D-B838-62581B3AFD64}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{9DAC340A-6CB2-4733-85D4-226D6ECCF6E0}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{19149D18-F596-4F8D-A1D8-39FD40F3D552}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{5F6DD265-0A65-49BF-9B8B-29061E3BC99C}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{BB6E1263-DEE8-498A-A032-CD870E4AFD83}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{6549ADC7-59ED-4861-9212-54C4DB15609D}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{D4523349-F1D7-42BE-B03E-33F49BD70089}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{960F1F17-6835-4363-B19E-EFD5D154C207}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{0285EE24-BDA5-4E16-9C06-4891E2A9D292}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{91DDAACB-8C27-4132-82A9-17492945CC8C}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{CBAEF320-3B59-4CA0-8A96-A7E1E6F07A0B}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{675FC99C-A7D1-4079-8AFC-D925682F9372}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{40B08459-1B61-47BA-B71E-4379D143CE0C}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{69E0B6F0-389E-4991-94DF-61595CBBBF29}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{9D671574-DCD4-4B05-8C85-E256907ECAA8}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{DF40DFF8-AAB1-4594-9C12-02C4722728F5}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{3353E644-9342-45CA-8D2E-AA743B7FC67C}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{C98D222A-59A8-4BD3-9BFA-C78A27DCFC0F}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{DF78361B-894B-4DE1-89D0-C652BB53AC85}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{281F6DE8-3BA3-4D1B-B8EA-7D4C466A7092}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{86442B54-A6CD-4292-971D-F5913D1CC86E}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{30A51694-0BD6-4DDD-BBF6-B71252C0C7B9}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{44B948CE-38D7-413A-AB91-A1D1C7D29F6B}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{5A6C3AC2-D307-4EAE-A53C-A5A826A95750}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{D4588F3B-B0A8-489B-B0AD-2B7A3C19D632}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{603CFE32-CA51-4A70-9ECD-4D79CAB9B992}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{31340E92-4CC8-409E-85D5-3AC70D908CE5}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{CCE53585-D529-4F99-9AAE-ECE3B7EEB970}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{1276FFB3-7299-4C03-8997-FD1AEEDF262A}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{DAF63189-C82A-4D04-9B27-E479AB192914}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{19EF2D9D-AB8A-4965-A896-81560B61D63B}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{A14C5EE2-3205-4B24-BF4D-A031FF80E7A4}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{2B0A5046-CD7B-4F7E-9D40-F0380850832D}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{4719FEB2-C711-4ABF-9015-8ED3820426D2}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{61DC9863-6759-4B8C-A5AC-E37E4EFFA198}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{DF7AF787-6186-40CD-9E16-031B70FA6B80}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{E7DE7E37-7237-466A-BDB7-1BE121F37FD8}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{0E29B912-7039-4A28-B0C7-A141153FB735}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{F0FCD770-451C-406F-B14D-FFED2B0A0100}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{FFF9CE35-B5CF-4F1E-8CA2-930647C64B97}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{899BE2C4-A06A-4325-88C9-861B017C12EB}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{3A418C3C-20C4-450C-A21A-12AEE7C8E47D}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{7B592699-A3F7-495E-8090-58463357802E}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{5AFB8BF0-760D-4816-B7CB-33E4FEC932E0}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{4B253C5E-5DDC-4F24-B313-D1B7D1F3E5BB}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{D97417EC-5ADD-4C08-945D-E1228B0AA6F8}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{4617FA53-E342-4AC3-8E31-89D9AA85F47E}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{3EDA86F0-9EE1-4C03-9304-35762B912DC6}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{8DD8DB20-BA47-48E5-B2F1-F5762C49CA7D}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{6581215D-9DB2-443C-96F0-5B1324BCA67B}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{7761D34E-97BE-428D-B210-8F1B6D7E9073}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{2C2073B3-B8B3-440B-A370-F7470D201E3E}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{167DCD94-18EF-4633-A21B-322A34A494DA}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{82D35AE3-AB28-478D-8CF5-373AD39280DF}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{C182967C-518F-4AF7-A07D-02C47AF1FF1A}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{82AC42E6-4A4F-429E-8A4B-C987F31D052A}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{70787C97-4872-4712-A385-08C9BB7FF0B2}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{0FBC97CF-A34B-4FF2-8658-B94AACF6A010}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{DB483E08-DE1A-4425-BA52-26874C80D595}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{F3BE3203-661B-4B5B-8301-593D478FD790}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{1D17DBAF-9922-4FA8-AC6B-FBEFFE5608E5}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{0784DFDC-F160-4FAF-823F-86734E61FAB1}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{7C3CB6F4-5572-4FF3-89A1-28266A615CC4}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{212A86AA-56A7-423B-990C-3A6344405FFA}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{9A231250-40DC-4CC0-8B53-F65210EB085E}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{7906325E-CD7C-4215-A78A-400EB5A7E1EF}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{3FE5A494-C472-44FC-8CEE-25BD7FC4BEEC}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{311FD07B-4680-4252-924E-0A80D14D2B6D}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{3444EF37-3541-42B8-BA51-C4416A58A2C0}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{62192F0D-8807-4C8C-93C6-B76D6531DF0D}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{638ACFC6-286B-4023-BE42-F6E19FCDCB40}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{66C81DE4-DF55-458E-884D-41C12E5EFF9C}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{C95617EA-9487-45FC-AF6E-A78FF4D366C8}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{3B6EE264-F28F-408A-B606-C987E07C8E71}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{34EF51DA-5977-4AB3-A1DD-4987710D9F1A}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{14A3E8B0-6B44-4864-A87A-8FD235984FC3}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{BEBAD603-7535-46FE-8E47-06DB7E9551E2}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{4BC07AD9-8131-4099-9A76-7598FADB87F0}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{06FE792C-B485-49D6-84A4-F66EA6778C62}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{BD513C53-19AC-4C64-918E-2E5FD5235F71}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{7884F252-4015-4405-96E9-72F2CC5D4A55}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{8FD0B193-BABA-4B6D-B685-34C08658FBF6}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{B97CA2BF-5501-4E48-B5D1-9143E927E70C}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{8534A5D0-F1C9-4ED0-806B-D1EF71790332}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{30BBE415-F826-40CA-9C5A-FE0A8BD726AA}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{88F7B35B-ECA9-46A6-844E-CA1F08CCD3D6}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{24A5185E-D014-4571-B146-26D6ABBC2D82}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{B3F9F8DD-1FA8-4882-8B36-8D72A203C6D6}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{B16F70D9-1288-4074-9FAB-E41A4B85D530}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{1DC07FE4-AAAD-4E79-8EA1-6D3FEAD15465}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{640B2DFA-1E33-4065-A0EC-8CF5FA526933}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{87CF7082-4E2C-4DF8-81FB-9CF9A07BAAE0}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{0DAE576E-2744-4A38-B6ED-6FDDCCE1C194}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{A8901A9E-CE22-4B31-95CB-8069ED1A2308}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{4246084E-C696-4DEC-B5A6-472581F5BAF3}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{2D4772E8-2ACC-4DAF-A4CE-0E797969B115}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{3D8DB65E-DA51-4104-812C-82801CE526EC}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{453C5CBF-0AC5-4C99-8147-C208797B4E3C}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{A46F4F60-E3E2-4D3F-AF82-93ADAB07AF4D}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{97850B8D-66E2-4015-AE24-2950CF8B60CE}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{FB2A3267-0D1A-4C0E-B899-6E4874732613}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{F68A167E-A87B-494A-AF51-21D21C86A407}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{110D2EF0-2F40-4730-BABE-92683C173640}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{59A3CF8A-348A-4D6F-AA96-5C3DB7E59024}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{78924957-D18A-4DA4-AE98-01E41165E3E3}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{9869F478-F457-4C22-BCB6-2D5963EB8773}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{AA3F78C5-67F6-4702-9C94-1E906482968A}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{C57856B1-7A7C-4159-9ABD-78185636D0EF}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{BD9347BE-92EA-4817-ADC9-70B5300669D4}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{E08CDDBF-C36A-4121-AE46-B12E28F4B39B}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{7BED1DEB-A492-41B4-9364-2350233BB9E5}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{82A92D6E-66F9-4285-B8BC-BAA203616AAD}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{810F6F86-6EF7-49A5-8E0C-044C2B71F4AB}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{62FA60A2-4C88-4398-BA9A-7C74F7900808}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{3BBDBA11-130F-4665-BF0D-564C01178AD3}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{F0C435CC-5821-430B-BB3C-15BC895FF3DB}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{99B6BE78-D3DB-4101-8E49-30D7497B291C}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{69EC841B-7680-4AEF-844A-21645382CF9E}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{A5E42D09-90FE-4C44-A3D6-73259CA943E2}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{D6E0A55A-D8E0-4EBF-9C3D-BD55BB19EE20}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{E010B529-3BBF-4654-A2D6-9B9B56529515}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{363AB0FC-F5FE-4863-93AE-1893E2DBEEF3}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{A5A0839E-3C85-4B97-9BD5-70BBDA1275D6}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{D3C90D1D-6300-42DE-BEC7-A50BA877A629}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{F077CE4F-F922-4EB7-B3F9-A3F1634F36E7}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{8C268920-51EB-41AA-A6F1-F6CD547DE958}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{FBE75348-DE69-48F2-8151-3C262021FB92}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{C30F1092-FFEF-429B-B3D1-8D3759B07C0F}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{D8526710-207E-4610-BAA1-942ADA93C668}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{1817C61A-BAA8-47A8-96A6-707A65F2D222}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{34BF8E9A-17E5-4507-AF80-BCC3A481E391}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{D1BD2E71-AF9D-4194-AD3E-C2CCFFBC687C}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{88D63A34-CD64-4B65-A01D-CECEA660E2AB}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{7DB6245B-EFD6-4369-A083-A866D4D3F19C}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{A014D0D3-65F0-49D4-8764-2D7229593D2F}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{583E4916-A7C7-4F48-A458-929299B787E4}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{1C1F7DA8-58A3-4228-8030-CBD758D0AD97}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{55F127EA-34A6-4726-9716-1B74F7839D96}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{626D3CFA-E881-4B8A-A614-36BDE5EF24AC}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{7BB20C1C-CF78-4961-B2F7-AA4E621F78BD}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{07C5E6E9-79C8-4A2C-ADCA-A4EB335E4670}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{E4404530-7429-4A5C-AE36-221CE76E8F42}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{85B65970-5A29-498C-AA66-2D36F5A9D8A1}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{BB2A4088-560F-4D25-A1C6-B53D6D6E6857}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{F8DDD0F8-429C-48B1-98CC-A735EB232876}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{9278F556-4012-45B9-8569-6CC34A6D764B}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{C03530B6-85F7-4CF5-8371-D0BF2B4B6E7C}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{94825110-463D-4E7B-A771-BAD900A80815}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{4FA438BA-E3FC-40D7-BB3A-F1CB295B835F}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{005AC1F2-23BF-4E47-ADC5-EFB00833CF9B}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{1C4040DB-79A4-4E82-A70E-534DA43E7B81}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{4673724B-96AB-4CAA-B338-7B31D09BAE5C}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{D8851976-D8B2-4205-9C05-96D8D41223CE}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{692A1774-3284-4E97-A0B8-A584B3FB3040}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{88706A56-B628-4597-B650-147ABDF9B4CD}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{79A3AE9B-5111-4E10-9F31-714C94638E29}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{530E1E9B-C95F-4EA6-B64C-850052654EC5}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{6C4F23BD-6711-4CF2-9505-26399987766F}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{872766A9-5621-4E53-978C-B66FD9919342}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{BAF0534C-0181-41D1-AC8F-4BD0BB958E5C}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{AD80B5C1-D55E-41E0-B3B4-79A1FECD4471}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{5174572A-29F5-4224-AF7B-A2C04BAC4778}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{4F1BFA16-6129-4B05-A43C-F0E9FC9872B0}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{4B1B8EB0-50C8-4D21-8577-ED8EDC7C2182}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{D37EE459-B57B-4ED6-B8EE-B0E6B0B89862}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{E8EFE3EF-EDB0-4757-9D81-17A1DAFB4FB6}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{D5334C99-3A9A-4FB0-A948-90735319C17D}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{4638D607-E39C-4B19-8D47-CE0DBA229E72}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{7BBB0ABD-5F32-49B8-AC65-109950883457}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{66C18F5B-1615-4446-9E81-C53D7C943F5E}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{EEBB466F-85DF-41E0-97FA-19C4DEE47226}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{BEC46DB5-3DFF-4F94-AAFE-B047549BFA7C}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{3D134619-2A60-4C0A-B393-7D3480AD16A1}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{CA242DE5-9271-4EDF-9522-66B5F072EBB6}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{65CC60B3-1F32-4B04-B7AB-5F86B4B1B0FA}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{3F1FA653-973A-4EAD-90E9-55F96932A347}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{D2ACDA8B-8064-49CE-B425-3039A83782E9}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{DA906C18-681F-4AF4-9F10-E1378A15209B}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{2BA2F78E-6B26-48FE-845E-0E7ECA39E071}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{8877B922-307F-4E51-A6E9-51A3623E9B4A}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{14D088ED-02B1-4FB2-8083-1EAD4054E5BF}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{5583EA92-1DC6-401A-84C1-86B79170B7C9}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{B1A62E79-86A6-4138-ADAC-7950C6028124}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{5BCC5DC6-6B62-4600-A4E2-44C0A6715B78}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{B765028D-25EE-47F7-A7D8-5CA82426BA8B}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{FD11E3E4-8167-4DD5-A214-542270947460}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{D051C57B-BE45-4E4A-884E-5FCF3C58A91A}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{1E7D7753-3130-4409-9351-EA4D0842B4B9}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{06EBA1D9-839A-4338-8FB1-EC0014547C2E}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{D2C72A92-A1E8-44C6-A1D3-08030FADAED5}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{58BAB32F-5B9F-4959-9141-EAA5A18D2150}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{79990874-0D35-4D3A-A81F-FB3EDDF5CD13}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{D67D23E4-D107-4C47-A6C2-0AF1A7AD2F8D}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{893D3346-B71D-4F39-A954-FFA8E77A41A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId110"/>
+    <tablePart r:id="rId139"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04048379-775A-4192-8CA8-83B02D135F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F695084F-9F37-4CBC-BE5A-3FC8735165E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
     <sheet name="masa de trabajo" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'masa de trabajo'!$B$1:$D$39</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="378">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -337,9 +340,6 @@
   </si>
   <si>
     <t>No limpia fibra con alcohol isopropilico fibra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre </t>
   </si>
   <si>
     <t>1-3N5HPGPG</t>
@@ -1325,6 +1325,51 @@
   </si>
   <si>
     <t>Instalación por cámaras.</t>
+  </si>
+  <si>
+    <t>1-3NOYLK2D</t>
+  </si>
+  <si>
+    <t>XAVIER NATERA MARTINEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los suspiros 2864, Quinta Normal </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14swrKT8z_gymQwhT5IhdH-mVs0pplGko</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ANguWjjWSjseyLds8byVP6N9nzOT39tx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1wKQpc_z6296Zpf7qLkmrb96dsJw9h1ez</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1-1rwkehkMlzlYTR3c3C47jf_-71kQDOU</t>
+  </si>
+  <si>
+    <t>1-3NOTROJ0</t>
+  </si>
+  <si>
+    <t>Av Cardenal Jose Maria Caro 3368, Independencia</t>
+  </si>
+  <si>
+    <t>Freddy Flores</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1fr8kqb0qYgoW1kJvGmuYSGKXphKqkO4S</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1GrHh-fNVvY4NmvaaOiftMkxS_2xxmyxP</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Wskr8uc0GZARG5xMSg7mC1mqiEcPBwIx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qFeraJ0W0wL6xeEvbWqkxvRVd6vkiZLO</t>
+  </si>
+  <si>
+    <t>Solo falta utilizar ambos one click</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1475,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1447,21 +1492,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF5B3F86"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1479,7 +1515,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1488,9 +1523,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1505,9 +1537,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1520,42 +1549,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1733,60 +1726,6 @@
         <color rgb="FF0000FF"/>
         <name val="Roboto"/>
         <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <name val="Roboto"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2111,6 +2050,96 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
@@ -2193,47 +2222,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ40" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ40" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ42" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ42" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="18"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
-    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="30"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="13"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="12"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="10"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="9"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="8"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="28"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="2"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="27"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="0"/>
+    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="26"/>
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="25" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno"/>
-    <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones " dataCellStyle="Bueno"/>
+    <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
+      <calculatedColumnFormula>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="31" xr3:uid="{6A4280CD-66D9-45AA-9502-7B76CE3469BE}" name="Observaciones " dataCellStyle="Bueno">
+      <calculatedColumnFormula>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Respuestas de formulario 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2440,7 +2473,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -2476,119 +2509,119 @@
     <col min="31" max="31" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="37.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="35.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="76" style="14" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="37.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="35.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="76" style="12" bestFit="1" customWidth="1"/>
     <col min="37" max="39" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="W1" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="X1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y1" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB1" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="L1" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="V1" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="W1" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="X1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y1" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="Z1" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA1" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB1" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AD1" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AE1" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="AE1" s="16" t="s">
+      <c r="AF1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AF1" s="16" t="s">
+      <c r="AG1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="AG1" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH1" s="13" t="s">
+      <c r="AH1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="AI1" s="14" t="s">
+      <c r="AI1" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="AJ1" s="14" t="s">
+      <c r="AJ1" s="12" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2680,12 +2713,17 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
-      <c r="AH2" s="13" t="str">
+      <c r="AH2" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI2" s="14" t="s">
-        <v>23</v>
+      <c r="AI2" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ2" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2770,15 +2808,17 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
-      <c r="AH3" s="13" t="str">
+      <c r="AH3" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI3" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ3" s="14" t="s">
-        <v>118</v>
+      <c r="AI3" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ3" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>Auque se nota una mejora, se realizara evantualemete seguimiento a los trabajos</v>
       </c>
     </row>
     <row r="4" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2865,12 +2905,17 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
-      <c r="AH4" s="13" t="str">
+      <c r="AH4" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI4" s="14" t="s">
-        <v>23</v>
+      <c r="AI4" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ4" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>Auque se nota una mejora, se realizara evantualemete seguimiento a los trabajos</v>
       </c>
     </row>
     <row r="5" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2957,9 +3002,17 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
-      <c r="AH5" s="13" t="str">
+      <c r="AH5" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
+      </c>
+      <c r="AI5" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ5" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3052,12 +3105,17 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
-      <c r="AH6" s="13" t="str">
+      <c r="AH6" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI6" s="14" t="s">
-        <v>23</v>
+      <c r="AI6" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ6" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3135,9 +3193,17 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
-      <c r="AH7" s="13" t="str">
+      <c r="AH7" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
+      </c>
+      <c r="AI7" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ7" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3224,11 +3290,17 @@
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
-      <c r="AH8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>23</v>
+      <c r="AH8" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI8" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ8" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3312,9 +3384,17 @@
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
-      <c r="AH9" s="13" t="str">
+      <c r="AH9" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
+      </c>
+      <c r="AI9" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ9" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3325,10 +3405,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>17</v>
@@ -3349,7 +3429,7 @@
         <v>21</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>21</v>
@@ -3364,19 +3444,19 @@
         <v>23</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T10" s="3">
         <v>4</v>
       </c>
       <c r="U10" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="V10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="V10" s="4" t="s">
+      <c r="X10" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="X10" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>30</v>
@@ -3388,19 +3468,24 @@
         <v>6</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
-      <c r="AH10" s="13" t="str">
+      <c r="AH10" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI10" s="14" t="s">
-        <v>23</v>
+      <c r="AI10" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ10" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3411,10 +3496,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>53</v>
@@ -3435,37 +3520,37 @@
         <v>21</v>
       </c>
       <c r="L11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="T11" s="3">
         <v>4</v>
       </c>
       <c r="U11" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="V11" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="V11" s="4" t="s">
+      <c r="W11" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="W11" s="4" t="s">
+      <c r="X11" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="X11" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>30</v>
@@ -3477,33 +3562,38 @@
         <v>10</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-      <c r="AH11" s="13" t="str">
+      <c r="AH11" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="AI11" s="14" t="s">
-        <v>238</v>
+        <v>-</v>
+      </c>
+      <c r="AI11" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ11" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46248.497756516204</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="10">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>17</v>
@@ -3515,7 +3605,7 @@
         <v>18</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>41</v>
@@ -3524,28 +3614,28 @@
         <v>23</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="T12" s="3">
         <v>4</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>23</v>
@@ -3562,26 +3652,31 @@
       <c r="AG12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH12" s="13" t="str">
+      <c r="AH12" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI12" s="14" t="s">
-        <v>23</v>
+      <c r="AI12" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ12" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="13" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46251.615196585648</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="10">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>53</v>
@@ -3593,7 +3688,7 @@
         <v>18</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>41</v>
@@ -3602,37 +3697,37 @@
         <v>23</v>
       </c>
       <c r="L13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="T13" s="3">
         <v>4</v>
       </c>
       <c r="U13" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="V13" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="V13" s="4" t="s">
+      <c r="W13" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="W13" s="4" t="s">
+      <c r="X13" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="Y13" s="3" t="s">
         <v>30</v>
@@ -3644,7 +3739,7 @@
         <v>8</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AD13" s="3" t="s">
         <v>23</v>
@@ -3655,23 +3750,31 @@
       <c r="AG13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH13" s="13" t="str">
+      <c r="AH13" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v>SI</v>
+        <v>-</v>
+      </c>
+      <c r="AI13" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ13" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46251.636683425924</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="10">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>53</v>
@@ -3683,7 +3786,7 @@
         <v>77</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>41</v>
@@ -3692,16 +3795,16 @@
         <v>21</v>
       </c>
       <c r="L14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W14" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W14" s="4" t="s">
+      <c r="X14" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="X14" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>72</v>
@@ -3710,7 +3813,7 @@
         <v>7</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>23</v>
@@ -3721,23 +3824,31 @@
       <c r="AG14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH14" s="13" t="str">
+      <c r="AH14" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v>SI</v>
+        <v>-</v>
+      </c>
+      <c r="AI14" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ14" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46252.401138136571</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="10">
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>17</v>
@@ -3758,31 +3869,31 @@
         <v>23</v>
       </c>
       <c r="L15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="T15" s="3">
         <v>4</v>
       </c>
       <c r="U15" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="V15" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="V15" s="4" t="s">
+      <c r="X15" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="X15" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>30</v>
@@ -3794,7 +3905,7 @@
         <v>7</v>
       </c>
       <c r="AB15" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>23</v>
@@ -3811,26 +3922,31 @@
       <c r="AG15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH15" s="13" t="str">
+      <c r="AH15" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="AI15" s="14" t="s">
-        <v>238</v>
+        <v>-</v>
+      </c>
+      <c r="AI15" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ15" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46252.407164965276</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>17</v>
@@ -3851,34 +3967,34 @@
         <v>23</v>
       </c>
       <c r="L16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="T16" s="3">
         <v>3</v>
       </c>
       <c r="U16" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="V16" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="V16" s="4" t="s">
+      <c r="W16" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="X16" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="X16" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="Y16" s="3" t="s">
         <v>72</v>
@@ -3890,7 +4006,7 @@
         <v>4</v>
       </c>
       <c r="AB16" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AC16" s="3" t="s">
         <v>23</v>
@@ -3907,26 +4023,31 @@
       <c r="AG16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH16" s="13" t="str">
+      <c r="AH16" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="AI16" s="14" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="17" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-</v>
+      </c>
+      <c r="AI16" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ16" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46252.439018576391</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="10">
         <v>6</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>64</v>
@@ -3938,10 +4059,10 @@
         <v>18</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>20</v>
@@ -3950,7 +4071,7 @@
         <v>23</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>21</v>
@@ -3971,19 +4092,19 @@
         <v>23</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="T17" s="3">
         <v>4</v>
       </c>
       <c r="U17" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="V17" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="V17" s="4" t="s">
+      <c r="X17" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="X17" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>30</v>
@@ -3995,7 +4116,7 @@
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>77</v>
@@ -4012,25 +4133,31 @@
       <c r="AG17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI17" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH17" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI17" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ17" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46252.569284895828</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>53</v>
@@ -4051,7 +4178,7 @@
         <v>23</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>23</v>
@@ -4072,16 +4199,16 @@
         <v>4</v>
       </c>
       <c r="U18" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="V18" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="V18" s="4" t="s">
+      <c r="W18" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="W18" s="4" t="s">
+      <c r="X18" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="X18" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>30</v>
@@ -4093,7 +4220,7 @@
         <v>9</v>
       </c>
       <c r="AB18" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>77</v>
@@ -4110,311 +4237,337 @@
       <c r="AG18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH18" s="13" t="str">
+      <c r="AH18" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI18" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ18" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46252.579421759263</v>
+      </c>
+      <c r="B19" s="10">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="T19" s="3">
+        <v>4</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH19" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="19" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>46252.579421759263</v>
-      </c>
-      <c r="B19" s="12">
-        <v>7</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="T19" s="3">
-        <v>4</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="X19" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y19" s="3" t="s">
+      <c r="AI19" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ19" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46252.687401099538</v>
+      </c>
+      <c r="B20" s="10">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P20" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" s="3">
+        <v>3</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Z19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA19" s="3">
-        <v>9</v>
-      </c>
-      <c r="AB19" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="AD19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH19" s="13" t="str">
+      <c r="AA20" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH20" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="20" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>46252.687401099538</v>
-      </c>
-      <c r="B20" s="12">
-        <v>8</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="AI20" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ20" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46253.408800335645</v>
+      </c>
+      <c r="B21" s="10">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P20" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="T20" s="3">
-        <v>3</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="V20" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="W20" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="X20" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y20" s="3" t="s">
+      <c r="J21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="T21" s="3">
+        <v>4</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA21" s="3">
         <v>5</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH20" s="13" t="str">
+      <c r="AB21" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH21" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-      <c r="AI20" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>46253.408800335645</v>
-      </c>
-      <c r="B21" s="12">
-        <v>7</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="T21" s="3">
-        <v>4</v>
-      </c>
-      <c r="U21" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="V21" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="X21" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH21" s="13" t="str">
-        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="AI21" s="14" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI21" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ21" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46254.036589560186</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="10">
         <v>9</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>63</v>
@@ -4435,37 +4588,37 @@
         <v>20</v>
       </c>
       <c r="L22" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="T22" s="3">
         <v>4</v>
       </c>
       <c r="U22" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="V22" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="V22" s="4" t="s">
+      <c r="W22" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="W22" s="4" t="s">
+      <c r="X22" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="X22" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>30</v>
@@ -4477,7 +4630,7 @@
         <v>10</v>
       </c>
       <c r="AB22" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>23</v>
@@ -4494,23 +4647,31 @@
       <c r="AG22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH22" s="13" t="str">
+      <c r="AH22" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="23" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI22" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ22" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46254.792688402777</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="10">
         <v>5</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>53</v>
@@ -4528,7 +4689,7 @@
         <v>54</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>23</v>
@@ -4546,22 +4707,22 @@
         <v>23</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="T23" s="3">
         <v>4</v>
       </c>
       <c r="U23" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="V23" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="W23" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="X23" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="X23" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>30</v>
@@ -4573,27 +4734,33 @@
         <v>9</v>
       </c>
       <c r="AB23" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="AH23" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI23" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="AH23" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI23" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ23" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46255.391508726854</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="10">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>64</v>
@@ -4614,7 +4781,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>21</v>
@@ -4635,22 +4802,22 @@
         <v>23</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="T24" s="3">
         <v>4</v>
       </c>
       <c r="U24" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="V24" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="V24" s="4" t="s">
+      <c r="W24" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="W24" s="4" t="s">
+      <c r="X24" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>30</v>
@@ -4662,7 +4829,7 @@
         <v>4</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>23</v>
@@ -4679,23 +4846,28 @@
       <c r="AG24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH24" s="13" t="str">
+      <c r="AH24" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="AI24" s="14" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-</v>
+      </c>
+      <c r="AI24" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ24" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46258.603575879628</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="10">
         <v>7</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>75</v>
@@ -4710,7 +4882,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>41</v>
@@ -4719,7 +4891,7 @@
         <v>23</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>23</v>
@@ -4737,19 +4909,19 @@
         <v>23</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T25" s="3">
         <v>4</v>
       </c>
       <c r="U25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="V25" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="V25" s="4" t="s">
+      <c r="X25" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="Y25" s="3" t="s">
         <v>30</v>
@@ -4761,7 +4933,7 @@
         <v>8</v>
       </c>
       <c r="AB25" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AD25" s="3" t="s">
         <v>23</v>
@@ -4772,23 +4944,31 @@
       <c r="AG25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH25" s="13" t="str">
+      <c r="AH25" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="26" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI25" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ25" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46258.674336504628</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="10">
         <v>7</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>53</v>
@@ -4800,7 +4980,7 @@
         <v>18</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>20</v>
@@ -4809,37 +4989,37 @@
         <v>23</v>
       </c>
       <c r="L26" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="T26" s="3">
         <v>4</v>
       </c>
       <c r="U26" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="V26" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="V26" s="4" t="s">
+      <c r="W26" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="W26" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>30</v>
@@ -4851,7 +5031,7 @@
         <v>8</v>
       </c>
       <c r="AB26" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>23</v>
@@ -4862,25 +5042,31 @@
       <c r="AG26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH26" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI26" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH26" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI26" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ26" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46260.768395266205</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="10">
         <v>6</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>53</v>
@@ -4892,7 +5078,7 @@
         <v>18</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>20</v>
@@ -4901,7 +5087,7 @@
         <v>23</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>21</v>
@@ -4916,22 +5102,22 @@
         <v>23</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T27" s="3">
         <v>4</v>
       </c>
       <c r="U27" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="V27" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="V27" s="4" t="s">
+      <c r="W27" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="W27" s="4" t="s">
+      <c r="X27" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="X27" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>30</v>
@@ -4943,7 +5129,7 @@
         <v>9</v>
       </c>
       <c r="AB27" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>23</v>
@@ -4954,20 +5140,28 @@
       <c r="AG27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH27" s="18" t="str">
+      <c r="AH27" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>SI</v>
+      </c>
+      <c r="AI27" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ27" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46261.683956793982</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="10">
         <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>84</v>
@@ -4991,37 +5185,37 @@
         <v>23</v>
       </c>
       <c r="L28" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="T28" s="3">
         <v>4</v>
       </c>
       <c r="U28" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="V28" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="V28" s="4" t="s">
+      <c r="W28" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="W28" s="4" t="s">
+      <c r="X28" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="X28" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="Y28" s="3" t="s">
         <v>30</v>
@@ -5033,7 +5227,7 @@
         <v>10</v>
       </c>
       <c r="AB28" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AC28" s="3" t="s">
         <v>23</v>
@@ -5050,23 +5244,31 @@
       <c r="AG28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH28" s="18" t="str">
+      <c r="AH28" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>SI</v>
+      </c>
+      <c r="AI28" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ28" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46266.650122476851</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="10">
         <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>53</v>
@@ -5084,7 +5286,7 @@
         <v>41</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>23</v>
@@ -5102,16 +5304,16 @@
         <v>4</v>
       </c>
       <c r="U29" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="V29" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="V29" s="4" t="s">
+      <c r="W29" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="W29" s="4" t="s">
+      <c r="X29" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="X29" s="4" t="s">
-        <v>275</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>30</v>
@@ -5123,7 +5325,7 @@
         <v>9</v>
       </c>
       <c r="AB29" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>77</v>
@@ -5140,23 +5342,31 @@
       <c r="AG29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH29" s="18" t="str">
+      <c r="AH29" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-</v>
+      </c>
+      <c r="AI29" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ29" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46266.829720358801</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="10">
         <v>9</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>53</v>
@@ -5177,7 +5387,7 @@
         <v>23</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>23</v>
@@ -5195,22 +5405,22 @@
         <v>23</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T30" s="3">
         <v>4</v>
       </c>
       <c r="U30" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="V30" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="V30" s="4" t="s">
+      <c r="W30" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="W30" s="4" t="s">
+      <c r="X30" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="X30" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="Y30" s="3" t="s">
         <v>30</v>
@@ -5222,7 +5432,7 @@
         <v>9</v>
       </c>
       <c r="AB30" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AC30" s="3" t="s">
         <v>77</v>
@@ -5239,23 +5449,31 @@
       <c r="AG30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH30" s="18" t="str">
+      <c r="AH30" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>SI</v>
+      </c>
+      <c r="AI30" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ30" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46267.696003368052</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="10">
         <v>8</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>53</v>
@@ -5276,7 +5494,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>21</v>
@@ -5294,16 +5512,16 @@
         <v>4</v>
       </c>
       <c r="U31" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="V31" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="V31" s="4" t="s">
+      <c r="W31" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="W31" s="4" t="s">
+      <c r="X31" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="X31" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="Y31" s="3" t="s">
         <v>30</v>
@@ -5315,7 +5533,7 @@
         <v>9</v>
       </c>
       <c r="AB31" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC31" s="3" t="s">
         <v>23</v>
@@ -5332,23 +5550,31 @@
       <c r="AG31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH31" s="18" t="str">
+      <c r="AH31" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>SI</v>
+      </c>
+      <c r="AI31" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ31" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46268.671411990741</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="10">
         <v>6</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>53</v>
@@ -5360,7 +5586,7 @@
         <v>18</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>41</v>
@@ -5369,37 +5595,37 @@
         <v>23</v>
       </c>
       <c r="L32" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="T32" s="3">
         <v>4</v>
       </c>
       <c r="U32" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="V32" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="V32" s="4" t="s">
+      <c r="W32" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="W32" s="4" t="s">
+      <c r="X32" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="X32" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>30</v>
@@ -5411,7 +5637,7 @@
         <v>9</v>
       </c>
       <c r="AB32" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>23</v>
@@ -5422,20 +5648,28 @@
       <c r="AG32" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH32" s="18" t="str">
+      <c r="AH32" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-</v>
+      </c>
+      <c r="AI32" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ32" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46269.998554641206</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="10">
         <v>10</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>63</v>
@@ -5459,7 +5693,7 @@
         <v>23</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>23</v>
@@ -5477,22 +5711,22 @@
         <v>23</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T33" s="3">
         <v>4</v>
       </c>
       <c r="U33" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="V33" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="V33" s="4" t="s">
+      <c r="W33" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="W33" s="4" t="s">
+      <c r="X33" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="X33" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>30</v>
@@ -5504,7 +5738,7 @@
         <v>9</v>
       </c>
       <c r="AB33" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>23</v>
@@ -5521,23 +5755,31 @@
       <c r="AG33" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH33" s="18" t="str">
+      <c r="AH33" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="34" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI33" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ33" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46271.900488796295</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="10">
         <v>10</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>17</v>
@@ -5558,7 +5800,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>23</v>
@@ -5579,22 +5821,22 @@
         <v>23</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="T34" s="3">
         <v>4</v>
       </c>
       <c r="U34" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="V34" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="V34" s="4" t="s">
+      <c r="W34" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="W34" s="4" t="s">
+      <c r="X34" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="X34" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="Y34" s="3" t="s">
         <v>30</v>
@@ -5606,7 +5848,7 @@
         <v>7</v>
       </c>
       <c r="AB34" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AC34" s="3" t="s">
         <v>23</v>
@@ -5623,23 +5865,31 @@
       <c r="AG34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH34" s="18" t="str">
+      <c r="AH34" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="35" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI34" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ34" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46271.909165335645</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="10">
         <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>17</v>
@@ -5660,7 +5910,7 @@
         <v>23</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>23</v>
@@ -5675,22 +5925,22 @@
         <v>23</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T35" s="3">
         <v>4</v>
       </c>
       <c r="U35" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="V35" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="V35" s="4" t="s">
+      <c r="W35" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="W35" s="4" t="s">
+      <c r="X35" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="X35" s="4" t="s">
-        <v>323</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>30</v>
@@ -5702,7 +5952,7 @@
         <v>8</v>
       </c>
       <c r="AB35" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>23</v>
@@ -5719,23 +5969,31 @@
       <c r="AG35" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AH35" s="18" t="str">
+      <c r="AH35" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="36" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI35" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ35" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46271.929969872683</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="10">
         <v>6</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>17</v>
@@ -5753,34 +6011,34 @@
         <v>65</v>
       </c>
       <c r="L36" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="T36" s="3">
         <v>4</v>
       </c>
       <c r="U36" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="V36" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="V36" s="4" t="s">
+      <c r="X36" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="X36" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="Y36" s="3" t="s">
         <v>30</v>
@@ -5792,28 +6050,36 @@
         <v>7</v>
       </c>
       <c r="AB36" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AD36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AH36" s="18" t="str">
+      <c r="AH36" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="37" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI36" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ36" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46271.935383136573</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="10">
         <v>8</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>17</v>
@@ -5831,7 +6097,7 @@
         <v>65</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>23</v>
@@ -5846,19 +6112,19 @@
         <v>23</v>
       </c>
       <c r="S37" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="T37" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="T37" s="19" t="s">
+      <c r="U37" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="U37" s="4" t="s">
+      <c r="V37" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="V37" s="4" t="s">
+      <c r="X37" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="X37" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="Y37" s="3" t="s">
         <v>30</v>
@@ -5870,7 +6136,7 @@
         <v>6</v>
       </c>
       <c r="AB37" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AC37" s="3" t="s">
         <v>23</v>
@@ -5881,23 +6147,31 @@
       <c r="AF37" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AH37" s="18" t="str">
+      <c r="AH37" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
         <v>SI</v>
       </c>
-    </row>
-    <row r="38" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI37" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ37" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46271.948370185186</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="10">
         <v>8</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>17</v>
@@ -5915,31 +6189,31 @@
         <v>65</v>
       </c>
       <c r="L38" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="T38" s="3">
         <v>4</v>
       </c>
       <c r="U38" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="V38" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="V38" s="4" t="s">
+      <c r="X38" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="X38" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="Y38" s="3" t="s">
         <v>30</v>
@@ -5951,7 +6225,7 @@
         <v>8</v>
       </c>
       <c r="AB38" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AC38" s="3" t="s">
         <v>23</v>
@@ -5962,23 +6236,31 @@
       <c r="AF38" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AH38" s="18" t="str">
+      <c r="AH38" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-</v>
+      </c>
+      <c r="AI38" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ38" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46271.955678379629</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="10">
         <v>7</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>349</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>17</v>
@@ -5996,7 +6278,7 @@
         <v>41</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>23</v>
@@ -6011,22 +6293,22 @@
         <v>23</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T39" s="3">
         <v>3</v>
       </c>
       <c r="U39" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="V39" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="V39" s="4" t="s">
+      <c r="W39" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="W39" s="4" t="s">
+      <c r="X39" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="X39" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="Y39" s="3" t="s">
         <v>30</v>
@@ -6038,7 +6320,7 @@
         <v>5</v>
       </c>
       <c r="AB39" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AC39" s="3" t="s">
         <v>23</v>
@@ -6052,23 +6334,31 @@
       <c r="AF39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AH39" s="18" t="str">
+      <c r="AH39" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-</v>
+      </c>
+      <c r="AI39" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ39" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="40" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46271.963903287033</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="10">
         <v>8</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>17</v>
@@ -6086,7 +6376,7 @@
         <v>41</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>23</v>
@@ -6098,22 +6388,22 @@
         <v>23</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T40" s="3">
         <v>4</v>
       </c>
       <c r="U40" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="V40" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="V40" s="4" t="s">
+      <c r="W40" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="W40" s="4" t="s">
+      <c r="X40" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="X40" s="4" t="s">
-        <v>362</v>
       </c>
       <c r="Y40" s="3" t="s">
         <v>30</v>
@@ -6125,269 +6415,957 @@
         <v>8</v>
       </c>
       <c r="AB40" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="AC40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH40" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI40" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ40" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="41" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46272.725015509262</v>
+      </c>
+      <c r="B41" s="10">
+        <v>9</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="AC40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH40" s="18" t="str">
+      <c r="D41" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T41" s="3">
+        <v>4</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="V41" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="W41" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="X41" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH41" s="15" t="str">
         <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
-        <v/>
+        <v>-</v>
+      </c>
+      <c r="AI41" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ41" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="42" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46273.385448194444</v>
+      </c>
+      <c r="B42" s="10">
+        <v>8</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="T42" s="3">
+        <v>4</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="V42" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="W42" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="X42" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH42" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI42" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ42" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{70787C97-4872-4712-A385-08C9BB7FF0B2}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{0FBC97CF-A34B-4FF2-8658-B94AACF6A010}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{DB483E08-DE1A-4425-BA52-26874C80D595}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{F3BE3203-661B-4B5B-8301-593D478FD790}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{1D17DBAF-9922-4FA8-AC6B-FBEFFE5608E5}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{0784DFDC-F160-4FAF-823F-86734E61FAB1}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{7C3CB6F4-5572-4FF3-89A1-28266A615CC4}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{212A86AA-56A7-423B-990C-3A6344405FFA}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{9A231250-40DC-4CC0-8B53-F65210EB085E}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{7906325E-CD7C-4215-A78A-400EB5A7E1EF}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{3FE5A494-C472-44FC-8CEE-25BD7FC4BEEC}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{311FD07B-4680-4252-924E-0A80D14D2B6D}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{3444EF37-3541-42B8-BA51-C4416A58A2C0}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{62192F0D-8807-4C8C-93C6-B76D6531DF0D}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{638ACFC6-286B-4023-BE42-F6E19FCDCB40}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{66C81DE4-DF55-458E-884D-41C12E5EFF9C}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{C95617EA-9487-45FC-AF6E-A78FF4D366C8}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{3B6EE264-F28F-408A-B606-C987E07C8E71}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{34EF51DA-5977-4AB3-A1DD-4987710D9F1A}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{14A3E8B0-6B44-4864-A87A-8FD235984FC3}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{BEBAD603-7535-46FE-8E47-06DB7E9551E2}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{4BC07AD9-8131-4099-9A76-7598FADB87F0}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{06FE792C-B485-49D6-84A4-F66EA6778C62}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{BD513C53-19AC-4C64-918E-2E5FD5235F71}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{7884F252-4015-4405-96E9-72F2CC5D4A55}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{8FD0B193-BABA-4B6D-B685-34C08658FBF6}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{B97CA2BF-5501-4E48-B5D1-9143E927E70C}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{8534A5D0-F1C9-4ED0-806B-D1EF71790332}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{30BBE415-F826-40CA-9C5A-FE0A8BD726AA}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{88F7B35B-ECA9-46A6-844E-CA1F08CCD3D6}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{24A5185E-D014-4571-B146-26D6ABBC2D82}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{B3F9F8DD-1FA8-4882-8B36-8D72A203C6D6}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{B16F70D9-1288-4074-9FAB-E41A4B85D530}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{1DC07FE4-AAAD-4E79-8EA1-6D3FEAD15465}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{640B2DFA-1E33-4065-A0EC-8CF5FA526933}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{87CF7082-4E2C-4DF8-81FB-9CF9A07BAAE0}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{0DAE576E-2744-4A38-B6ED-6FDDCCE1C194}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{A8901A9E-CE22-4B31-95CB-8069ED1A2308}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{4246084E-C696-4DEC-B5A6-472581F5BAF3}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{2D4772E8-2ACC-4DAF-A4CE-0E797969B115}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{3D8DB65E-DA51-4104-812C-82801CE526EC}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{453C5CBF-0AC5-4C99-8147-C208797B4E3C}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{A46F4F60-E3E2-4D3F-AF82-93ADAB07AF4D}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{97850B8D-66E2-4015-AE24-2950CF8B60CE}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{FB2A3267-0D1A-4C0E-B899-6E4874732613}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{F68A167E-A87B-494A-AF51-21D21C86A407}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{110D2EF0-2F40-4730-BABE-92683C173640}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{59A3CF8A-348A-4D6F-AA96-5C3DB7E59024}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{78924957-D18A-4DA4-AE98-01E41165E3E3}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{9869F478-F457-4C22-BCB6-2D5963EB8773}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{AA3F78C5-67F6-4702-9C94-1E906482968A}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{C57856B1-7A7C-4159-9ABD-78185636D0EF}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{BD9347BE-92EA-4817-ADC9-70B5300669D4}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{E08CDDBF-C36A-4121-AE46-B12E28F4B39B}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{7BED1DEB-A492-41B4-9364-2350233BB9E5}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{82A92D6E-66F9-4285-B8BC-BAA203616AAD}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{810F6F86-6EF7-49A5-8E0C-044C2B71F4AB}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{62FA60A2-4C88-4398-BA9A-7C74F7900808}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{3BBDBA11-130F-4665-BF0D-564C01178AD3}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{F0C435CC-5821-430B-BB3C-15BC895FF3DB}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{99B6BE78-D3DB-4101-8E49-30D7497B291C}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{69EC841B-7680-4AEF-844A-21645382CF9E}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{A5E42D09-90FE-4C44-A3D6-73259CA943E2}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{D6E0A55A-D8E0-4EBF-9C3D-BD55BB19EE20}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{E010B529-3BBF-4654-A2D6-9B9B56529515}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{363AB0FC-F5FE-4863-93AE-1893E2DBEEF3}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{A5A0839E-3C85-4B97-9BD5-70BBDA1275D6}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{D3C90D1D-6300-42DE-BEC7-A50BA877A629}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{F077CE4F-F922-4EB7-B3F9-A3F1634F36E7}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{8C268920-51EB-41AA-A6F1-F6CD547DE958}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{FBE75348-DE69-48F2-8151-3C262021FB92}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{C30F1092-FFEF-429B-B3D1-8D3759B07C0F}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{D8526710-207E-4610-BAA1-942ADA93C668}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{1817C61A-BAA8-47A8-96A6-707A65F2D222}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{34BF8E9A-17E5-4507-AF80-BCC3A481E391}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{D1BD2E71-AF9D-4194-AD3E-C2CCFFBC687C}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{88D63A34-CD64-4B65-A01D-CECEA660E2AB}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{7DB6245B-EFD6-4369-A083-A866D4D3F19C}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{A014D0D3-65F0-49D4-8764-2D7229593D2F}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{583E4916-A7C7-4F48-A458-929299B787E4}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{1C1F7DA8-58A3-4228-8030-CBD758D0AD97}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{55F127EA-34A6-4726-9716-1B74F7839D96}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{626D3CFA-E881-4B8A-A614-36BDE5EF24AC}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{7BB20C1C-CF78-4961-B2F7-AA4E621F78BD}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{07C5E6E9-79C8-4A2C-ADCA-A4EB335E4670}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{E4404530-7429-4A5C-AE36-221CE76E8F42}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{85B65970-5A29-498C-AA66-2D36F5A9D8A1}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{BB2A4088-560F-4D25-A1C6-B53D6D6E6857}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{F8DDD0F8-429C-48B1-98CC-A735EB232876}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{9278F556-4012-45B9-8569-6CC34A6D764B}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{C03530B6-85F7-4CF5-8371-D0BF2B4B6E7C}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{94825110-463D-4E7B-A771-BAD900A80815}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{4FA438BA-E3FC-40D7-BB3A-F1CB295B835F}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{005AC1F2-23BF-4E47-ADC5-EFB00833CF9B}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{1C4040DB-79A4-4E82-A70E-534DA43E7B81}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{4673724B-96AB-4CAA-B338-7B31D09BAE5C}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{D8851976-D8B2-4205-9C05-96D8D41223CE}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{692A1774-3284-4E97-A0B8-A584B3FB3040}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{88706A56-B628-4597-B650-147ABDF9B4CD}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{79A3AE9B-5111-4E10-9F31-714C94638E29}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{530E1E9B-C95F-4EA6-B64C-850052654EC5}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{6C4F23BD-6711-4CF2-9505-26399987766F}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{872766A9-5621-4E53-978C-B66FD9919342}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{BAF0534C-0181-41D1-AC8F-4BD0BB958E5C}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{AD80B5C1-D55E-41E0-B3B4-79A1FECD4471}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{5174572A-29F5-4224-AF7B-A2C04BAC4778}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{4F1BFA16-6129-4B05-A43C-F0E9FC9872B0}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{4B1B8EB0-50C8-4D21-8577-ED8EDC7C2182}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{D37EE459-B57B-4ED6-B8EE-B0E6B0B89862}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{E8EFE3EF-EDB0-4757-9D81-17A1DAFB4FB6}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{D5334C99-3A9A-4FB0-A948-90735319C17D}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{4638D607-E39C-4B19-8D47-CE0DBA229E72}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{7BBB0ABD-5F32-49B8-AC65-109950883457}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{66C18F5B-1615-4446-9E81-C53D7C943F5E}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{EEBB466F-85DF-41E0-97FA-19C4DEE47226}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{BEC46DB5-3DFF-4F94-AAFE-B047549BFA7C}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{3D134619-2A60-4C0A-B393-7D3480AD16A1}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{CA242DE5-9271-4EDF-9522-66B5F072EBB6}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{65CC60B3-1F32-4B04-B7AB-5F86B4B1B0FA}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{3F1FA653-973A-4EAD-90E9-55F96932A347}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{D2ACDA8B-8064-49CE-B425-3039A83782E9}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{DA906C18-681F-4AF4-9F10-E1378A15209B}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{2BA2F78E-6B26-48FE-845E-0E7ECA39E071}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{8877B922-307F-4E51-A6E9-51A3623E9B4A}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{14D088ED-02B1-4FB2-8083-1EAD4054E5BF}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{5583EA92-1DC6-401A-84C1-86B79170B7C9}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{B1A62E79-86A6-4138-ADAC-7950C6028124}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{5BCC5DC6-6B62-4600-A4E2-44C0A6715B78}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{B765028D-25EE-47F7-A7D8-5CA82426BA8B}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{FD11E3E4-8167-4DD5-A214-542270947460}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{D051C57B-BE45-4E4A-884E-5FCF3C58A91A}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{1E7D7753-3130-4409-9351-EA4D0842B4B9}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{06EBA1D9-839A-4338-8FB1-EC0014547C2E}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{D2C72A92-A1E8-44C6-A1D3-08030FADAED5}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{58BAB32F-5B9F-4959-9141-EAA5A18D2150}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{79990874-0D35-4D3A-A81F-FB3EDDF5CD13}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{D67D23E4-D107-4C47-A6C2-0AF1A7AD2F8D}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{893D3346-B71D-4F39-A954-FFA8E77A41A7}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{FA24DAC5-79BF-40B8-902A-663247C9BA62}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{DD93F2AC-48FD-46F6-8BBB-2F8BA3BB18F3}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{AA604D2E-5BF0-4E75-BE39-AEF7C6FEC810}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{EA732884-C5B8-4CD4-BB2C-3E68D3864E0E}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{23144703-70A5-4665-AFF0-D05777959C8C}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{27EF0068-712C-48C6-9085-1B1565D45379}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{4A3E215B-531E-4DA4-ACF5-75FF84815439}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{38B3022E-01F4-4537-BEB7-991B92CB1C1D}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{6FA972DC-3F17-431A-9DDE-DAF40A6F3B17}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{2EA66452-4F78-4F32-8C32-4015CE383EDB}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{9255DEB3-7859-4530-8D8E-7FFFDE88F51C}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{8EA45CC4-FB01-4319-8FE7-BBE3A8F5ACFF}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{8828C835-27D2-4899-98BF-844F161467F4}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{67914B03-A309-46B3-8F69-6DCFECE48319}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{B6EB4B69-D657-4339-A264-9EBBC0966954}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{545B04D9-363E-4BEE-BEE7-E294C306C587}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{DD5ACD82-0BE8-404D-8709-61C44254B672}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{D2C80122-7971-4A04-85B5-86DAD4F32F4D}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{E48C3B82-93E9-4F4F-B81F-5D69013A0A4B}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{53930DF6-9755-4EB3-AA78-D12B96411C9F}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{9F6F9AA2-290B-4769-AEBA-59B4975A9480}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{D569153D-34BA-4044-9121-03137FB37226}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{A41062F8-ED38-4792-B7FF-AC2ED6A66A48}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{65A85253-311B-4115-BE52-E22AF8A85334}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{363DB1A0-7366-4EC3-B130-09ED4CC8998C}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{9F945503-3DA0-4D11-8387-97D7B885CB95}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{595A77F0-31CC-43C4-BA44-12A5C34C061E}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{FA2E1F29-F5F1-407D-B292-1B892BA4B7A7}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{657D2C4D-323C-4020-A8C3-4A87BBD2B876}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{A4144407-ADF2-4062-B84B-248E1D9C19A7}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{09059C5A-F53C-4FFE-BF0A-4509B126220C}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{79832B2B-EC47-4B7A-8A99-B482708AB98B}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{CD95EBE8-D9F9-4163-A2D3-0D481CB4C279}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{AE994840-B38C-4CDA-875D-E7B0B9555EDA}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{86C9D3AB-424B-4F27-8F98-975E01E97D2B}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{CB7FC036-8423-4D38-94C6-FBD696E27007}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{64AEFB8E-F31F-4150-A821-41EC0913801D}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{4AF3A949-39F0-4B39-AF73-FE7109C4AE77}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{7D19E6A5-65FD-42D3-A9C4-59B3C064189A}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{0EFB356F-1ED5-48AA-BCE9-E05EE5223341}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{DD6E1835-08D7-4CAE-80E9-6B34BBE13CCE}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{58D4B17F-1574-4D9B-BC99-4B7260F47067}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{55FD7077-29BD-47C8-92F2-5D1D32F3DCA6}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{4C238566-9A5B-4E2F-9F46-09527C656D2D}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{40D214E6-F97F-46A1-A955-437A48A0F707}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{91234A49-85DF-4935-8D8A-0F177DC67610}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{DBBAF817-6C8A-419B-80AA-E17E241A1408}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{E28BE88C-B6BF-46DC-B03D-208D9FC788B2}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{7F7A18BA-A257-47EF-AB69-FBB5766AEC89}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{1997C5CD-D08B-4DB6-A3B6-6775002CD2A6}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{FB21800C-F69C-4E99-9DC9-7569BD69B062}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{4878BEF9-8862-4B7E-82DC-5EF40D3097CF}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{8584E850-F45E-4910-B337-E0CFAE688259}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{4A7E849C-725F-417D-8668-F7641682EDB6}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{DC353ED2-2BDD-4ED7-B0C8-89C00AC7940A}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{F8C0C4B2-30D0-453A-9319-1FB2B901CC93}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{8257713B-E450-4FBD-A67C-CD37110AAF30}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{BF280434-A5DD-4D32-9F7B-28772A8DEEEB}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{8D180FD4-5EDF-4A44-B236-F7A7BFF2382D}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{7CD6BE83-BDE8-4BFE-A0FA-F8261F274D16}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{B322976D-4FAE-4996-B6FD-7B4A90318FF6}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{109E6270-75C4-49E9-B092-FD479EF061ED}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{3045C563-0F0F-4401-BAFE-ED8E447DFE01}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{86D87D32-CB47-448F-ACA2-D138493ADD23}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{26237F25-40CF-45CA-BFDD-6490B70F493F}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{9B85A5FD-8F85-43B4-A146-6E35581AEC7E}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{98F1A1CE-3684-4850-955E-51DF8D0E88D7}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{BDC4F305-7211-4C35-82EF-6D85BCAFD484}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{75953646-217B-4244-B660-638143FD1A48}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{B94AF63C-273F-4FB8-B61F-2BDD7E539214}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{3B0BD0A0-5BBC-4E86-AF9B-ADCCCE05BFD6}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{3218345E-0CA2-4C1A-B71C-F150AA9C8C0A}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{7CFA2044-EDBC-4A52-A3FF-56A1F41DA994}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{0ACF44D4-56DF-47D9-8657-F33CA555A0D1}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{EAB0D2B8-B3EF-4EB7-AC07-B39FA717CB81}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{F50328CA-A88E-495F-A204-BD693B904478}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{037BC719-702D-42E4-82C1-3FD547E8F326}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{C5CB90E3-1F27-46C5-94D3-8F793B56474E}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{4FDEB653-6C2C-4B37-B2FC-E65AD2DA7FA5}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{54AA03FA-085D-407B-A871-BE279FB67E02}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{E65C2086-0E78-4A72-AFA2-C0DC990D42DD}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{E96B1C75-C7D4-4CD4-B006-1D1E90D0F35C}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{12B8A92F-2C9C-4810-A8E0-055E5F29DFAD}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{8844C06B-79CB-486C-A38B-6D17C9B72DF3}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{A1CBDC3E-EE0A-4834-8AFC-C2FA6DD94405}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{5DFE2C18-EF7C-44D9-B563-50F4791E3872}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{F960EC81-247A-4083-8426-0C17D6C039F9}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{1CE802F8-CD85-4342-92FB-1AB8F1FA4ED1}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{22233F05-D9D9-44FE-9739-346F1691E627}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{BEFEA8A1-04FA-420E-A6F9-6BBDCD8F22DE}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{ADDF831D-843A-487B-AE33-691AEF23C31B}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{1D311652-D068-4667-A041-F5F67193A052}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{EE6B16F5-59C0-4F60-840F-6326AA811E78}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{C0408603-935C-47B8-9F89-96D3416668E5}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{1570869D-9315-4788-8392-F977246F2C23}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{58D90039-598E-4FE0-B213-102336B3DE41}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{F8168A8B-4ECF-4A6A-BD38-D4FF28B1475A}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{C5A42525-7F5E-40AE-BD5E-EF08B0251524}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{FF13EF06-C83E-4C3F-AD61-BA51930E47CC}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{FB82ED5C-54EB-4D98-B58D-8032A0956AAF}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{711E0205-CBA2-44B8-83EB-538A7791D3DF}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{33B9F123-331A-43B4-B2FB-33B25C833C00}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{9B7455C1-5AF0-4B3C-A10F-DB47E420E52B}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{1CD4EF3F-38E1-45C3-A1F2-F72254CCAF0A}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{D7DDDAAE-4D26-4153-9C9A-A48638D508CF}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{6EA49552-503A-4306-B5E4-F0E3FC7372A2}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{3C7FCDC3-500F-4281-A912-5083B181EFF2}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{CEC20A54-C47B-4537-82DB-BB8E9D0BB108}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{6DBD43B8-F6EE-4935-95BC-3AA34DB7D8FF}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{A83142ED-5ECA-41ED-A6E4-914230AE0DA4}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{9BF8FFEC-1E1C-4A5E-8749-6355A12133EF}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{7AA812E7-2037-43CE-99CF-76752415845A}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{AC1988A9-50C8-405F-B817-1284C5321B12}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{EAD56A16-6EBD-4E5B-9BBA-8888161FB3A7}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{AFF20957-3628-4233-86F3-1C488D9433D3}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{C47C0951-C8EF-4AC8-AD40-CCCF002C0122}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{7F712A21-C3AA-4117-ACD9-E4B6ADFB7F9E}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{CD23EE85-A779-455D-8638-6BCC56C86FD7}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{05DAC071-F733-4CAC-BEFE-8967A7C9EA45}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{43564A07-A550-4696-9E05-96D3E188BA1B}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{E2FCC100-5B83-4658-9B67-189689023395}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{72EC7CD4-73CA-49AF-9265-5FB7429B0F71}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{96CBFD70-D68D-4C6B-A0B0-FFB54164CDA4}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{093A8624-8A2A-4C70-82EF-8EF3A52EBAE9}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{2860B91F-8711-4761-A9F9-8320917376B6}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{8884C231-C6CA-4A7D-BB09-A6256276EC3F}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{85D582FF-99B8-4424-B14A-FE501E51AC19}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{15F676B5-A6AA-4A87-ACB8-BDD7777A1691}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{705AAF17-9235-4903-AE58-79DCDD2D6645}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{BA4F1031-7F1D-4A44-BCEE-D9AA369BC5A4}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{1B8E6436-D951-4D63-A15F-140B3B1B9A8D}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{F17EA83F-A1F5-4EED-8DA3-464E01A5D1F4}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{1C4A90BB-95CE-4CEB-A324-B55C42C17D0E}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{D1A60ED8-5D46-44F7-AF69-D08F46715F88}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{A27DC0EA-D8EF-4C21-8FA9-FD7CF4731146}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{8FA0DD77-EC99-4A10-BB3D-09D98686A0BD}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{748B80ED-6E18-440D-90FC-D087AC9DEE04}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{068737BE-E333-4A7E-83BC-24AA927EF639}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{0C039852-8D48-445E-95D2-492A8138C514}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{A93B4204-B221-44A8-928D-B49255EE44EA}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{30B6D75F-E994-41D8-88BF-21CC983A53BD}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{9220ECE7-689E-4288-AF0A-283C3B9B6CE4}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{4FEC783E-5B0C-47C1-B29F-2239F679B886}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{FCD28C38-DDC2-4317-9B4A-61B1B6667A93}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{7EEE5836-54D7-44D4-8C7F-8040A05FE654}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{6C084EF1-018F-4704-937B-DEB5E178B5BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId139"/>
+    <tablePart r:id="rId147"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B86AD5-214A-4E29-8C3C-D28012B13A5F}">
-  <dimension ref="B1:D9"/>
+  <dimension ref="B1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.6640625" customWidth="1"/>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C1" s="10" t="s">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="C18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
+      <c r="C22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
+      <c r="C25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E27" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>23</v>
+      <c r="C31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:D39" xr:uid="{77B86AD5-214A-4E29-8C3C-D28012B13A5F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F695084F-9F37-4CBC-BE5A-3FC8735165E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21039437-7C3F-457A-A448-9E7C5C6E0A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="385">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1370,6 +1370,27 @@
   </si>
   <si>
     <t>Solo falta utilizar ambos one click</t>
+  </si>
+  <si>
+    <t>1-3NPLUJ4C</t>
+  </si>
+  <si>
+    <t>Av costanera sur 4832, Quinta Normal</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1EUNQ_WLp7Z_eaFBr4GxAOwQf2hohRZLu</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1mQ-GjTcSvbY8EU1ZE7qg5Wn1xToM9WZ5</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ff7gndt56j206swD5de6hpheDUPgwmmI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Fq_WRrGKyUsT7_5INBoXsvGn7V7Xu18W</t>
+  </si>
+  <si>
+    <t>No utiliza one click</t>
   </si>
 </sst>
 </file>
@@ -1672,6 +1693,60 @@
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2050,60 +2125,6 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <name val="Roboto"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
@@ -2222,43 +2243,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ42" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ42" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ43" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ43" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="21"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="19"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="32"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="18"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="30"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="29"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="13"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="12"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="10"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="9"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="8"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="28"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="7"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="2"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="1"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="27"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="0"/>
-    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="26"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="25" dataCellStyle="Bueno">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="28" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
@@ -2473,7 +2494,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ42"/>
+  <dimension ref="A1:AJ43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -6650,159 +6671,261 @@
         <v>-</v>
       </c>
     </row>
+    <row r="43" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46273.679735358797</v>
+      </c>
+      <c r="B43" s="10">
+        <v>8</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T43" s="3">
+        <v>4</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="V43" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="W43" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="X43" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH43" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI43" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ43" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{FA24DAC5-79BF-40B8-902A-663247C9BA62}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{DD93F2AC-48FD-46F6-8BBB-2F8BA3BB18F3}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{AA604D2E-5BF0-4E75-BE39-AEF7C6FEC810}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{EA732884-C5B8-4CD4-BB2C-3E68D3864E0E}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{23144703-70A5-4665-AFF0-D05777959C8C}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{27EF0068-712C-48C6-9085-1B1565D45379}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{4A3E215B-531E-4DA4-ACF5-75FF84815439}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{38B3022E-01F4-4537-BEB7-991B92CB1C1D}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{6FA972DC-3F17-431A-9DDE-DAF40A6F3B17}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{2EA66452-4F78-4F32-8C32-4015CE383EDB}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{9255DEB3-7859-4530-8D8E-7FFFDE88F51C}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{8EA45CC4-FB01-4319-8FE7-BBE3A8F5ACFF}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{8828C835-27D2-4899-98BF-844F161467F4}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{67914B03-A309-46B3-8F69-6DCFECE48319}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{B6EB4B69-D657-4339-A264-9EBBC0966954}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{545B04D9-363E-4BEE-BEE7-E294C306C587}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{DD5ACD82-0BE8-404D-8709-61C44254B672}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{D2C80122-7971-4A04-85B5-86DAD4F32F4D}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{E48C3B82-93E9-4F4F-B81F-5D69013A0A4B}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{53930DF6-9755-4EB3-AA78-D12B96411C9F}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{9F6F9AA2-290B-4769-AEBA-59B4975A9480}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{D569153D-34BA-4044-9121-03137FB37226}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{A41062F8-ED38-4792-B7FF-AC2ED6A66A48}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{65A85253-311B-4115-BE52-E22AF8A85334}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{363DB1A0-7366-4EC3-B130-09ED4CC8998C}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{9F945503-3DA0-4D11-8387-97D7B885CB95}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{595A77F0-31CC-43C4-BA44-12A5C34C061E}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{FA2E1F29-F5F1-407D-B292-1B892BA4B7A7}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{657D2C4D-323C-4020-A8C3-4A87BBD2B876}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{A4144407-ADF2-4062-B84B-248E1D9C19A7}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{09059C5A-F53C-4FFE-BF0A-4509B126220C}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{79832B2B-EC47-4B7A-8A99-B482708AB98B}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{CD95EBE8-D9F9-4163-A2D3-0D481CB4C279}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{AE994840-B38C-4CDA-875D-E7B0B9555EDA}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{86C9D3AB-424B-4F27-8F98-975E01E97D2B}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{CB7FC036-8423-4D38-94C6-FBD696E27007}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{64AEFB8E-F31F-4150-A821-41EC0913801D}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{4AF3A949-39F0-4B39-AF73-FE7109C4AE77}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{7D19E6A5-65FD-42D3-A9C4-59B3C064189A}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{0EFB356F-1ED5-48AA-BCE9-E05EE5223341}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{DD6E1835-08D7-4CAE-80E9-6B34BBE13CCE}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{58D4B17F-1574-4D9B-BC99-4B7260F47067}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{55FD7077-29BD-47C8-92F2-5D1D32F3DCA6}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{4C238566-9A5B-4E2F-9F46-09527C656D2D}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{40D214E6-F97F-46A1-A955-437A48A0F707}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{91234A49-85DF-4935-8D8A-0F177DC67610}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{DBBAF817-6C8A-419B-80AA-E17E241A1408}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{E28BE88C-B6BF-46DC-B03D-208D9FC788B2}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{7F7A18BA-A257-47EF-AB69-FBB5766AEC89}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{1997C5CD-D08B-4DB6-A3B6-6775002CD2A6}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{FB21800C-F69C-4E99-9DC9-7569BD69B062}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{4878BEF9-8862-4B7E-82DC-5EF40D3097CF}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{8584E850-F45E-4910-B337-E0CFAE688259}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{4A7E849C-725F-417D-8668-F7641682EDB6}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{DC353ED2-2BDD-4ED7-B0C8-89C00AC7940A}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{F8C0C4B2-30D0-453A-9319-1FB2B901CC93}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{8257713B-E450-4FBD-A67C-CD37110AAF30}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{BF280434-A5DD-4D32-9F7B-28772A8DEEEB}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{8D180FD4-5EDF-4A44-B236-F7A7BFF2382D}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{7CD6BE83-BDE8-4BFE-A0FA-F8261F274D16}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{B322976D-4FAE-4996-B6FD-7B4A90318FF6}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{109E6270-75C4-49E9-B092-FD479EF061ED}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{3045C563-0F0F-4401-BAFE-ED8E447DFE01}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{86D87D32-CB47-448F-ACA2-D138493ADD23}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{26237F25-40CF-45CA-BFDD-6490B70F493F}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{9B85A5FD-8F85-43B4-A146-6E35581AEC7E}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{98F1A1CE-3684-4850-955E-51DF8D0E88D7}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{BDC4F305-7211-4C35-82EF-6D85BCAFD484}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{75953646-217B-4244-B660-638143FD1A48}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{B94AF63C-273F-4FB8-B61F-2BDD7E539214}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{3B0BD0A0-5BBC-4E86-AF9B-ADCCCE05BFD6}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{3218345E-0CA2-4C1A-B71C-F150AA9C8C0A}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{7CFA2044-EDBC-4A52-A3FF-56A1F41DA994}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{0ACF44D4-56DF-47D9-8657-F33CA555A0D1}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{EAB0D2B8-B3EF-4EB7-AC07-B39FA717CB81}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{F50328CA-A88E-495F-A204-BD693B904478}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{037BC719-702D-42E4-82C1-3FD547E8F326}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{C5CB90E3-1F27-46C5-94D3-8F793B56474E}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{4FDEB653-6C2C-4B37-B2FC-E65AD2DA7FA5}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{54AA03FA-085D-407B-A871-BE279FB67E02}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{E65C2086-0E78-4A72-AFA2-C0DC990D42DD}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{E96B1C75-C7D4-4CD4-B006-1D1E90D0F35C}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{12B8A92F-2C9C-4810-A8E0-055E5F29DFAD}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{8844C06B-79CB-486C-A38B-6D17C9B72DF3}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{A1CBDC3E-EE0A-4834-8AFC-C2FA6DD94405}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{5DFE2C18-EF7C-44D9-B563-50F4791E3872}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{F960EC81-247A-4083-8426-0C17D6C039F9}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{1CE802F8-CD85-4342-92FB-1AB8F1FA4ED1}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{22233F05-D9D9-44FE-9739-346F1691E627}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{BEFEA8A1-04FA-420E-A6F9-6BBDCD8F22DE}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{ADDF831D-843A-487B-AE33-691AEF23C31B}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{1D311652-D068-4667-A041-F5F67193A052}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{EE6B16F5-59C0-4F60-840F-6326AA811E78}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{C0408603-935C-47B8-9F89-96D3416668E5}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{1570869D-9315-4788-8392-F977246F2C23}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{58D90039-598E-4FE0-B213-102336B3DE41}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{F8168A8B-4ECF-4A6A-BD38-D4FF28B1475A}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{C5A42525-7F5E-40AE-BD5E-EF08B0251524}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{FF13EF06-C83E-4C3F-AD61-BA51930E47CC}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{FB82ED5C-54EB-4D98-B58D-8032A0956AAF}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{711E0205-CBA2-44B8-83EB-538A7791D3DF}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{33B9F123-331A-43B4-B2FB-33B25C833C00}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{9B7455C1-5AF0-4B3C-A10F-DB47E420E52B}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{1CD4EF3F-38E1-45C3-A1F2-F72254CCAF0A}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{D7DDDAAE-4D26-4153-9C9A-A48638D508CF}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{6EA49552-503A-4306-B5E4-F0E3FC7372A2}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{3C7FCDC3-500F-4281-A912-5083B181EFF2}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{CEC20A54-C47B-4537-82DB-BB8E9D0BB108}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{6DBD43B8-F6EE-4935-95BC-3AA34DB7D8FF}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{A83142ED-5ECA-41ED-A6E4-914230AE0DA4}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{9BF8FFEC-1E1C-4A5E-8749-6355A12133EF}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{7AA812E7-2037-43CE-99CF-76752415845A}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{AC1988A9-50C8-405F-B817-1284C5321B12}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{EAD56A16-6EBD-4E5B-9BBA-8888161FB3A7}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{AFF20957-3628-4233-86F3-1C488D9433D3}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{C47C0951-C8EF-4AC8-AD40-CCCF002C0122}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{7F712A21-C3AA-4117-ACD9-E4B6ADFB7F9E}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{CD23EE85-A779-455D-8638-6BCC56C86FD7}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{05DAC071-F733-4CAC-BEFE-8967A7C9EA45}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{43564A07-A550-4696-9E05-96D3E188BA1B}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{E2FCC100-5B83-4658-9B67-189689023395}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{72EC7CD4-73CA-49AF-9265-5FB7429B0F71}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{96CBFD70-D68D-4C6B-A0B0-FFB54164CDA4}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{093A8624-8A2A-4C70-82EF-8EF3A52EBAE9}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{2860B91F-8711-4761-A9F9-8320917376B6}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{8884C231-C6CA-4A7D-BB09-A6256276EC3F}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{85D582FF-99B8-4424-B14A-FE501E51AC19}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{15F676B5-A6AA-4A87-ACB8-BDD7777A1691}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{705AAF17-9235-4903-AE58-79DCDD2D6645}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{BA4F1031-7F1D-4A44-BCEE-D9AA369BC5A4}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{1B8E6436-D951-4D63-A15F-140B3B1B9A8D}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{F17EA83F-A1F5-4EED-8DA3-464E01A5D1F4}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{1C4A90BB-95CE-4CEB-A324-B55C42C17D0E}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{D1A60ED8-5D46-44F7-AF69-D08F46715F88}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{A27DC0EA-D8EF-4C21-8FA9-FD7CF4731146}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{8FA0DD77-EC99-4A10-BB3D-09D98686A0BD}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{748B80ED-6E18-440D-90FC-D087AC9DEE04}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{068737BE-E333-4A7E-83BC-24AA927EF639}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{0C039852-8D48-445E-95D2-492A8138C514}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{A93B4204-B221-44A8-928D-B49255EE44EA}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{30B6D75F-E994-41D8-88BF-21CC983A53BD}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{9220ECE7-689E-4288-AF0A-283C3B9B6CE4}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{4FEC783E-5B0C-47C1-B29F-2239F679B886}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{FCD28C38-DDC2-4317-9B4A-61B1B6667A93}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{7EEE5836-54D7-44D4-8C7F-8040A05FE654}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{6C084EF1-018F-4704-937B-DEB5E178B5BF}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{5F254211-F2B7-4192-A99C-FA12631F1DCA}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{D999DC53-AFBA-4024-94D9-4343B0424687}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{5BC54CAC-3C30-4AE9-9C6D-883C397905BA}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{8A7D9812-F621-4886-9D0C-3D33A6AC09AB}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{B0D8831A-6C36-4DED-AFA5-86B0EF0C8406}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{82A1A44F-12DD-449F-A338-DC35E0DCAF3C}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{66E85A3E-19FC-4912-8F94-372C14DACDAE}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{052B7706-53AB-4D60-AF09-B30B0B755DE2}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{AF7C3B0F-6CDE-4FBF-8C7B-4A839AFD79DC}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{6DEE0415-9F35-43FB-B27F-40318E90EBB0}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{299D698C-7DD2-40A9-BD83-EA52EE3231DE}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{BBCA4C60-30E2-4583-9389-79C5AF3CA416}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{EBC420B7-D1FA-40E6-A198-D075FA1649EB}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{507DD8FA-8EDA-4993-9E5B-5189A32D424B}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{7D690290-DC2A-4BF9-B0C5-88998BBABBBB}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{547DF65E-28B8-4BBA-9A90-8982EC100970}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{68074B07-C458-48AC-969B-7CC40E55704F}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{B273B0F3-4EDC-4110-8866-3246552CFDD8}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{12B2B75B-F72A-4A56-9EB7-EF0DD2E40773}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{E27FB2C3-76CA-4B4F-9DDF-384AFB78C329}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{E8CA8A60-0184-47AE-A344-EE331D8EF526}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{8CEC6C17-EA0D-41CF-BD38-ED89B5CDE55E}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{D928947D-4627-4B81-AB2F-12BD773F3EF0}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{E623AFCB-67A6-47ED-9A78-DC7B525A1E9A}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{EF0C84F1-BAFB-48B1-BE03-55815DCF221D}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{322A9CF4-298E-41C6-8D40-BC08B5CE6E8A}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{E17032A1-CFB5-4AB6-99C1-1874A3508782}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{39541214-9D4C-4819-8A48-AE1DD79B00B3}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{EFB6FAFE-F11F-4D6E-AADD-EE382C0D1DB5}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{D988AAC9-9129-40A3-B5E0-625C03CB9AF0}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{2000B902-6097-4820-A3C2-54F49651284F}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{99B77298-655C-4D1B-B2AE-665D49E4D07F}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{3C8ECAD3-0D75-400C-B44D-DFF18D144919}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{198F14E6-9FC0-4F0A-8E05-790A42292AED}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{E0F1D95D-1BE9-4491-8739-46022B9FE99B}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{2A5AA804-0CDC-47EC-81F8-C4B5F0DFB620}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{96EEFAD7-CF8B-44E0-81D6-A472E76854C1}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{A8111485-F280-4EC1-AEA7-205416319816}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{0695E8A4-7A81-4777-8A7A-CB16C7219FE3}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{8D1FABA8-CF06-4D94-A50D-29D50D404C2E}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{DC900745-BF32-4458-8A02-49B82263685A}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{76B079D9-A72B-444B-A4C9-9FCEA069F2D3}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{C5253A3B-0827-49EE-8FF1-6D7DAC0217D9}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{6D4DF2C6-7188-4143-B5E7-D2502949A650}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{C51950B2-E420-4A32-BB63-89225BBC76AD}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{097D967C-3F6D-4727-8BA9-6A37B111AF91}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{A280732E-36CE-4F25-AD94-DB4FC2E10CF6}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{D0CFF362-761B-48C0-871E-C12184F8339E}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{F2B9E9EE-6133-4068-AB7D-3D1EDBC2C22B}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{46CA7A45-9CA4-4626-BA3A-381F7930C7AD}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{42BE30D1-2F5B-418F-8495-2E38353D2AA7}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{7CE77D46-0023-469C-8E8B-75674ED3538A}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{064269DD-3443-4254-99B5-C3FECA0CA579}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{03AD4640-53E6-4008-BAFB-B3F037F2644C}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{374D9E4C-7963-48EB-8AA4-6A26E8A11B4E}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{B4AE9A98-32AF-4B43-83A7-E0133D8415FC}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{247CF6CF-6681-4E76-86B1-5F98E25ED6F2}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{6B5A6079-7158-4B4A-BF06-F0A06F2A4F70}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{5B747CB5-C5D3-4BEE-8E6A-6743F6D8E5CC}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{6A309DD9-CF17-45CC-983F-F683CAEE58A1}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{D5E138EC-07E9-41F5-9AAF-5239A268A225}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{241423D1-7707-4183-B8D8-1D3889C03BA5}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{9A981A24-03C2-469A-A4DD-27AD9CB91D42}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{9EA09D93-43AA-4673-9375-6CCEC1B0CE79}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{69C878CD-1B16-4A90-A5B5-F1326F1C7ECF}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{9F3DA76B-8C30-4F08-B5FF-09D258F147F6}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{1E10B9E4-D03C-4A50-AF66-D06EDF3D73E5}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{F6C81866-1CCA-4642-B52C-2ED48808EE6A}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{18FE4689-89A4-4170-BD36-82AD238F8316}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{67BA256B-ADAF-4104-955E-90DD4D4CA3D6}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{7CCFAB91-63B8-480A-A3F0-0AA83A414AE3}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{557E32B1-E258-49E1-AEA8-9FECC7EA8737}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{F5BF5EA7-3E4A-4A77-8BFB-AE6AA062A549}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{0F9E754E-B867-4E48-8FF9-B730A3342C8A}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{1DA2C18F-93EF-470E-80A7-953BAE8150CA}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{D57266DF-4EDB-4718-9BCF-F76C498B5ACE}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{11E5CA26-1793-452D-A4E2-E407B929F860}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{1AEFF898-381E-4401-8B9C-8EFFE4FB011B}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{786231F9-3F8A-4339-8669-D482DC181878}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{64B3E192-7256-4248-9D80-484017E6AE2D}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{F7E4824F-54BA-416D-924F-3B52833F9171}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{DB39FD18-04E4-4F72-87C1-00539C728B80}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{4F208D31-D45C-4448-8E6E-9AC16A8DC595}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{3F0A040F-825D-4938-97EC-9AB8EE9751DF}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{A32D45CC-352C-4B5D-AF6D-7C999D47CA76}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{8301C53B-565D-47B4-A6DA-9FA689CF06CF}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{85B98E01-EA22-405C-82A6-4B2E2C2F7C55}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{904B4E83-81C5-4848-BCF5-AEA1F8A8A71D}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{40115122-A05E-4E9E-B960-939E58BB43E9}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{522A18A8-83CB-4BB1-B5B5-714ADD1E7E40}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{32A31CE7-0BF4-4109-B038-D3418C5C489A}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{4F691391-89F0-41D7-9B27-96AB3149BD54}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{1DD6FF1A-6B01-4CF7-B92D-42046CA27D07}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{D3EC40D1-E409-4507-9C43-6F93DC25BAE5}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{AA1A8367-3F8A-439A-87FE-29B284FC3951}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{24AF8D37-0532-47A2-8A97-904CD0FDA84F}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{F129DBD7-3227-4B5C-B72D-6B02D51694B6}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{72FF8280-EA16-4E8D-8BC5-3A2040C51A06}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{0EB046CB-F0FE-42D9-AE5C-6CB162557D41}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{9253B446-3E49-4610-B078-FFAC2060B84B}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{8E877FC2-3778-4781-9DC7-A3917CA29E6E}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{C3DCC16F-8716-43CC-9D88-1408E051D7DB}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{3095F005-C8A0-4CA1-B7FC-0065840DD19B}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{C02CDEC0-1376-492C-9673-827B0B48D4A3}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{039741F1-305D-43F0-87E2-79C9D4DC8015}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{388FA400-3C91-4A1F-B583-34EAC403CE16}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{85A1D267-1F4D-42A7-8ECF-CE7ABFEDDEFA}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{E4D117AC-669F-4DA8-9883-30FFB1C0C4EB}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{0BBAF61A-21C2-4B14-B89F-291DC3AC65B1}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{23A23EE4-2787-419C-9BCB-7AF7886B47A3}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{B9F0F0A4-4141-4054-BF62-FAD25D059898}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{003D3DC2-25EC-4AD5-B17B-97BF227A02DA}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{777FD07B-6069-410A-A3C6-7FBAAF977E9A}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{76BF9D2F-DA1C-494A-A2CF-C117022BCE68}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{04359006-080D-4679-A8CA-631F39D5D6B3}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{4C5A80D1-0D91-4869-BF72-684A7ADCD854}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{D567138C-CC5A-4DF8-8E65-4D6B6F19E32E}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{AD8F5A5E-F274-4E00-8C38-7A2F778C5F5A}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{0DB47F9A-762A-48A7-B602-AEF75120CD20}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{E7AEBD21-2C22-4CBA-BB9D-3804DE14BF8F}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{99CADC59-87A0-49C8-A6AF-9636DE74CABC}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{552ED68B-2FB5-47FC-9851-CB34393EE682}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{4FE0EA1A-C0A3-428D-9CF0-98266FC7C16D}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{C048DFD1-F49E-4A81-9095-ADF179A93A35}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{9382917C-9951-4C90-B675-6C0E37B5E039}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{F5C283EB-746C-4584-8266-D7F55057F5CC}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{2B90DC7B-BB40-4635-9EDE-39B563F9A321}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{08F1A139-52AB-4CDB-8E4C-F9FA4F1C318F}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{1BFB4195-CC2D-42F0-9829-C7E845BF80C8}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{606A651C-3B29-46D1-B989-BB443ED7D4DB}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{4EC47887-1F45-4F1A-91C9-07A941402ECE}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{AAF91783-6FAF-4B77-95DD-99786FA368A7}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{C62F8623-5D7F-40C7-9440-360B95358ADC}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{7EBC70E5-A538-4F8D-B9B2-3AD8AA8F795C}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{FAEE187A-6C4C-4185-8109-ED16D6281B85}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{C82FF10C-8E38-458F-B28D-0F88CC276C0E}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{D47979A7-5A4C-4D5F-B5FD-D3FB718CCD3F}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{7AC0AED3-26AA-4488-BE9D-CBC6C4A9DCF9}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{28B2AD14-E3D4-449F-89BF-6E900026015A}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{0D580A8C-6494-427E-8225-A3B6EBFCB3C1}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{EED1E3F3-78FE-4549-92E1-C688C5BC31AD}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{79F5BD78-5103-4474-BDF5-67968327512F}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{43A993D5-79A0-4B2B-932A-82E13022AC99}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{8648E60C-56B9-4204-AF24-2B9219396BCC}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{9E771987-2959-494C-A52C-855B0B6A86EC}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{54F05E70-3130-43C6-A8BA-17319227D0F4}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{9F5C407E-4960-4FCC-8661-E267EA91AEA8}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{A33186C2-3971-41A8-B8A9-EB7AB024C69F}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{9DE64AA0-6EB2-4251-9788-6FC096D15ED8}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{793106FD-70BB-474D-81CA-60CB125432EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId147"/>
+    <tablePart r:id="rId151"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21039437-7C3F-457A-A448-9E7C5C6E0A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CCF993-111D-4815-97C2-78BEABDEC2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="393">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1391,6 +1391,30 @@
   </si>
   <si>
     <t>No utiliza one click</t>
+  </si>
+  <si>
+    <t>1-3NQ40XW0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Martinez De Rosa 5093, Quinta Normal </t>
+  </si>
+  <si>
+    <t>Ricardo Morales</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1FPvFPDgEnnypJWf0VXmV29yOAdaRKUZR</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1otNSCl6WVib1dsbC8I8_nAyXRJ9qrRVm</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=10tliLsuE2PB_Jc-GAEJOLCkIX_U0HfhN</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Qp5ezsgZAQ38PrHjL_3U5p91DxI5bHmh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No retira pestaña en roseta, sin dificultad Conector </t>
   </si>
 </sst>
 </file>
@@ -2054,6 +2078,24 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2079,24 +2121,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2243,25 +2267,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ43" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ43" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ44" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ44" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="22"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="19"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="32"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="29"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="30"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
@@ -2279,7 +2303,7 @@
     <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
     <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="28" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="29" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
@@ -2494,7 +2518,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AJ44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -6769,163 +6793,265 @@
         <v>-</v>
       </c>
     </row>
+    <row r="44" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46275.333339247685</v>
+      </c>
+      <c r="B44" s="10">
+        <v>8</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="T44" s="3">
+        <v>4</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="V44" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="W44" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="X44" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH44" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI44" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ44" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{5F254211-F2B7-4192-A99C-FA12631F1DCA}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{D999DC53-AFBA-4024-94D9-4343B0424687}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{5BC54CAC-3C30-4AE9-9C6D-883C397905BA}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{8A7D9812-F621-4886-9D0C-3D33A6AC09AB}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{B0D8831A-6C36-4DED-AFA5-86B0EF0C8406}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{82A1A44F-12DD-449F-A338-DC35E0DCAF3C}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{66E85A3E-19FC-4912-8F94-372C14DACDAE}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{052B7706-53AB-4D60-AF09-B30B0B755DE2}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{AF7C3B0F-6CDE-4FBF-8C7B-4A839AFD79DC}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{6DEE0415-9F35-43FB-B27F-40318E90EBB0}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{299D698C-7DD2-40A9-BD83-EA52EE3231DE}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{BBCA4C60-30E2-4583-9389-79C5AF3CA416}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{EBC420B7-D1FA-40E6-A198-D075FA1649EB}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{507DD8FA-8EDA-4993-9E5B-5189A32D424B}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{7D690290-DC2A-4BF9-B0C5-88998BBABBBB}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{547DF65E-28B8-4BBA-9A90-8982EC100970}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{68074B07-C458-48AC-969B-7CC40E55704F}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{B273B0F3-4EDC-4110-8866-3246552CFDD8}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{12B2B75B-F72A-4A56-9EB7-EF0DD2E40773}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{E27FB2C3-76CA-4B4F-9DDF-384AFB78C329}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{E8CA8A60-0184-47AE-A344-EE331D8EF526}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{8CEC6C17-EA0D-41CF-BD38-ED89B5CDE55E}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{D928947D-4627-4B81-AB2F-12BD773F3EF0}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{E623AFCB-67A6-47ED-9A78-DC7B525A1E9A}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{EF0C84F1-BAFB-48B1-BE03-55815DCF221D}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{322A9CF4-298E-41C6-8D40-BC08B5CE6E8A}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{E17032A1-CFB5-4AB6-99C1-1874A3508782}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{39541214-9D4C-4819-8A48-AE1DD79B00B3}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{EFB6FAFE-F11F-4D6E-AADD-EE382C0D1DB5}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{D988AAC9-9129-40A3-B5E0-625C03CB9AF0}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{2000B902-6097-4820-A3C2-54F49651284F}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{99B77298-655C-4D1B-B2AE-665D49E4D07F}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{3C8ECAD3-0D75-400C-B44D-DFF18D144919}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{198F14E6-9FC0-4F0A-8E05-790A42292AED}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{E0F1D95D-1BE9-4491-8739-46022B9FE99B}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{2A5AA804-0CDC-47EC-81F8-C4B5F0DFB620}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{96EEFAD7-CF8B-44E0-81D6-A472E76854C1}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{A8111485-F280-4EC1-AEA7-205416319816}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{0695E8A4-7A81-4777-8A7A-CB16C7219FE3}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{8D1FABA8-CF06-4D94-A50D-29D50D404C2E}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{DC900745-BF32-4458-8A02-49B82263685A}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{76B079D9-A72B-444B-A4C9-9FCEA069F2D3}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{C5253A3B-0827-49EE-8FF1-6D7DAC0217D9}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{6D4DF2C6-7188-4143-B5E7-D2502949A650}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{C51950B2-E420-4A32-BB63-89225BBC76AD}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{097D967C-3F6D-4727-8BA9-6A37B111AF91}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{A280732E-36CE-4F25-AD94-DB4FC2E10CF6}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{D0CFF362-761B-48C0-871E-C12184F8339E}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{F2B9E9EE-6133-4068-AB7D-3D1EDBC2C22B}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{46CA7A45-9CA4-4626-BA3A-381F7930C7AD}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{42BE30D1-2F5B-418F-8495-2E38353D2AA7}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{7CE77D46-0023-469C-8E8B-75674ED3538A}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{064269DD-3443-4254-99B5-C3FECA0CA579}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{03AD4640-53E6-4008-BAFB-B3F037F2644C}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{374D9E4C-7963-48EB-8AA4-6A26E8A11B4E}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{B4AE9A98-32AF-4B43-83A7-E0133D8415FC}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{247CF6CF-6681-4E76-86B1-5F98E25ED6F2}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{6B5A6079-7158-4B4A-BF06-F0A06F2A4F70}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{5B747CB5-C5D3-4BEE-8E6A-6743F6D8E5CC}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{6A309DD9-CF17-45CC-983F-F683CAEE58A1}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{D5E138EC-07E9-41F5-9AAF-5239A268A225}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{241423D1-7707-4183-B8D8-1D3889C03BA5}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{9A981A24-03C2-469A-A4DD-27AD9CB91D42}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{9EA09D93-43AA-4673-9375-6CCEC1B0CE79}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{69C878CD-1B16-4A90-A5B5-F1326F1C7ECF}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{9F3DA76B-8C30-4F08-B5FF-09D258F147F6}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{1E10B9E4-D03C-4A50-AF66-D06EDF3D73E5}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{F6C81866-1CCA-4642-B52C-2ED48808EE6A}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{18FE4689-89A4-4170-BD36-82AD238F8316}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{67BA256B-ADAF-4104-955E-90DD4D4CA3D6}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{7CCFAB91-63B8-480A-A3F0-0AA83A414AE3}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{557E32B1-E258-49E1-AEA8-9FECC7EA8737}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{F5BF5EA7-3E4A-4A77-8BFB-AE6AA062A549}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{0F9E754E-B867-4E48-8FF9-B730A3342C8A}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{1DA2C18F-93EF-470E-80A7-953BAE8150CA}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{D57266DF-4EDB-4718-9BCF-F76C498B5ACE}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{11E5CA26-1793-452D-A4E2-E407B929F860}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{1AEFF898-381E-4401-8B9C-8EFFE4FB011B}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{786231F9-3F8A-4339-8669-D482DC181878}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{64B3E192-7256-4248-9D80-484017E6AE2D}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{F7E4824F-54BA-416D-924F-3B52833F9171}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{DB39FD18-04E4-4F72-87C1-00539C728B80}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{4F208D31-D45C-4448-8E6E-9AC16A8DC595}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{3F0A040F-825D-4938-97EC-9AB8EE9751DF}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{A32D45CC-352C-4B5D-AF6D-7C999D47CA76}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{8301C53B-565D-47B4-A6DA-9FA689CF06CF}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{85B98E01-EA22-405C-82A6-4B2E2C2F7C55}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{904B4E83-81C5-4848-BCF5-AEA1F8A8A71D}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{40115122-A05E-4E9E-B960-939E58BB43E9}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{522A18A8-83CB-4BB1-B5B5-714ADD1E7E40}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{32A31CE7-0BF4-4109-B038-D3418C5C489A}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{4F691391-89F0-41D7-9B27-96AB3149BD54}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{1DD6FF1A-6B01-4CF7-B92D-42046CA27D07}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{D3EC40D1-E409-4507-9C43-6F93DC25BAE5}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{AA1A8367-3F8A-439A-87FE-29B284FC3951}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{24AF8D37-0532-47A2-8A97-904CD0FDA84F}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{F129DBD7-3227-4B5C-B72D-6B02D51694B6}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{72FF8280-EA16-4E8D-8BC5-3A2040C51A06}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{0EB046CB-F0FE-42D9-AE5C-6CB162557D41}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{9253B446-3E49-4610-B078-FFAC2060B84B}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{8E877FC2-3778-4781-9DC7-A3917CA29E6E}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{C3DCC16F-8716-43CC-9D88-1408E051D7DB}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{3095F005-C8A0-4CA1-B7FC-0065840DD19B}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{C02CDEC0-1376-492C-9673-827B0B48D4A3}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{039741F1-305D-43F0-87E2-79C9D4DC8015}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{388FA400-3C91-4A1F-B583-34EAC403CE16}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{85A1D267-1F4D-42A7-8ECF-CE7ABFEDDEFA}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{E4D117AC-669F-4DA8-9883-30FFB1C0C4EB}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{0BBAF61A-21C2-4B14-B89F-291DC3AC65B1}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{23A23EE4-2787-419C-9BCB-7AF7886B47A3}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{B9F0F0A4-4141-4054-BF62-FAD25D059898}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{003D3DC2-25EC-4AD5-B17B-97BF227A02DA}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{777FD07B-6069-410A-A3C6-7FBAAF977E9A}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{76BF9D2F-DA1C-494A-A2CF-C117022BCE68}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{04359006-080D-4679-A8CA-631F39D5D6B3}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{4C5A80D1-0D91-4869-BF72-684A7ADCD854}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{D567138C-CC5A-4DF8-8E65-4D6B6F19E32E}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{AD8F5A5E-F274-4E00-8C38-7A2F778C5F5A}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{0DB47F9A-762A-48A7-B602-AEF75120CD20}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{E7AEBD21-2C22-4CBA-BB9D-3804DE14BF8F}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{99CADC59-87A0-49C8-A6AF-9636DE74CABC}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{552ED68B-2FB5-47FC-9851-CB34393EE682}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{4FE0EA1A-C0A3-428D-9CF0-98266FC7C16D}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{C048DFD1-F49E-4A81-9095-ADF179A93A35}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{9382917C-9951-4C90-B675-6C0E37B5E039}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{F5C283EB-746C-4584-8266-D7F55057F5CC}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{2B90DC7B-BB40-4635-9EDE-39B563F9A321}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{08F1A139-52AB-4CDB-8E4C-F9FA4F1C318F}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{1BFB4195-CC2D-42F0-9829-C7E845BF80C8}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{606A651C-3B29-46D1-B989-BB443ED7D4DB}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{4EC47887-1F45-4F1A-91C9-07A941402ECE}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{AAF91783-6FAF-4B77-95DD-99786FA368A7}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{C62F8623-5D7F-40C7-9440-360B95358ADC}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{7EBC70E5-A538-4F8D-B9B2-3AD8AA8F795C}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{FAEE187A-6C4C-4185-8109-ED16D6281B85}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{C82FF10C-8E38-458F-B28D-0F88CC276C0E}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{D47979A7-5A4C-4D5F-B5FD-D3FB718CCD3F}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{7AC0AED3-26AA-4488-BE9D-CBC6C4A9DCF9}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{28B2AD14-E3D4-449F-89BF-6E900026015A}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{0D580A8C-6494-427E-8225-A3B6EBFCB3C1}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{EED1E3F3-78FE-4549-92E1-C688C5BC31AD}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{79F5BD78-5103-4474-BDF5-67968327512F}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{43A993D5-79A0-4B2B-932A-82E13022AC99}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{8648E60C-56B9-4204-AF24-2B9219396BCC}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{9E771987-2959-494C-A52C-855B0B6A86EC}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{54F05E70-3130-43C6-A8BA-17319227D0F4}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{9F5C407E-4960-4FCC-8661-E267EA91AEA8}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{A33186C2-3971-41A8-B8A9-EB7AB024C69F}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{9DE64AA0-6EB2-4251-9788-6FC096D15ED8}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{793106FD-70BB-474D-81CA-60CB125432EA}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{925FC58D-7DCA-4C67-89B8-E3A6014C7D8B}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{18111B09-AD44-475F-A026-A8B12E31D3AA}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{9F3C486D-4C47-44B9-8F73-81DCC323DF81}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{6A60F384-EDBC-4CBF-9BAC-A18159C5CEAF}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{A03AA744-E572-4986-A64D-3B9D3DBD3DA4}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{980574FD-7311-4314-8CFE-167FA94760A1}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{6359A01F-F5EE-4471-A9AB-D430E06AE361}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{8945B62B-0588-4C21-AD82-F215929ABBD3}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{A851AC66-AEB5-4868-BF36-82ED4CB00C6F}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{A720506F-771E-4774-8FDA-2D9188F28AF1}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{16517F14-DA08-4AAB-B1AC-4F041EBE3037}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{D5C79D21-89DA-404D-B062-F14268E7AB43}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{DAF03589-41C4-43A6-903E-CEE5CE6AA42B}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{8C9670D7-E738-46C5-B5D0-15F9C4526142}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{D86BCF07-7F1C-47DF-BE5B-B76CA9A687E4}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{E311C054-599F-453D-A7E8-6D6CBCDFBACC}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{1887BEF3-94D9-4D42-9A74-E6F1E611D30F}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{D0B5011E-9C16-4642-9850-BBEA3F864415}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{639F908C-E0B2-47C4-87F1-E0641369AA95}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{3FE266F6-5CE0-4E3B-85C8-4B6A28F14339}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{F14F1A04-B481-4729-B26F-B3B455B63C61}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{2A9B3327-C60F-4C5F-A1E3-31591A3F1365}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{83C064D4-F4BF-42AF-B8E5-741B920CE459}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{E84D5A9E-AD3B-499A-85EC-DC2FFFF40B62}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{A35C51BE-86A9-4D99-983D-C232167438FA}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{ED22CC3D-EB54-4A33-932F-A59E8262088E}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{60B28E60-8C19-413E-8885-06BA8A3FB274}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{2DF30F86-B61C-4035-9297-4622F7420975}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{4236ABB0-65F3-4E7B-9E7C-675C4C5FE21A}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{6D649FB9-2453-4F4E-B26B-79D6FA27D838}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{CB5E6C3A-96CE-417D-907F-78790113579C}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{6FF54CFF-CF8B-4FD2-B26D-57AD8FB4B9E5}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{285AC3FC-F2A2-4861-9D38-A79612E5BE08}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{FE7C9732-8B4D-43EC-A6F2-9FF3A9715971}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{4B0D7500-A7EA-453C-A061-BC57758CA80D}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{3DCD24E3-4DB1-45D5-934D-D6652254CC84}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{960CAF09-1A1C-43D9-9B0E-67EB3971563B}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{EA4889A9-1FE3-43A2-B179-CBDD29D55574}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{626F8464-64A4-4DB6-B66A-09F9BED1B026}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{50170F6B-CB51-40D3-8A47-261BC11D6CCA}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{E9F8661D-D176-49B5-9BDE-F0D472C11E42}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{A1AC231E-3BAB-4A4D-B00A-54CB2202878B}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{9232F53B-B157-479C-B548-38AAC14E5DBD}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{F01AC0C8-5D7E-4117-882E-2B8785FB4D99}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{6BC5D361-95CD-4BB8-A6D8-75BA87E9029B}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{05636045-C61A-4283-A0F9-53B10A42EB90}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{953B8216-3054-41B4-9581-141FA0E69D47}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{ACBD6272-0D09-4E60-ABA8-77C9F2960334}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{AE6611B2-D295-4543-9F74-416750A8AEF1}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{88805471-0B75-45E7-AAB7-34E8B8527DB9}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{E34DE2CC-4EEB-4ADF-865C-286F311F5382}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{CE571F4C-D029-4A03-A868-878378940177}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{50930D19-5F4E-464F-909D-5A66A1D65A10}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{FA6A1C49-BC0E-4706-B97D-600C2DBE721B}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{9368AAB3-429F-43BD-B318-2B88970FAFF5}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{7B542AFD-4125-4731-89EB-BA1EE44CF1A7}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{F4677972-DFBA-4783-A68D-808E4A936AC3}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{C64C09E6-3079-495E-A9C0-B5A1AAFAD3A2}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{A9B9967C-5697-4037-A9A9-A1076606892B}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{877C030F-1558-4B87-80B7-E9D1742C7A97}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{64698B3B-298A-4494-B87E-265A7C1FBA4D}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{DBF29DF7-C653-45C1-B40B-E1DC8F3DBFEF}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{C6AC32DB-843D-41A9-8B9A-525EB318F0DD}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{656DB7B1-83B3-44B6-9982-989C3B89153C}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{D75200F0-F2CF-4222-92D3-5BF34B4DB1A0}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{A6D71CF9-7378-48A0-9FFA-D64FC0F3D025}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{6D0588B9-FBA2-44EE-A113-521B742F5163}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{EF422D65-C771-40D7-9D06-C6F7C30D735D}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{6A198ADF-51A8-4A75-80FA-726A433E70EC}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{F15F9269-81FC-4A3D-B3A6-C44B392DCEC3}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{A3972392-2E52-42B5-B21B-0E0485FDC61F}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{9DF8D3BB-4CB7-43D1-8463-DCE502F64912}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{B589BFA2-3FF0-4AE0-AB28-6F9391F2FFE6}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{F269A479-9A5F-44D8-8649-D4CE306F367D}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{5B4B22AE-8930-44C5-9B10-9854D147F1C6}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{3035B81A-4440-4D7A-BD4C-8312A1C741C5}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{3892B915-9E58-43DD-971D-075BCD111740}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{AD675849-9EA1-4D66-9CCE-AED2CA2D30C9}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{4C016655-DAA2-4F2C-BA57-7C0B821F2651}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{63A10FAB-999A-4659-AE68-52BC965BFA01}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{906F0307-2AC7-4666-A3C8-C2C155F8C9AE}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{B05FF665-3DEE-4F87-8357-A1575572785E}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{9C021503-EF0B-42F1-BD3E-28E4D86B2774}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{1EB9E233-F5B2-4AAA-B206-1D173A234561}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{D43B564C-A9E2-453A-B237-168A922B0737}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{CE1F5974-6E6C-4D8C-9C40-97FD726A32F3}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{BD28E67F-5575-469C-BF46-9EDAF9BE86C6}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{B65D4DAE-0030-4E66-BCB8-4DF5BAE69951}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{2239BA25-1594-491F-981D-C08F5134A26A}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{4512931A-BE12-4A98-AFDC-1BBAFCCED042}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{CF8C33F5-5EF5-4D7E-92C6-B8B0B60492ED}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{5FE30E0C-CDB2-41C0-BB47-562917F15B91}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{D69E3EE2-7470-4EC7-833A-AD44B63C0015}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{EFFAB196-CC74-4F0C-8F87-1D034803B6EF}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{45CC51C1-D3A4-4FF0-BF9F-427A5B9FA149}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{FAF54131-5874-4DF2-B614-103B3F65F581}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{2000BEF9-41E6-4051-B49B-9FB54E354031}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{78255EBE-3670-4019-827A-7947DCB4C6CD}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{5AC434F6-F3DD-4D9B-99B6-4B960910F924}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{D7B56FA3-5E27-459E-929B-6A391961C475}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{8406D192-61C0-46CB-B868-7D929E014589}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{4E2586D8-FB6B-4EAD-AA3D-E7CB1727BAB0}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{5CC550E1-0420-4184-9BE9-B4F4843941B5}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{25874451-F753-4089-87B3-AE9FBE53E429}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{4F767D2D-9725-4C9D-A1D6-EE9A2525607A}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{BC677F08-F3A3-4E0E-B0D9-5A0912F7B0DD}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{9A3882EF-4598-4B97-9EED-735F7A524ABF}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{8E40E1A9-6675-408B-93F8-C630A87C0CCD}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{C8CFF744-0230-465E-BA2B-357A55516B25}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{FBEAF307-BDEE-4A77-9955-C006489ED9FF}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{0FA7F1C9-6B3A-470D-BAC6-9994D1534EFE}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{74E81F2C-BBEA-4495-B920-E53558A10322}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{499A0AFD-EE98-4461-8447-10302538CB5C}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{3FBF53C6-16BF-42EC-957D-C57F6FB46D3C}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{828E218F-0EC2-4D93-ADD2-6DCAB44018E4}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{E2E2272E-8220-488B-B420-EC3DBCA93E12}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{9337151B-DCCA-4DE9-9631-9046C29D5AF5}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{EF4B8B34-3B9E-4B3B-851B-2E0EBBD9F2ED}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{F18F69EE-C29D-4AC7-84E9-0A988FBAD99E}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{7D8132EA-50FD-40C2-B511-EE26D5D8F8A5}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{443F0186-29CC-4695-9CDC-73F7D69AD853}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{9EBF14CF-2104-4709-A5D3-C30CCBD382EA}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{D72FD1D6-C88E-4007-BB4F-4D4107841F51}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{13DE014B-99DE-4B28-8DD9-D14119E7480A}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{4F841FAB-3E5D-40EB-9DDD-2092B2BD31E9}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{F4B6ACF5-8E56-4E04-ACBF-71BE4895087C}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{65D0F8BF-31EC-4ACF-8B09-4A033CE4A3C1}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{F177CC47-5BF7-4B03-9C38-8D4463045D9A}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{44A9379E-AC5D-406C-94C9-CBC65D8FDDEB}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{0502054A-224E-4294-9DBF-2509EB53B149}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{D9BCE975-BAF3-4407-B51B-F9F59CEFCAA7}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{6AB6D8B8-61A9-4ED3-9933-60C7AC058E52}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{C289C055-2FAA-4958-A6AC-D3AD825DE64D}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{A8A590AF-2DB4-4957-96FB-FDCA5DBD3ECF}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{54FD5F76-5D9E-4CBD-B492-A7E57D9DEDF1}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{63EA3447-4DF5-468B-A324-E3166BDE524F}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{7E03EBBC-7A09-4C1C-8FD6-DB7C7F2E8F1D}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{501ABFE6-284F-4C17-93E0-1B5251A63095}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{5F6D72B7-DB9A-4A3A-9204-E695E4976C49}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{C719578E-6F8B-41FE-ABBA-E87BE5F697E7}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{9BB7F5E6-0C64-42A9-B7BD-C9A1D7EBE347}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{560816C2-AAF4-4C96-9C24-D356F2679EAC}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{709B483D-153D-4178-997A-AD61E23F19E9}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{E4C253AC-664E-4475-AA82-7C71A340681F}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{45E3C517-86B0-400A-BA6B-2407FBC62E91}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{E70B9E63-A8B5-430F-8776-8B586A63EC05}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{F5CD087B-E3A8-493D-B9BE-164CEFE5B3FA}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{8DD7AE8C-BA41-4386-9F6A-8DDCA52BE3BE}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{09746913-47E1-46E7-B175-3FBB6A503AD9}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{687218B7-7777-43EE-B5BE-C8FE3CD384FA}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{91922D3B-40A9-44D9-A147-F2B11AF6C34D}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{3D8359C2-15F4-405E-A9C9-0DC5D8B75BDD}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{E6ABF7D9-13DF-4940-8213-6756FA99C4E0}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{A822630F-6D6A-45F7-8C2A-41E5F599DC09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId151"/>
+    <tablePart r:id="rId155"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CCF993-111D-4815-97C2-78BEABDEC2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20950A98-EF30-4C7B-83CF-DD45714555DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="409">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1415,6 +1415,54 @@
   </si>
   <si>
     <t xml:space="preserve">No retira pestaña en roseta, sin dificultad Conector </t>
+  </si>
+  <si>
+    <t>1-3NRRATPK</t>
+  </si>
+  <si>
+    <t>Cuadro verde 150 edif 1 dpto 83, Estacion Central</t>
+  </si>
+  <si>
+    <t>Jaime Carrillo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1H08P5rlpRN_laQ_a1DAfCZydYE8kle1J</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14uxy8hUORxfoeCTanmU6qVyMCVQR5mFg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1QUbHfHIInppcuY4avzGQ8BoX81fsrszR</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1V9PMOnlqYqfCZoTXIqI4Jj4cEQqAC2Gi</t>
+  </si>
+  <si>
+    <t>No retira pestaña en roseta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3NRWT22T </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mundo Nuevo 4405, Quinta Normal </t>
+  </si>
+  <si>
+    <t>Andrea Muñoz</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HuvvMuctR9m1VrvdLiRxt2OQIB1-g_Iv</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PVSZSZf1DgoMJ-OqDtUMa_7eL8vMTWsJ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1iBf4CyIyl_Kn6bd5FQcqxIVLAlexu6wI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1bkLvpgjZFHF_EH3JYOlqWL_viViW592z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalación de roseta fuera de norma a petición de cliente, técnico ocupa herramientas one click según procedimiento </t>
   </si>
 </sst>
 </file>
@@ -2096,6 +2144,24 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2121,24 +2187,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2267,25 +2315,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ44" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ44" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ46" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ46" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="18"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="31"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
@@ -2303,7 +2351,7 @@
     <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
     <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="29" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
@@ -2518,7 +2566,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ44"/>
+  <dimension ref="A1:AJ46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -6891,167 +6939,371 @@
         <v>-</v>
       </c>
     </row>
+    <row r="45" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46275.584452997689</v>
+      </c>
+      <c r="B45" s="10">
+        <v>6</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="T45" s="3">
+        <v>4</v>
+      </c>
+      <c r="U45" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="V45" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="W45" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="X45" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH45" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI45" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ45" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="46" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46275.784461053241</v>
+      </c>
+      <c r="B46" s="10">
+        <v>9</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="T46" s="3">
+        <v>4</v>
+      </c>
+      <c r="U46" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="V46" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="W46" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="X46" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH46" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI46" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ46" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{925FC58D-7DCA-4C67-89B8-E3A6014C7D8B}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{18111B09-AD44-475F-A026-A8B12E31D3AA}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{9F3C486D-4C47-44B9-8F73-81DCC323DF81}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{6A60F384-EDBC-4CBF-9BAC-A18159C5CEAF}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{A03AA744-E572-4986-A64D-3B9D3DBD3DA4}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{980574FD-7311-4314-8CFE-167FA94760A1}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{6359A01F-F5EE-4471-A9AB-D430E06AE361}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{8945B62B-0588-4C21-AD82-F215929ABBD3}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{A851AC66-AEB5-4868-BF36-82ED4CB00C6F}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{A720506F-771E-4774-8FDA-2D9188F28AF1}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{16517F14-DA08-4AAB-B1AC-4F041EBE3037}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{D5C79D21-89DA-404D-B062-F14268E7AB43}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{DAF03589-41C4-43A6-903E-CEE5CE6AA42B}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{8C9670D7-E738-46C5-B5D0-15F9C4526142}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{D86BCF07-7F1C-47DF-BE5B-B76CA9A687E4}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{E311C054-599F-453D-A7E8-6D6CBCDFBACC}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{1887BEF3-94D9-4D42-9A74-E6F1E611D30F}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{D0B5011E-9C16-4642-9850-BBEA3F864415}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{639F908C-E0B2-47C4-87F1-E0641369AA95}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{3FE266F6-5CE0-4E3B-85C8-4B6A28F14339}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{F14F1A04-B481-4729-B26F-B3B455B63C61}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{2A9B3327-C60F-4C5F-A1E3-31591A3F1365}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{83C064D4-F4BF-42AF-B8E5-741B920CE459}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{E84D5A9E-AD3B-499A-85EC-DC2FFFF40B62}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{A35C51BE-86A9-4D99-983D-C232167438FA}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{ED22CC3D-EB54-4A33-932F-A59E8262088E}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{60B28E60-8C19-413E-8885-06BA8A3FB274}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{2DF30F86-B61C-4035-9297-4622F7420975}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{4236ABB0-65F3-4E7B-9E7C-675C4C5FE21A}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{6D649FB9-2453-4F4E-B26B-79D6FA27D838}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{CB5E6C3A-96CE-417D-907F-78790113579C}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{6FF54CFF-CF8B-4FD2-B26D-57AD8FB4B9E5}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{285AC3FC-F2A2-4861-9D38-A79612E5BE08}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{FE7C9732-8B4D-43EC-A6F2-9FF3A9715971}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{4B0D7500-A7EA-453C-A061-BC57758CA80D}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{3DCD24E3-4DB1-45D5-934D-D6652254CC84}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{960CAF09-1A1C-43D9-9B0E-67EB3971563B}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{EA4889A9-1FE3-43A2-B179-CBDD29D55574}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{626F8464-64A4-4DB6-B66A-09F9BED1B026}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{50170F6B-CB51-40D3-8A47-261BC11D6CCA}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{E9F8661D-D176-49B5-9BDE-F0D472C11E42}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{A1AC231E-3BAB-4A4D-B00A-54CB2202878B}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{9232F53B-B157-479C-B548-38AAC14E5DBD}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{F01AC0C8-5D7E-4117-882E-2B8785FB4D99}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{6BC5D361-95CD-4BB8-A6D8-75BA87E9029B}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{05636045-C61A-4283-A0F9-53B10A42EB90}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{953B8216-3054-41B4-9581-141FA0E69D47}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{ACBD6272-0D09-4E60-ABA8-77C9F2960334}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{AE6611B2-D295-4543-9F74-416750A8AEF1}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{88805471-0B75-45E7-AAB7-34E8B8527DB9}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{E34DE2CC-4EEB-4ADF-865C-286F311F5382}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{CE571F4C-D029-4A03-A868-878378940177}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{50930D19-5F4E-464F-909D-5A66A1D65A10}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{FA6A1C49-BC0E-4706-B97D-600C2DBE721B}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{9368AAB3-429F-43BD-B318-2B88970FAFF5}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{7B542AFD-4125-4731-89EB-BA1EE44CF1A7}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{F4677972-DFBA-4783-A68D-808E4A936AC3}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{C64C09E6-3079-495E-A9C0-B5A1AAFAD3A2}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{A9B9967C-5697-4037-A9A9-A1076606892B}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{877C030F-1558-4B87-80B7-E9D1742C7A97}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{64698B3B-298A-4494-B87E-265A7C1FBA4D}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{DBF29DF7-C653-45C1-B40B-E1DC8F3DBFEF}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{C6AC32DB-843D-41A9-8B9A-525EB318F0DD}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{656DB7B1-83B3-44B6-9982-989C3B89153C}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{D75200F0-F2CF-4222-92D3-5BF34B4DB1A0}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{A6D71CF9-7378-48A0-9FFA-D64FC0F3D025}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{6D0588B9-FBA2-44EE-A113-521B742F5163}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{EF422D65-C771-40D7-9D06-C6F7C30D735D}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{6A198ADF-51A8-4A75-80FA-726A433E70EC}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{F15F9269-81FC-4A3D-B3A6-C44B392DCEC3}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{A3972392-2E52-42B5-B21B-0E0485FDC61F}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{9DF8D3BB-4CB7-43D1-8463-DCE502F64912}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{B589BFA2-3FF0-4AE0-AB28-6F9391F2FFE6}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{F269A479-9A5F-44D8-8649-D4CE306F367D}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{5B4B22AE-8930-44C5-9B10-9854D147F1C6}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{3035B81A-4440-4D7A-BD4C-8312A1C741C5}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{3892B915-9E58-43DD-971D-075BCD111740}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{AD675849-9EA1-4D66-9CCE-AED2CA2D30C9}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{4C016655-DAA2-4F2C-BA57-7C0B821F2651}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{63A10FAB-999A-4659-AE68-52BC965BFA01}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{906F0307-2AC7-4666-A3C8-C2C155F8C9AE}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{B05FF665-3DEE-4F87-8357-A1575572785E}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{9C021503-EF0B-42F1-BD3E-28E4D86B2774}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{1EB9E233-F5B2-4AAA-B206-1D173A234561}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{D43B564C-A9E2-453A-B237-168A922B0737}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{CE1F5974-6E6C-4D8C-9C40-97FD726A32F3}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{BD28E67F-5575-469C-BF46-9EDAF9BE86C6}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{B65D4DAE-0030-4E66-BCB8-4DF5BAE69951}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{2239BA25-1594-491F-981D-C08F5134A26A}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{4512931A-BE12-4A98-AFDC-1BBAFCCED042}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{CF8C33F5-5EF5-4D7E-92C6-B8B0B60492ED}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{5FE30E0C-CDB2-41C0-BB47-562917F15B91}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{D69E3EE2-7470-4EC7-833A-AD44B63C0015}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{EFFAB196-CC74-4F0C-8F87-1D034803B6EF}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{45CC51C1-D3A4-4FF0-BF9F-427A5B9FA149}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{FAF54131-5874-4DF2-B614-103B3F65F581}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{2000BEF9-41E6-4051-B49B-9FB54E354031}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{78255EBE-3670-4019-827A-7947DCB4C6CD}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{5AC434F6-F3DD-4D9B-99B6-4B960910F924}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{D7B56FA3-5E27-459E-929B-6A391961C475}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{8406D192-61C0-46CB-B868-7D929E014589}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{4E2586D8-FB6B-4EAD-AA3D-E7CB1727BAB0}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{5CC550E1-0420-4184-9BE9-B4F4843941B5}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{25874451-F753-4089-87B3-AE9FBE53E429}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{4F767D2D-9725-4C9D-A1D6-EE9A2525607A}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{BC677F08-F3A3-4E0E-B0D9-5A0912F7B0DD}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{9A3882EF-4598-4B97-9EED-735F7A524ABF}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{8E40E1A9-6675-408B-93F8-C630A87C0CCD}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{C8CFF744-0230-465E-BA2B-357A55516B25}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{FBEAF307-BDEE-4A77-9955-C006489ED9FF}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{0FA7F1C9-6B3A-470D-BAC6-9994D1534EFE}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{74E81F2C-BBEA-4495-B920-E53558A10322}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{499A0AFD-EE98-4461-8447-10302538CB5C}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{3FBF53C6-16BF-42EC-957D-C57F6FB46D3C}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{828E218F-0EC2-4D93-ADD2-6DCAB44018E4}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{E2E2272E-8220-488B-B420-EC3DBCA93E12}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{9337151B-DCCA-4DE9-9631-9046C29D5AF5}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{EF4B8B34-3B9E-4B3B-851B-2E0EBBD9F2ED}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{F18F69EE-C29D-4AC7-84E9-0A988FBAD99E}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{7D8132EA-50FD-40C2-B511-EE26D5D8F8A5}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{443F0186-29CC-4695-9CDC-73F7D69AD853}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{9EBF14CF-2104-4709-A5D3-C30CCBD382EA}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{D72FD1D6-C88E-4007-BB4F-4D4107841F51}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{13DE014B-99DE-4B28-8DD9-D14119E7480A}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{4F841FAB-3E5D-40EB-9DDD-2092B2BD31E9}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{F4B6ACF5-8E56-4E04-ACBF-71BE4895087C}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{65D0F8BF-31EC-4ACF-8B09-4A033CE4A3C1}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{F177CC47-5BF7-4B03-9C38-8D4463045D9A}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{44A9379E-AC5D-406C-94C9-CBC65D8FDDEB}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{0502054A-224E-4294-9DBF-2509EB53B149}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{D9BCE975-BAF3-4407-B51B-F9F59CEFCAA7}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{6AB6D8B8-61A9-4ED3-9933-60C7AC058E52}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{C289C055-2FAA-4958-A6AC-D3AD825DE64D}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{A8A590AF-2DB4-4957-96FB-FDCA5DBD3ECF}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{54FD5F76-5D9E-4CBD-B492-A7E57D9DEDF1}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{63EA3447-4DF5-468B-A324-E3166BDE524F}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{7E03EBBC-7A09-4C1C-8FD6-DB7C7F2E8F1D}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{501ABFE6-284F-4C17-93E0-1B5251A63095}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{5F6D72B7-DB9A-4A3A-9204-E695E4976C49}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{C719578E-6F8B-41FE-ABBA-E87BE5F697E7}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{9BB7F5E6-0C64-42A9-B7BD-C9A1D7EBE347}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{560816C2-AAF4-4C96-9C24-D356F2679EAC}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{709B483D-153D-4178-997A-AD61E23F19E9}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{E4C253AC-664E-4475-AA82-7C71A340681F}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{45E3C517-86B0-400A-BA6B-2407FBC62E91}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{E70B9E63-A8B5-430F-8776-8B586A63EC05}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{F5CD087B-E3A8-493D-B9BE-164CEFE5B3FA}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{8DD7AE8C-BA41-4386-9F6A-8DDCA52BE3BE}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{09746913-47E1-46E7-B175-3FBB6A503AD9}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{687218B7-7777-43EE-B5BE-C8FE3CD384FA}"/>
-    <hyperlink ref="U44" r:id="rId151" xr:uid="{91922D3B-40A9-44D9-A147-F2B11AF6C34D}"/>
-    <hyperlink ref="V44" r:id="rId152" xr:uid="{3D8359C2-15F4-405E-A9C9-0DC5D8B75BDD}"/>
-    <hyperlink ref="W44" r:id="rId153" xr:uid="{E6ABF7D9-13DF-4940-8213-6756FA99C4E0}"/>
-    <hyperlink ref="X44" r:id="rId154" xr:uid="{A822630F-6D6A-45F7-8C2A-41E5F599DC09}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{DDBFDC9A-1F33-4E03-ADB9-6268541CBC04}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{37A63072-5673-4FDB-B792-AD2E8A8E369E}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{7560B42B-76B0-4E97-BCA7-F8FAEBD33588}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{F154A939-7995-471B-8AB0-4A7753B33551}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{E0F44651-48B1-4B38-BC1D-47CA23FF8C0B}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{BE30D6A7-46DB-4F6C-AD72-1752CB939B95}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{CA167C38-8F38-4D12-AE3E-36A962686EEB}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{D097F255-C057-4EA6-9959-F5E9FE6D4DAF}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{667BF350-5C7E-4BED-BAB4-B70AD633AC2B}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{F204F857-ABAC-4851-9133-5468969ED01B}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{DBB757EF-35DB-4D87-BB71-25929AE0A4DD}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{6CFA9AA9-5BF6-4FEE-B7D1-7CD1E09C49B2}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{2064B47C-688E-4391-B5A3-325534D4FDE9}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{01CC9F0F-7D6E-4F7E-A1BF-0E1F848836E4}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{AB478435-471C-4371-91AD-4C7AE618A5FF}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{1EA9BA0C-5718-40EC-809B-97CAF885DFC4}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{0AACC061-E43D-4813-BE65-7C3A318243DE}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{AB734527-DA29-4B4E-85CD-8A81E8978831}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{F0234C13-FC96-4BFA-B4E9-1276D809C0EB}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{56890858-0899-46E3-84C8-28783176AD09}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{F3DFDF6D-9060-4F4C-A52E-3C3B20622D9A}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{8556F2B1-6E7D-4DEF-97C4-C23C1A13369C}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{55EF873B-9B2F-4306-98AB-4564E0A9F058}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{451F7615-519A-4673-9E53-5786221C25D1}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{688A3B1F-0BA4-4781-A0CB-6809A29080F9}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{317B89F5-DC8F-4170-B014-3CA990B1D0B1}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{259F6E59-0FB6-4428-84F6-5BCCED13C6EE}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{9C383BA3-6457-442F-B94C-BB4E0F80489C}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{1AE8D042-D7A5-4359-8C8B-0C7882A8659B}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{D5F855A3-32AB-452E-B7DA-6D286F75E434}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{2E98CCEC-C8DB-4CA1-8DF1-BD9EA71F5584}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{981B028C-BF4C-4551-B014-DB0DE6F682B9}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{79DCB601-B9E4-447B-A3E1-8B9A85B7F79D}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{369FE38C-C785-47EA-AF50-8E5D73FA114B}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{40241DDA-871F-41D8-9A1B-52D63CC16BE9}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{DEF10765-457C-487F-B247-FBFF1096ABA9}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{511B6544-9065-40F8-9721-670D67904B82}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{0B0DD9D6-D5CE-4586-8C57-D30A19CBF4ED}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{4FD65566-231D-43FE-814D-A35E38AA825B}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{7A2B9253-086D-46A5-803B-86583BB00CF6}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{DD0E201A-EB33-4386-9B23-38ABD9888947}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{599D673E-2ECA-4F67-8CEF-7EAA3021EF76}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{4FED9D57-B887-4464-B6B5-6DC77B90C335}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{C3C596D1-FEE6-40D1-BE1D-4AC2AABBF423}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{3D276E5B-D504-4EA8-8D39-BD14994B4C01}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{F471B65E-2254-4F7B-94EA-5C992C4CEAB7}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{2C34D939-BB6F-4D47-8AB3-5B0523DB10A4}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{7C7F9036-1BAA-47F0-A89D-0D42B5B7BB78}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{3DBA7FA1-36F8-4524-9900-B98697EF4E97}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{CABBCBCE-D583-4F73-B775-C0F0957771C2}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{C0EE8CB2-B23C-450F-B351-6E80558FB718}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{C4205633-57D5-4DD6-B7A0-9A6570C8C800}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{58F70ED4-8861-460A-A941-26C04771A6A5}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{C8972FD6-D88E-42B6-AE2A-2C9524BFF4EC}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{9CA89E4E-C7A6-4970-9900-1A55FA3DC74F}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{BC35CF3E-F8D9-42CA-9322-D66D328A3696}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{C4C2803B-118B-450D-A8E6-2B4E4078B4F4}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{0C50FE68-3073-4AD3-8C30-B01793E6DB01}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{9503D9B1-5A1D-4598-8B97-E87252E55B5C}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{FA52065B-FFCA-4253-8A9B-EAD6B5C700A9}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{7964542F-BD5D-420C-A653-0D406FD2F1B9}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{7737848E-5BF0-4DB7-BCFE-0801402157EC}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{0408DD99-6506-44EC-8379-D45F1F5FD787}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{0D4E291B-BBFF-4EDA-8258-82C66ACE68E0}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{BA91BCF2-1BCB-4C42-962B-B691DDE2B95E}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{439AD546-3F59-4679-9D74-50376B859BA6}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{7022BE44-7059-48B8-86D1-5400A32CEC42}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{0118C6BD-6D3E-4915-A88C-386FED5BAF52}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{807BD08A-F505-4466-A344-0A62A4A7A36C}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{26B2223F-93EA-4217-8D6A-28A705215955}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{6670DE45-74D5-4C34-8FC6-E11EC6125E35}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{E7CA74E5-2CDA-4C8A-B422-C818EEE83613}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{35AC1A89-9AA0-4F4B-A2A1-0E1FFE625852}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{918F7188-5576-42ED-9530-B4A43E4C4CC5}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{5CF6C3D7-EAEB-47CC-94F7-B6285EB6DD42}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{E1A2DA5B-AE8E-442A-967D-FDB628BDC924}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{C49F6890-93B4-4E5B-9FC4-A38171C07963}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{D0082366-8FFE-4760-B2F8-B02329DFA5B9}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{E5CB28BD-F8BD-4AD1-9DDF-EF68BF03A553}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{7FE4F5EC-3B3C-4BC0-A2E8-FB5BF28FE374}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{92478EA1-AE14-490F-8487-78619C16FBC3}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{B4C42EF2-F878-4CAE-9E4C-8027219B6D30}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{88605C68-F3D8-459A-B2BD-705156EB7A25}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{8F375607-EA18-4BDB-B936-3E8B3162395A}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{0B100F8D-4A99-44F7-9AAA-18AFF11963B0}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{7378445F-63C1-4933-BCBB-4217A8376AEF}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{609408E4-D310-4AAA-AE0F-491F2C7E0306}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{12A85933-7B62-4251-9DDD-2762425C87E4}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{D5FD3A1B-BB6A-4F38-B4F5-B18203EDF7EF}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{8F4C6928-FD68-4C0C-BEDD-8EF3FA59C8A6}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{D2CA4097-F182-47FC-BFE4-486A9446141F}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{30C333E4-51FD-42F8-85AE-3A2B17819CDD}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{C697959B-FEC2-4EEE-A464-12ACE2E4E6B0}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{14148B04-9C03-446D-9710-511F451BF5CD}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{F0CD0B32-7277-4B8E-9E9A-60E412EF605A}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{12206559-7A39-4CC6-AD1B-46116C490ED1}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{6F08EAFD-EF61-4B8E-8623-872BB46F1743}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{A30CDA79-83F0-4102-8F2E-49EE403D73AD}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{A1D6CA62-5AB4-4D99-8AA5-C457C7C96E23}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{3A5FF30B-3B14-449C-8674-927250ED0F19}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{556288A5-3ED8-4D40-8642-6225D91BE6A3}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{67AA8B3A-B50A-4C46-BB41-BD1500700BC9}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{6C80FFCB-6C9C-4C1D-8F97-5D5ED33D2E04}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{C0CAE8AE-8C4D-4FB5-8835-2732415A5848}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{62093E28-603B-4C75-9AD9-0FA8A8EAA92B}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{C93E48BF-A4E2-40E5-B794-44BE748FECFF}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{9A37D409-BB8D-43E2-9E67-7E22C38262DE}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{0B6855FF-AEA8-4429-96A9-EB840E2AC548}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{851C25A1-3A5D-49CA-90A9-2C07A5FC2D31}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{BFC72F42-BD63-490F-9A5F-249304ACAB94}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{F4ABDE7E-3849-4EB2-B359-92308053C2D0}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{39CC47C5-E27C-4D15-8366-18995F694D4D}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{0973F0A0-F246-4135-91C3-BCDB4022B69B}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{E0627294-079F-4D93-B0AB-680BCEBF04A7}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{1EA8C8C5-17CF-4AB6-86B3-B940AF53AF04}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{5CB991D7-EB0F-49B9-A1CC-E7B517EA7497}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{258784B4-7D62-4686-8FD9-268198C047EE}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{BA6E21FF-669A-4A62-9870-FF818366D7D0}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{3DC8FFAB-734A-4314-B54F-EABF89868C02}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{708568FB-C225-4F6E-912F-4A1B806A20BB}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{803E7794-076D-464A-A089-090F522374F7}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{AC14DA8F-4D2D-477C-995D-3F439F582B01}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{45BF6B29-0223-4AB2-9A03-DD51B15C078D}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{F03719BF-409D-4772-9EB1-2AB86F16F6A3}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{BFCFD6BE-B507-4DB3-AD20-BB6C76F2B6DC}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{D5530399-BF1B-44BD-AB3D-48D6EC63C5C9}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{D9E3AFCE-64EE-4B46-A602-4A93A24F3D28}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{6DEDB9B2-2770-4F58-A2D8-3FE4D10D8944}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{342EE9B3-57E7-4AE4-B762-857DBF54E92A}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{8819762E-1ABD-4D66-815D-DAE1FA03FBEB}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{C94EA869-5876-452F-8E01-3F8A6576CE73}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{FEA34FE3-C2C4-44DA-B716-9AC6B69887C8}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{01C97428-0630-471D-B216-C8B7A50A7AD9}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{A419126A-D3A6-479C-9830-F66D1F8BDBA2}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{894CEE8B-6F6D-4AA9-AAFB-9091582EFB9E}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{E94F2D77-5925-45AF-BA6B-5FC386EF2E67}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{F7C88AB4-B05F-4073-B49E-F0DAEF821069}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{133C79DA-F126-4C46-91CF-F10029D7BDD3}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{2F1E2530-0B87-418D-B751-59BCE3079115}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{5D174CDA-B2C8-498C-B13C-10CA0C1A712B}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{22539A30-A9BC-4892-B2EA-5C0CC44271B1}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{9435BECE-4C2E-4F25-BFAF-D82CF6494C4C}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{5FF4DCC7-15FF-433C-8914-E61CED61C49D}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{93C64831-21F0-4156-98CB-896CF9CC9FC8}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{51742480-CF1F-4E62-8BE1-3ADC4C9D3592}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{B68BE086-7928-4795-BFA9-6C99CFA086BE}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{6AAC6E43-1BEB-476D-B176-E9829F783F80}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{A7ECA785-BF1B-4155-B02C-F71259BE6504}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{68405735-469D-4C0E-A149-088FF907236A}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{18AA080B-C5EB-4482-B3DB-6C751E23CE57}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{CBEAE434-A402-4793-B945-B8843C6B78C2}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{D0A90D49-1628-4899-A82D-E8D91504C00B}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{40CB3DF2-5944-4898-997F-2E97DDE9EFF1}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{87194BE9-0DE4-4324-AC6A-991E697C9563}"/>
+    <hyperlink ref="U45" r:id="rId155" xr:uid="{B293FE62-397B-48FB-96C8-EC7EEA85D7F2}"/>
+    <hyperlink ref="V45" r:id="rId156" xr:uid="{70FFD98F-2A2C-4FFA-BD86-BAD6C4427400}"/>
+    <hyperlink ref="W45" r:id="rId157" xr:uid="{0FCF52BF-D2C2-43A3-9530-E51FD88E85CB}"/>
+    <hyperlink ref="X45" r:id="rId158" xr:uid="{96D1697A-64AC-4375-9702-061A649B6AFA}"/>
+    <hyperlink ref="U46" r:id="rId159" xr:uid="{147C99A2-B5D0-4E67-8FA0-C541DB4A37AE}"/>
+    <hyperlink ref="V46" r:id="rId160" xr:uid="{A9A315A8-117C-49B6-97C1-92EE0CB108EC}"/>
+    <hyperlink ref="W46" r:id="rId161" xr:uid="{1E94CBC7-253C-414C-A9ED-24476AAFA640}"/>
+    <hyperlink ref="X46" r:id="rId162" xr:uid="{F96F9756-2F53-48EF-B45F-CE45431B096E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId155"/>
+    <tablePart r:id="rId163"/>
   </tableParts>
 </worksheet>
 </file>
